--- a/xls/Amostragem.xlsx
+++ b/xls/Amostragem.xlsx
@@ -1,27 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Camilo\OneDrive\Documentos\estatistica2024\xls\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/eac9aab033b2f962/Documentos/estatistica2025/xls/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="5" documentId="11_4E7C30BA6A8916509F05B54A2979D2F4DD3A67BB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9ACEF6E1-557B-417F-9AF4-E104C6FC6F1E}"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="30" windowWidth="9555" windowHeight="5970"/>
+    <workbookView xWindow="330" yWindow="1740" windowWidth="26610" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Simples" sheetId="1" r:id="rId1"/>
     <sheet name="Estratificada" sheetId="2" r:id="rId2"/>
     <sheet name="Sistemático" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="13">
   <si>
     <t>ID</t>
   </si>
@@ -53,16 +67,19 @@
     <t>nrows</t>
   </si>
   <si>
-    <t>#http://www.dpi.inpe.br/~camilo/estatistica</t>
+    <t>#http://urlib.net/8JMKD2USNRW34T/4D6DMD2</t>
   </si>
   <si>
-    <t>#Estatística: Aplicação ao Sensoriamento Remoto - SER204, INPE, 2024</t>
+    <t>#https://cdrenno.github.io/Estatistica/</t>
+  </si>
+  <si>
+    <t>#Estatística: Aplicação ao Sensoriamento Remoto - SER204, INPE, 2025</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -205,9 +222,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Escritório">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -245,9 +262,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Escritório">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -282,7 +299,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -317,7 +334,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Escritório">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -490,7 +507,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AH222"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -556,9 +573,9 @@
         <f t="shared" ref="W1:AH1" ca="1" si="0">IF(ISNUMBER(MATCH(B1,$S$2:$S$11,0)),B1," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="X1" s="2">
+      <c r="X1" s="2" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>3</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="Y1" s="2" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -656,18 +673,18 @@
       </c>
       <c r="O2">
         <f ca="1">RAND()</f>
-        <v>7.8039930133918411E-2</v>
+        <v>0.37102966958355255</v>
       </c>
       <c r="P2" s="1">
         <v>1</v>
       </c>
       <c r="R2" s="1">
         <f ca="1">SMALL(O:O,ROW(R1))</f>
-        <v>3.3892744375629835E-3</v>
+        <v>2.0191793424561011E-3</v>
       </c>
       <c r="S2">
         <f ca="1">VLOOKUP(R2,O$2:P$222,2,0)</f>
-        <v>3</v>
+        <v>47</v>
       </c>
       <c r="V2" s="2" t="str">
         <f t="shared" ref="V2:V17" ca="1" si="2">IF(ISNUMBER(MATCH(A2,$S$2:$S$11,0)),A2," ")</f>
@@ -685,9 +702,9 @@
         <f t="shared" ref="Y2:Y17" ca="1" si="5">IF(ISNUMBER(MATCH(D2,$S$2:$S$11,0)),D2," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="Z2" s="2" t="str">
+      <c r="Z2" s="2">
         <f t="shared" ref="Z2:Z17" ca="1" si="6">IF(ISNUMBER(MATCH(E2,$S$2:$S$11,0)),E2," ")</f>
-        <v xml:space="preserve"> </v>
+        <v>18</v>
       </c>
       <c r="AA2" s="2" t="str">
         <f t="shared" ref="AA2:AA17" ca="1" si="7">IF(ISNUMBER(MATCH(F2,$S$2:$S$11,0)),F2," ")</f>
@@ -777,26 +794,26 @@
       </c>
       <c r="O3">
         <f t="shared" ref="O3:O66" ca="1" si="28">RAND()</f>
-        <v>0.22010390845330596</v>
+        <v>0.52157335097252822</v>
       </c>
       <c r="P3" s="1">
         <v>2</v>
       </c>
       <c r="R3" s="1">
         <f t="shared" ref="R3:R11" ca="1" si="29">SMALL(O:O,ROW(R2))</f>
-        <v>5.0347954181646504E-3</v>
+        <v>3.134557691421791E-3</v>
       </c>
       <c r="S3">
         <f t="shared" ref="S3:S11" ca="1" si="30">VLOOKUP(R3,O$2:P$222,2,0)</f>
-        <v>217</v>
+        <v>62</v>
       </c>
       <c r="V3" s="2" t="str">
         <f t="shared" ca="1" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="W3" s="2">
+      <c r="W3" s="2" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>28</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="X3" s="2" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -838,9 +855,9 @@
         <f t="shared" ca="1" si="13"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="AH3" s="2">
+      <c r="AH3" s="2" t="str">
         <f t="shared" ca="1" si="14"/>
-        <v>39</v>
+        <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="4" spans="1:34" x14ac:dyDescent="0.25">
@@ -898,18 +915,18 @@
       </c>
       <c r="O4">
         <f t="shared" ca="1" si="28"/>
-        <v>3.3892744375629835E-3</v>
+        <v>0.63380872530826826</v>
       </c>
       <c r="P4" s="1">
         <v>3</v>
       </c>
       <c r="R4" s="1">
         <f t="shared" ca="1" si="29"/>
-        <v>1.0546698119426545E-2</v>
+        <v>5.8647228006990515E-3</v>
       </c>
       <c r="S4">
         <f t="shared" ca="1" si="30"/>
-        <v>39</v>
+        <v>174</v>
       </c>
       <c r="V4" s="2" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -939,9 +956,9 @@
         <f t="shared" ca="1" si="8"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="AC4" s="2" t="str">
+      <c r="AC4" s="2">
         <f t="shared" ca="1" si="9"/>
-        <v xml:space="preserve"> </v>
+        <v>47</v>
       </c>
       <c r="AD4" s="2" t="str">
         <f t="shared" ca="1" si="10"/>
@@ -1019,26 +1036,26 @@
       </c>
       <c r="O5">
         <f t="shared" ca="1" si="28"/>
-        <v>0.95398739084700279</v>
+        <v>0.3117588885773076</v>
       </c>
       <c r="P5" s="1">
         <v>4</v>
       </c>
       <c r="R5" s="1">
         <f t="shared" ca="1" si="29"/>
-        <v>1.6171736832217842E-2</v>
+        <v>9.9997976703954938E-3</v>
       </c>
       <c r="S5">
         <f t="shared" ca="1" si="30"/>
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="V5" s="2" t="str">
         <f t="shared" ca="1" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="W5" s="2">
+      <c r="W5" s="2" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>54</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="X5" s="2" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -1068,9 +1085,9 @@
         <f t="shared" ca="1" si="10"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="AE5" s="2" t="str">
+      <c r="AE5" s="2">
         <f t="shared" ca="1" si="11"/>
-        <v xml:space="preserve"> </v>
+        <v>62</v>
       </c>
       <c r="AF5" s="2" t="str">
         <f t="shared" ca="1" si="12"/>
@@ -1140,18 +1157,18 @@
       </c>
       <c r="O6">
         <f t="shared" ca="1" si="28"/>
-        <v>0.12026594595406148</v>
+        <v>0.54509459625213796</v>
       </c>
       <c r="P6" s="1">
         <v>5</v>
       </c>
       <c r="R6" s="1">
         <f t="shared" ca="1" si="29"/>
-        <v>1.6378581319868579E-2</v>
+        <v>1.0876098334274831E-2</v>
       </c>
       <c r="S6">
         <f t="shared" ca="1" si="30"/>
-        <v>28</v>
+        <v>95</v>
       </c>
       <c r="V6" s="2" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -1261,18 +1278,18 @@
       </c>
       <c r="O7">
         <f t="shared" ca="1" si="28"/>
-        <v>0.89766063926059281</v>
+        <v>0.51005437621835992</v>
       </c>
       <c r="P7" s="1">
         <v>6</v>
       </c>
       <c r="R7" s="1">
         <f t="shared" ca="1" si="29"/>
-        <v>2.1636286840233998E-2</v>
+        <v>2.043789116537853E-2</v>
       </c>
       <c r="S7">
         <f t="shared" ca="1" si="30"/>
-        <v>108</v>
+        <v>171</v>
       </c>
       <c r="V7" s="2" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -1382,18 +1399,18 @@
       </c>
       <c r="O8">
         <f t="shared" ca="1" si="28"/>
-        <v>0.91331161324429355</v>
+        <v>0.5663795707219017</v>
       </c>
       <c r="P8" s="1">
         <v>7</v>
       </c>
       <c r="R8" s="1">
         <f t="shared" ca="1" si="29"/>
-        <v>2.8105359189493195E-2</v>
+        <v>2.1567376858265153E-2</v>
       </c>
       <c r="S8">
         <f t="shared" ca="1" si="30"/>
-        <v>221</v>
+        <v>110</v>
       </c>
       <c r="V8" s="2" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -1407,9 +1424,9 @@
         <f t="shared" ca="1" si="4"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="Y8" s="2" t="str">
+      <c r="Y8" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v xml:space="preserve"> </v>
+        <v>95</v>
       </c>
       <c r="Z8" s="2" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -1503,42 +1520,42 @@
       </c>
       <c r="O9">
         <f t="shared" ca="1" si="28"/>
-        <v>0.5722733989429083</v>
+        <v>0.82494394690037753</v>
       </c>
       <c r="P9" s="1">
         <v>8</v>
       </c>
       <c r="R9" s="1">
         <f t="shared" ca="1" si="29"/>
-        <v>3.2939460795968434E-2</v>
+        <v>2.1602811127403365E-2</v>
       </c>
       <c r="S9">
         <f t="shared" ca="1" si="30"/>
-        <v>54</v>
+        <v>18</v>
       </c>
       <c r="V9" s="2" t="str">
         <f t="shared" ca="1" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="W9" s="2" t="str">
+      <c r="W9" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v xml:space="preserve"> </v>
+        <v>106</v>
       </c>
       <c r="X9" s="2" t="str">
         <f t="shared" ca="1" si="4"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="Y9" s="2">
+      <c r="Y9" s="2" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>108</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="Z9" s="2" t="str">
         <f t="shared" ca="1" si="6"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="AA9" s="2" t="str">
+      <c r="AA9" s="2">
         <f t="shared" ca="1" si="7"/>
-        <v xml:space="preserve"> </v>
+        <v>110</v>
       </c>
       <c r="AB9" s="2" t="str">
         <f t="shared" ca="1" si="8"/>
@@ -1624,18 +1641,18 @@
       </c>
       <c r="O10">
         <f t="shared" ca="1" si="28"/>
-        <v>5.3387151510176256E-2</v>
+        <v>0.51763543851128369</v>
       </c>
       <c r="P10" s="1">
         <v>9</v>
       </c>
       <c r="R10" s="1">
         <f t="shared" ca="1" si="29"/>
-        <v>3.3032987152778914E-2</v>
+        <v>2.4872290531851804E-2</v>
       </c>
       <c r="S10">
         <f t="shared" ca="1" si="30"/>
-        <v>162</v>
+        <v>106</v>
       </c>
       <c r="V10" s="2" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -1745,18 +1762,18 @@
       </c>
       <c r="O11">
         <f t="shared" ca="1" si="28"/>
-        <v>0.87807649845808777</v>
+        <v>0.9768084591494286</v>
       </c>
       <c r="P11" s="1">
         <v>10</v>
       </c>
       <c r="R11" s="1">
         <f t="shared" ca="1" si="29"/>
-        <v>3.5953968040543072E-2</v>
+        <v>2.496026590579703E-2</v>
       </c>
       <c r="S11">
         <f t="shared" ca="1" si="30"/>
-        <v>177</v>
+        <v>141</v>
       </c>
       <c r="V11" s="2" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -1798,9 +1815,9 @@
         <f t="shared" ca="1" si="11"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="AF11" s="2" t="str">
+      <c r="AF11" s="2">
         <f t="shared" ca="1" si="12"/>
-        <v xml:space="preserve"> </v>
+        <v>141</v>
       </c>
       <c r="AG11" s="2" t="str">
         <f t="shared" ca="1" si="13"/>
@@ -1866,7 +1883,7 @@
       </c>
       <c r="O12">
         <f t="shared" ca="1" si="28"/>
-        <v>0.30156225088292954</v>
+        <v>0.78284801737501664</v>
       </c>
       <c r="P12" s="1">
         <v>11</v>
@@ -1979,7 +1996,7 @@
       </c>
       <c r="O13">
         <f t="shared" ca="1" si="28"/>
-        <v>0.58452353294808312</v>
+        <v>0.94377798994688777</v>
       </c>
       <c r="P13" s="1">
         <v>12</v>
@@ -2004,9 +2021,9 @@
         <f t="shared" ca="1" si="6"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="AA13" s="2">
+      <c r="AA13" s="2" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>162</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="AB13" s="2" t="str">
         <f t="shared" ca="1" si="8"/>
@@ -2092,7 +2109,7 @@
       </c>
       <c r="O14">
         <f t="shared" ca="1" si="28"/>
-        <v>0.13490746298610268</v>
+        <v>0.56791494017624755</v>
       </c>
       <c r="P14" s="1">
         <v>13</v>
@@ -2113,9 +2130,9 @@
         <f t="shared" ca="1" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="Z14" s="2" t="str">
+      <c r="Z14" s="2">
         <f t="shared" ca="1" si="6"/>
-        <v xml:space="preserve"> </v>
+        <v>174</v>
       </c>
       <c r="AA14" s="2" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -2125,9 +2142,9 @@
         <f t="shared" ca="1" si="8"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="AC14" s="2">
+      <c r="AC14" s="2" t="str">
         <f t="shared" ca="1" si="9"/>
-        <v>177</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="AD14" s="2" t="str">
         <f t="shared" ca="1" si="10"/>
@@ -2205,14 +2222,14 @@
       </c>
       <c r="O15">
         <f t="shared" ca="1" si="28"/>
-        <v>0.2019318055691488</v>
+        <v>0.4881619094932429</v>
       </c>
       <c r="P15" s="1">
         <v>14</v>
       </c>
-      <c r="V15" s="2" t="str">
+      <c r="V15" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v xml:space="preserve"> </v>
+        <v>183</v>
       </c>
       <c r="W15" s="2" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -2318,7 +2335,7 @@
       </c>
       <c r="O16">
         <f t="shared" ca="1" si="28"/>
-        <v>0.11151785000623216</v>
+        <v>0.85516191515029016</v>
       </c>
       <c r="P16" s="1">
         <v>15</v>
@@ -2431,7 +2448,7 @@
       </c>
       <c r="O17">
         <f t="shared" ca="1" si="28"/>
-        <v>0.11636566249610625</v>
+        <v>0.26573904006182092</v>
       </c>
       <c r="P17" s="1">
         <v>16</v>
@@ -2468,9 +2485,9 @@
         <f t="shared" ca="1" si="9"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="AD17" s="2">
+      <c r="AD17" s="2" t="str">
         <f t="shared" ca="1" si="10"/>
-        <v>217</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="AE17" s="2" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -2484,15 +2501,15 @@
         <f t="shared" ca="1" si="13"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="AH17" s="2">
+      <c r="AH17" s="2" t="str">
         <f t="shared" ca="1" si="14"/>
-        <v>221</v>
+        <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="18" spans="1:34" x14ac:dyDescent="0.25">
       <c r="O18">
         <f t="shared" ca="1" si="28"/>
-        <v>0.85118362592967967</v>
+        <v>4.4122555877982195E-2</v>
       </c>
       <c r="P18" s="1">
         <v>17</v>
@@ -2500,11 +2517,11 @@
     </row>
     <row r="19" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O19">
         <f t="shared" ca="1" si="28"/>
-        <v>0.50548790408206312</v>
+        <v>2.1602811127403365E-2</v>
       </c>
       <c r="P19" s="1">
         <v>18</v>
@@ -2516,16 +2533,19 @@
       </c>
       <c r="O20">
         <f t="shared" ca="1" si="28"/>
-        <v>0.66190894842506676</v>
+        <v>0.50949092136283192</v>
       </c>
       <c r="P20" s="1">
         <v>19</v>
       </c>
     </row>
     <row r="21" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>11</v>
+      </c>
       <c r="O21">
         <f t="shared" ca="1" si="28"/>
-        <v>0.42763345675735198</v>
+        <v>0.38293590227926178</v>
       </c>
       <c r="P21" s="1">
         <v>20</v>
@@ -2534,7 +2554,7 @@
     <row r="22" spans="1:34" x14ac:dyDescent="0.25">
       <c r="O22">
         <f t="shared" ca="1" si="28"/>
-        <v>0.81320269651558208</v>
+        <v>0.10403086450863352</v>
       </c>
       <c r="P22" s="1">
         <v>21</v>
@@ -2543,7 +2563,7 @@
     <row r="23" spans="1:34" x14ac:dyDescent="0.25">
       <c r="O23">
         <f t="shared" ca="1" si="28"/>
-        <v>0.71874493498920222</v>
+        <v>0.66199899030155918</v>
       </c>
       <c r="P23" s="1">
         <v>22</v>
@@ -2552,7 +2572,7 @@
     <row r="24" spans="1:34" x14ac:dyDescent="0.25">
       <c r="O24">
         <f t="shared" ca="1" si="28"/>
-        <v>0.28965161016795815</v>
+        <v>0.57929792754602849</v>
       </c>
       <c r="P24" s="1">
         <v>23</v>
@@ -2561,7 +2581,7 @@
     <row r="25" spans="1:34" x14ac:dyDescent="0.25">
       <c r="O25">
         <f t="shared" ca="1" si="28"/>
-        <v>0.11789860874810043</v>
+        <v>0.18681650081644618</v>
       </c>
       <c r="P25" s="1">
         <v>24</v>
@@ -2570,7 +2590,7 @@
     <row r="26" spans="1:34" x14ac:dyDescent="0.25">
       <c r="O26">
         <f t="shared" ca="1" si="28"/>
-        <v>0.94628630660154478</v>
+        <v>0.40530570492740725</v>
       </c>
       <c r="P26" s="1">
         <v>25</v>
@@ -2579,7 +2599,7 @@
     <row r="27" spans="1:34" x14ac:dyDescent="0.25">
       <c r="O27">
         <f t="shared" ca="1" si="28"/>
-        <v>0.43651643970440046</v>
+        <v>0.43327522580525679</v>
       </c>
       <c r="P27" s="1">
         <v>26</v>
@@ -2588,7 +2608,7 @@
     <row r="28" spans="1:34" x14ac:dyDescent="0.25">
       <c r="O28">
         <f t="shared" ca="1" si="28"/>
-        <v>0.54627646428503152</v>
+        <v>0.32810127683493273</v>
       </c>
       <c r="P28" s="1">
         <v>27</v>
@@ -2597,7 +2617,7 @@
     <row r="29" spans="1:34" x14ac:dyDescent="0.25">
       <c r="O29">
         <f t="shared" ca="1" si="28"/>
-        <v>1.6378581319868579E-2</v>
+        <v>0.85484959849554187</v>
       </c>
       <c r="P29" s="1">
         <v>28</v>
@@ -2606,7 +2626,7 @@
     <row r="30" spans="1:34" x14ac:dyDescent="0.25">
       <c r="O30">
         <f t="shared" ca="1" si="28"/>
-        <v>0.56972432304692389</v>
+        <v>0.59696064086587441</v>
       </c>
       <c r="P30" s="1">
         <v>29</v>
@@ -2615,7 +2635,7 @@
     <row r="31" spans="1:34" x14ac:dyDescent="0.25">
       <c r="O31">
         <f t="shared" ca="1" si="28"/>
-        <v>0.3439236450852754</v>
+        <v>0.78807818817708064</v>
       </c>
       <c r="P31" s="1">
         <v>30</v>
@@ -2624,7 +2644,7 @@
     <row r="32" spans="1:34" x14ac:dyDescent="0.25">
       <c r="O32">
         <f t="shared" ca="1" si="28"/>
-        <v>0.14912709589830786</v>
+        <v>0.60507273032808739</v>
       </c>
       <c r="P32" s="1">
         <v>31</v>
@@ -2633,7 +2653,7 @@
     <row r="33" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O33">
         <f t="shared" ca="1" si="28"/>
-        <v>0.90710204293868935</v>
+        <v>0.74922628934047153</v>
       </c>
       <c r="P33" s="1">
         <v>32</v>
@@ -2642,7 +2662,7 @@
     <row r="34" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O34">
         <f t="shared" ca="1" si="28"/>
-        <v>0.15010218968618283</v>
+        <v>0.43020444317209561</v>
       </c>
       <c r="P34" s="1">
         <v>33</v>
@@ -2651,7 +2671,7 @@
     <row r="35" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O35">
         <f t="shared" ca="1" si="28"/>
-        <v>0.97380672225147913</v>
+        <v>0.75671837232957806</v>
       </c>
       <c r="P35" s="1">
         <v>34</v>
@@ -2660,7 +2680,7 @@
     <row r="36" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O36">
         <f t="shared" ca="1" si="28"/>
-        <v>0.86330125563524307</v>
+        <v>0.79568915211013713</v>
       </c>
       <c r="P36" s="1">
         <v>35</v>
@@ -2669,7 +2689,7 @@
     <row r="37" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O37">
         <f t="shared" ca="1" si="28"/>
-        <v>0.43936887342379627</v>
+        <v>0.70449353362568601</v>
       </c>
       <c r="P37" s="1">
         <v>36</v>
@@ -2678,7 +2698,7 @@
     <row r="38" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O38">
         <f t="shared" ca="1" si="28"/>
-        <v>0.45299585016047994</v>
+        <v>0.54292924838758205</v>
       </c>
       <c r="P38" s="1">
         <v>37</v>
@@ -2687,7 +2707,7 @@
     <row r="39" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O39">
         <f t="shared" ca="1" si="28"/>
-        <v>0.94040411691983539</v>
+        <v>0.43388098338988601</v>
       </c>
       <c r="P39" s="1">
         <v>38</v>
@@ -2696,7 +2716,7 @@
     <row r="40" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O40">
         <f t="shared" ca="1" si="28"/>
-        <v>1.0546698119426545E-2</v>
+        <v>0.33783337933943547</v>
       </c>
       <c r="P40" s="1">
         <v>39</v>
@@ -2705,7 +2725,7 @@
     <row r="41" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O41">
         <f t="shared" ca="1" si="28"/>
-        <v>0.48988621747899153</v>
+        <v>0.67478873896790381</v>
       </c>
       <c r="P41" s="1">
         <v>40</v>
@@ -2714,7 +2734,7 @@
     <row r="42" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O42">
         <f t="shared" ca="1" si="28"/>
-        <v>0.13464655093180455</v>
+        <v>0.84771265139377228</v>
       </c>
       <c r="P42" s="1">
         <v>41</v>
@@ -2723,7 +2743,7 @@
     <row r="43" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O43">
         <f t="shared" ca="1" si="28"/>
-        <v>0.41963482764613014</v>
+        <v>0.19614379752005506</v>
       </c>
       <c r="P43" s="1">
         <v>42</v>
@@ -2732,7 +2752,7 @@
     <row r="44" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O44">
         <f t="shared" ca="1" si="28"/>
-        <v>0.3929899812633727</v>
+        <v>0.69571575606989555</v>
       </c>
       <c r="P44" s="1">
         <v>43</v>
@@ -2741,7 +2761,7 @@
     <row r="45" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O45">
         <f t="shared" ca="1" si="28"/>
-        <v>0.92759627693728564</v>
+        <v>0.4508797028528494</v>
       </c>
       <c r="P45" s="1">
         <v>44</v>
@@ -2750,7 +2770,7 @@
     <row r="46" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O46">
         <f t="shared" ca="1" si="28"/>
-        <v>0.71028002066259355</v>
+        <v>0.17859237453903565</v>
       </c>
       <c r="P46" s="1">
         <v>45</v>
@@ -2759,7 +2779,7 @@
     <row r="47" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O47">
         <f t="shared" ca="1" si="28"/>
-        <v>0.33760000531609058</v>
+        <v>0.45618890210766461</v>
       </c>
       <c r="P47" s="1">
         <v>46</v>
@@ -2768,7 +2788,7 @@
     <row r="48" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O48">
         <f t="shared" ca="1" si="28"/>
-        <v>0.75130116786223067</v>
+        <v>2.0191793424561011E-3</v>
       </c>
       <c r="P48" s="1">
         <v>47</v>
@@ -2777,7 +2797,7 @@
     <row r="49" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O49">
         <f t="shared" ca="1" si="28"/>
-        <v>0.87351705772008681</v>
+        <v>0.60969741229845043</v>
       </c>
       <c r="P49" s="1">
         <v>48</v>
@@ -2786,7 +2806,7 @@
     <row r="50" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O50">
         <f t="shared" ca="1" si="28"/>
-        <v>0.11162090312325412</v>
+        <v>0.66382264484389664</v>
       </c>
       <c r="P50" s="1">
         <v>49</v>
@@ -2795,7 +2815,7 @@
     <row r="51" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O51">
         <f t="shared" ca="1" si="28"/>
-        <v>0.90732266334518519</v>
+        <v>0.95705523125701253</v>
       </c>
       <c r="P51" s="1">
         <v>50</v>
@@ -2804,7 +2824,7 @@
     <row r="52" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O52">
         <f t="shared" ca="1" si="28"/>
-        <v>0.5255849758196226</v>
+        <v>0.66744084382289759</v>
       </c>
       <c r="P52" s="1">
         <v>51</v>
@@ -2813,7 +2833,7 @@
     <row r="53" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O53">
         <f t="shared" ca="1" si="28"/>
-        <v>0.19583813387293503</v>
+        <v>0.39898415743665983</v>
       </c>
       <c r="P53" s="1">
         <v>52</v>
@@ -2822,7 +2842,7 @@
     <row r="54" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O54">
         <f t="shared" ca="1" si="28"/>
-        <v>0.65779504096631147</v>
+        <v>0.91016522653306331</v>
       </c>
       <c r="P54" s="1">
         <v>53</v>
@@ -2831,7 +2851,7 @@
     <row r="55" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O55">
         <f t="shared" ca="1" si="28"/>
-        <v>3.2939460795968434E-2</v>
+        <v>0.62599551713930812</v>
       </c>
       <c r="P55" s="1">
         <v>54</v>
@@ -2840,7 +2860,7 @@
     <row r="56" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O56">
         <f t="shared" ca="1" si="28"/>
-        <v>0.24213816390639908</v>
+        <v>9.0319112608777674E-2</v>
       </c>
       <c r="P56" s="1">
         <v>55</v>
@@ -2849,7 +2869,7 @@
     <row r="57" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O57">
         <f t="shared" ca="1" si="28"/>
-        <v>0.85212643503863494</v>
+        <v>0.86646538354934843</v>
       </c>
       <c r="P57" s="1">
         <v>56</v>
@@ -2858,7 +2878,7 @@
     <row r="58" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O58">
         <f t="shared" ca="1" si="28"/>
-        <v>0.18723186140620651</v>
+        <v>0.40907002604899423</v>
       </c>
       <c r="P58" s="1">
         <v>57</v>
@@ -2867,7 +2887,7 @@
     <row r="59" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O59">
         <f t="shared" ca="1" si="28"/>
-        <v>0.21062469384036819</v>
+        <v>0.67004623607692304</v>
       </c>
       <c r="P59" s="1">
         <v>58</v>
@@ -2876,7 +2896,7 @@
     <row r="60" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O60">
         <f t="shared" ca="1" si="28"/>
-        <v>6.5476375057842762E-2</v>
+        <v>0.65420911693824546</v>
       </c>
       <c r="P60" s="1">
         <v>59</v>
@@ -2885,7 +2905,7 @@
     <row r="61" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O61">
         <f t="shared" ca="1" si="28"/>
-        <v>0.27938268431344115</v>
+        <v>0.92796509401366678</v>
       </c>
       <c r="P61" s="1">
         <v>60</v>
@@ -2894,7 +2914,7 @@
     <row r="62" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O62">
         <f t="shared" ca="1" si="28"/>
-        <v>0.32017173208618077</v>
+        <v>0.52811227181591003</v>
       </c>
       <c r="P62" s="1">
         <v>61</v>
@@ -2903,7 +2923,7 @@
     <row r="63" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O63">
         <f t="shared" ca="1" si="28"/>
-        <v>0.83776117157118568</v>
+        <v>3.134557691421791E-3</v>
       </c>
       <c r="P63" s="1">
         <v>62</v>
@@ -2912,7 +2932,7 @@
     <row r="64" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O64">
         <f t="shared" ca="1" si="28"/>
-        <v>0.4541773986600931</v>
+        <v>0.54267903475901136</v>
       </c>
       <c r="P64" s="1">
         <v>63</v>
@@ -2921,7 +2941,7 @@
     <row r="65" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O65">
         <f t="shared" ca="1" si="28"/>
-        <v>0.52381930623953066</v>
+        <v>7.0848575465014996E-2</v>
       </c>
       <c r="P65" s="1">
         <v>64</v>
@@ -2930,7 +2950,7 @@
     <row r="66" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O66">
         <f t="shared" ca="1" si="28"/>
-        <v>0.57430578933628817</v>
+        <v>0.82802963644508942</v>
       </c>
       <c r="P66" s="1">
         <v>65</v>
@@ -2939,7 +2959,7 @@
     <row r="67" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O67">
         <f t="shared" ref="O67:O130" ca="1" si="31">RAND()</f>
-        <v>0.69088683700121267</v>
+        <v>0.93039830240936638</v>
       </c>
       <c r="P67" s="1">
         <v>66</v>
@@ -2948,7 +2968,7 @@
     <row r="68" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O68">
         <f t="shared" ca="1" si="31"/>
-        <v>0.63163389249754898</v>
+        <v>0.32292467180316009</v>
       </c>
       <c r="P68" s="1">
         <v>67</v>
@@ -2957,7 +2977,7 @@
     <row r="69" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O69">
         <f t="shared" ca="1" si="31"/>
-        <v>0.21288172274249484</v>
+        <v>0.36243339814992859</v>
       </c>
       <c r="P69" s="1">
         <v>68</v>
@@ -2966,7 +2986,7 @@
     <row r="70" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O70">
         <f t="shared" ca="1" si="31"/>
-        <v>0.10932393231780446</v>
+        <v>0.60584159362207746</v>
       </c>
       <c r="P70" s="1">
         <v>69</v>
@@ -2975,7 +2995,7 @@
     <row r="71" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O71">
         <f t="shared" ca="1" si="31"/>
-        <v>9.7358352885341226E-2</v>
+        <v>0.11713456746873352</v>
       </c>
       <c r="P71" s="1">
         <v>70</v>
@@ -2984,7 +3004,7 @@
     <row r="72" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O72">
         <f t="shared" ca="1" si="31"/>
-        <v>0.42405474964380585</v>
+        <v>0.91711939450652213</v>
       </c>
       <c r="P72" s="1">
         <v>71</v>
@@ -2993,7 +3013,7 @@
     <row r="73" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O73">
         <f t="shared" ca="1" si="31"/>
-        <v>0.85717221586785419</v>
+        <v>0.55367897065532246</v>
       </c>
       <c r="P73" s="1">
         <v>72</v>
@@ -3002,7 +3022,7 @@
     <row r="74" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O74">
         <f t="shared" ca="1" si="31"/>
-        <v>0.25501626806331013</v>
+        <v>0.71957787091052461</v>
       </c>
       <c r="P74" s="1">
         <v>73</v>
@@ -3011,7 +3031,7 @@
     <row r="75" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O75">
         <f t="shared" ca="1" si="31"/>
-        <v>0.12421443753429995</v>
+        <v>0.90282823498110354</v>
       </c>
       <c r="P75" s="1">
         <v>74</v>
@@ -3020,7 +3040,7 @@
     <row r="76" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O76">
         <f t="shared" ca="1" si="31"/>
-        <v>0.11012324002775409</v>
+        <v>0.56214732769817166</v>
       </c>
       <c r="P76" s="1">
         <v>75</v>
@@ -3029,7 +3049,7 @@
     <row r="77" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O77">
         <f t="shared" ca="1" si="31"/>
-        <v>4.1120826754364015E-2</v>
+        <v>0.28595600135760202</v>
       </c>
       <c r="P77" s="1">
         <v>76</v>
@@ -3038,7 +3058,7 @@
     <row r="78" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O78">
         <f t="shared" ca="1" si="31"/>
-        <v>0.5484905193579539</v>
+        <v>2.9168653973689063E-2</v>
       </c>
       <c r="P78" s="1">
         <v>77</v>
@@ -3047,7 +3067,7 @@
     <row r="79" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O79">
         <f t="shared" ca="1" si="31"/>
-        <v>0.4622673560869508</v>
+        <v>0.60736521054292547</v>
       </c>
       <c r="P79" s="1">
         <v>78</v>
@@ -3056,7 +3076,7 @@
     <row r="80" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O80">
         <f t="shared" ca="1" si="31"/>
-        <v>0.11502615219894863</v>
+        <v>0.63721069796361174</v>
       </c>
       <c r="P80" s="1">
         <v>79</v>
@@ -3065,7 +3085,7 @@
     <row r="81" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O81">
         <f t="shared" ca="1" si="31"/>
-        <v>4.5200206228634632E-2</v>
+        <v>0.81462816034269125</v>
       </c>
       <c r="P81" s="1">
         <v>80</v>
@@ -3074,7 +3094,7 @@
     <row r="82" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O82">
         <f t="shared" ca="1" si="31"/>
-        <v>0.39537109273518034</v>
+        <v>0.91037613502909376</v>
       </c>
       <c r="P82" s="1">
         <v>81</v>
@@ -3083,7 +3103,7 @@
     <row r="83" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O83">
         <f t="shared" ca="1" si="31"/>
-        <v>0.43152518770263859</v>
+        <v>5.4968297360973417E-2</v>
       </c>
       <c r="P83" s="1">
         <v>82</v>
@@ -3092,7 +3112,7 @@
     <row r="84" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O84">
         <f t="shared" ca="1" si="31"/>
-        <v>0.72064988072218872</v>
+        <v>0.53871992953234638</v>
       </c>
       <c r="P84" s="1">
         <v>83</v>
@@ -3101,7 +3121,7 @@
     <row r="85" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O85">
         <f t="shared" ca="1" si="31"/>
-        <v>0.70614251951083096</v>
+        <v>0.19803158125461151</v>
       </c>
       <c r="P85" s="1">
         <v>84</v>
@@ -3110,7 +3130,7 @@
     <row r="86" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O86">
         <f t="shared" ca="1" si="31"/>
-        <v>0.21228134524409525</v>
+        <v>0.67765472518094116</v>
       </c>
       <c r="P86" s="1">
         <v>85</v>
@@ -3119,7 +3139,7 @@
     <row r="87" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O87">
         <f t="shared" ca="1" si="31"/>
-        <v>0.82607964681087664</v>
+        <v>0.47701583087396604</v>
       </c>
       <c r="P87" s="1">
         <v>86</v>
@@ -3128,7 +3148,7 @@
     <row r="88" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O88">
         <f t="shared" ca="1" si="31"/>
-        <v>0.66562071278894019</v>
+        <v>0.9953717896134191</v>
       </c>
       <c r="P88" s="1">
         <v>87</v>
@@ -3137,7 +3157,7 @@
     <row r="89" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O89">
         <f t="shared" ca="1" si="31"/>
-        <v>0.10230852710739469</v>
+        <v>0.60296355502827259</v>
       </c>
       <c r="P89" s="1">
         <v>88</v>
@@ -3146,7 +3166,7 @@
     <row r="90" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O90">
         <f t="shared" ca="1" si="31"/>
-        <v>0.75443765944835472</v>
+        <v>0.2504515002470995</v>
       </c>
       <c r="P90" s="1">
         <v>89</v>
@@ -3155,7 +3175,7 @@
     <row r="91" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O91">
         <f t="shared" ca="1" si="31"/>
-        <v>0.83132174858356278</v>
+        <v>0.8422036527324428</v>
       </c>
       <c r="P91" s="1">
         <v>90</v>
@@ -3164,7 +3184,7 @@
     <row r="92" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O92">
         <f t="shared" ca="1" si="31"/>
-        <v>0.86672744990388195</v>
+        <v>0.16916195424214331</v>
       </c>
       <c r="P92" s="1">
         <v>91</v>
@@ -3173,7 +3193,7 @@
     <row r="93" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O93">
         <f t="shared" ca="1" si="31"/>
-        <v>0.54214540421896795</v>
+        <v>0.19041296124807461</v>
       </c>
       <c r="P93" s="1">
         <v>92</v>
@@ -3182,7 +3202,7 @@
     <row r="94" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O94">
         <f t="shared" ca="1" si="31"/>
-        <v>0.53505739146085363</v>
+        <v>0.71714373558348354</v>
       </c>
       <c r="P94" s="1">
         <v>93</v>
@@ -3191,7 +3211,7 @@
     <row r="95" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O95">
         <f t="shared" ca="1" si="31"/>
-        <v>0.32224952148154107</v>
+        <v>0.5104372183439998</v>
       </c>
       <c r="P95" s="1">
         <v>94</v>
@@ -3200,7 +3220,7 @@
     <row r="96" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O96">
         <f t="shared" ca="1" si="31"/>
-        <v>0.31813308072196778</v>
+        <v>1.0876098334274831E-2</v>
       </c>
       <c r="P96" s="1">
         <v>95</v>
@@ -3209,7 +3229,7 @@
     <row r="97" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O97">
         <f t="shared" ca="1" si="31"/>
-        <v>0.93271010652068809</v>
+        <v>0.1624291859768392</v>
       </c>
       <c r="P97" s="1">
         <v>96</v>
@@ -3218,7 +3238,7 @@
     <row r="98" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O98">
         <f t="shared" ca="1" si="31"/>
-        <v>0.34156663991238512</v>
+        <v>0.91746167328523687</v>
       </c>
       <c r="P98" s="1">
         <v>97</v>
@@ -3227,7 +3247,7 @@
     <row r="99" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O99">
         <f t="shared" ca="1" si="31"/>
-        <v>0.67050890656624385</v>
+        <v>0.79631408241411106</v>
       </c>
       <c r="P99" s="1">
         <v>98</v>
@@ -3236,7 +3256,7 @@
     <row r="100" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O100">
         <f t="shared" ca="1" si="31"/>
-        <v>0.6529890138068799</v>
+        <v>0.99632539031565759</v>
       </c>
       <c r="P100" s="1">
         <v>99</v>
@@ -3245,7 +3265,7 @@
     <row r="101" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O101">
         <f t="shared" ca="1" si="31"/>
-        <v>0.33865223427120728</v>
+        <v>0.48044757108451408</v>
       </c>
       <c r="P101" s="1">
         <v>100</v>
@@ -3254,7 +3274,7 @@
     <row r="102" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O102">
         <f t="shared" ca="1" si="31"/>
-        <v>0.56277087658813651</v>
+        <v>0.50756400186222717</v>
       </c>
       <c r="P102" s="1">
         <v>101</v>
@@ -3263,7 +3283,7 @@
     <row r="103" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O103">
         <f t="shared" ca="1" si="31"/>
-        <v>0.66667301254099121</v>
+        <v>0.66587433455487077</v>
       </c>
       <c r="P103" s="1">
         <v>102</v>
@@ -3272,7 +3292,7 @@
     <row r="104" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O104">
         <f t="shared" ca="1" si="31"/>
-        <v>0.87871163484223935</v>
+        <v>0.68929232624988379</v>
       </c>
       <c r="P104" s="1">
         <v>103</v>
@@ -3281,7 +3301,7 @@
     <row r="105" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O105">
         <f t="shared" ca="1" si="31"/>
-        <v>0.52841521754062659</v>
+        <v>0.72518088675187298</v>
       </c>
       <c r="P105" s="1">
         <v>104</v>
@@ -3290,7 +3310,7 @@
     <row r="106" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O106">
         <f t="shared" ca="1" si="31"/>
-        <v>0.26249890716406155</v>
+        <v>0.41492760649780125</v>
       </c>
       <c r="P106" s="1">
         <v>105</v>
@@ -3299,7 +3319,7 @@
     <row r="107" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O107">
         <f t="shared" ca="1" si="31"/>
-        <v>0.18196743665585124</v>
+        <v>2.4872290531851804E-2</v>
       </c>
       <c r="P107" s="1">
         <v>106</v>
@@ -3308,7 +3328,7 @@
     <row r="108" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O108">
         <f t="shared" ca="1" si="31"/>
-        <v>0.81840375752174399</v>
+        <v>6.4474859784251271E-2</v>
       </c>
       <c r="P108" s="1">
         <v>107</v>
@@ -3317,7 +3337,7 @@
     <row r="109" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O109">
         <f t="shared" ca="1" si="31"/>
-        <v>2.1636286840233998E-2</v>
+        <v>0.32786625687497406</v>
       </c>
       <c r="P109" s="1">
         <v>108</v>
@@ -3326,7 +3346,7 @@
     <row r="110" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O110">
         <f t="shared" ca="1" si="31"/>
-        <v>0.22993056914782539</v>
+        <v>0.98280473646816258</v>
       </c>
       <c r="P110" s="1">
         <v>109</v>
@@ -3335,7 +3355,7 @@
     <row r="111" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O111">
         <f t="shared" ca="1" si="31"/>
-        <v>0.49398080449942317</v>
+        <v>2.1567376858265153E-2</v>
       </c>
       <c r="P111" s="1">
         <v>110</v>
@@ -3344,7 +3364,7 @@
     <row r="112" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O112">
         <f t="shared" ca="1" si="31"/>
-        <v>0.72310040327488834</v>
+        <v>0.72423513309502774</v>
       </c>
       <c r="P112" s="1">
         <v>111</v>
@@ -3353,7 +3373,7 @@
     <row r="113" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O113">
         <f t="shared" ca="1" si="31"/>
-        <v>0.38853815159575567</v>
+        <v>0.70849985449114783</v>
       </c>
       <c r="P113" s="1">
         <v>112</v>
@@ -3362,7 +3382,7 @@
     <row r="114" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O114">
         <f t="shared" ca="1" si="31"/>
-        <v>0.82208872209765105</v>
+        <v>0.8361117802596244</v>
       </c>
       <c r="P114" s="1">
         <v>113</v>
@@ -3371,7 +3391,7 @@
     <row r="115" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O115">
         <f t="shared" ca="1" si="31"/>
-        <v>0.3751301928959293</v>
+        <v>0.68010145468997629</v>
       </c>
       <c r="P115" s="1">
         <v>114</v>
@@ -3380,7 +3400,7 @@
     <row r="116" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O116">
         <f t="shared" ca="1" si="31"/>
-        <v>0.34163169190986042</v>
+        <v>0.11657535518248574</v>
       </c>
       <c r="P116" s="1">
         <v>115</v>
@@ -3389,7 +3409,7 @@
     <row r="117" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O117">
         <f t="shared" ca="1" si="31"/>
-        <v>0.65519212306351615</v>
+        <v>0.785828441240498</v>
       </c>
       <c r="P117" s="1">
         <v>116</v>
@@ -3398,7 +3418,7 @@
     <row r="118" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O118">
         <f t="shared" ca="1" si="31"/>
-        <v>0.82883775277200877</v>
+        <v>0.13505586812171488</v>
       </c>
       <c r="P118" s="1">
         <v>117</v>
@@ -3407,7 +3427,7 @@
     <row r="119" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O119">
         <f t="shared" ca="1" si="31"/>
-        <v>0.35990944555919724</v>
+        <v>0.82411230217701925</v>
       </c>
       <c r="P119" s="1">
         <v>118</v>
@@ -3416,7 +3436,7 @@
     <row r="120" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O120">
         <f t="shared" ca="1" si="31"/>
-        <v>0.64925296549072864</v>
+        <v>0.13698393131398234</v>
       </c>
       <c r="P120" s="1">
         <v>119</v>
@@ -3425,7 +3445,7 @@
     <row r="121" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O121">
         <f t="shared" ca="1" si="31"/>
-        <v>0.39415915269884561</v>
+        <v>0.15011548775569883</v>
       </c>
       <c r="P121" s="1">
         <v>120</v>
@@ -3434,7 +3454,7 @@
     <row r="122" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O122">
         <f t="shared" ca="1" si="31"/>
-        <v>0.37883514047015965</v>
+        <v>0.33208773736786845</v>
       </c>
       <c r="P122" s="1">
         <v>121</v>
@@ -3443,7 +3463,7 @@
     <row r="123" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O123">
         <f t="shared" ca="1" si="31"/>
-        <v>0.3572383231205859</v>
+        <v>0.26813588114065268</v>
       </c>
       <c r="P123" s="1">
         <v>122</v>
@@ -3452,7 +3472,7 @@
     <row r="124" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O124">
         <f t="shared" ca="1" si="31"/>
-        <v>0.70965442931319955</v>
+        <v>0.92196776053228335</v>
       </c>
       <c r="P124" s="1">
         <v>123</v>
@@ -3461,7 +3481,7 @@
     <row r="125" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O125">
         <f t="shared" ca="1" si="31"/>
-        <v>0.89730809521589638</v>
+        <v>0.49118736941859731</v>
       </c>
       <c r="P125" s="1">
         <v>124</v>
@@ -3470,7 +3490,7 @@
     <row r="126" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O126">
         <f t="shared" ca="1" si="31"/>
-        <v>0.57340327162453619</v>
+        <v>0.82853278720272339</v>
       </c>
       <c r="P126" s="1">
         <v>125</v>
@@ -3479,7 +3499,7 @@
     <row r="127" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O127">
         <f t="shared" ca="1" si="31"/>
-        <v>0.90686044904424501</v>
+        <v>0.96015135877776248</v>
       </c>
       <c r="P127" s="1">
         <v>126</v>
@@ -3488,7 +3508,7 @@
     <row r="128" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O128">
         <f t="shared" ca="1" si="31"/>
-        <v>0.3499345904614336</v>
+        <v>0.30290632972651699</v>
       </c>
       <c r="P128" s="1">
         <v>127</v>
@@ -3497,7 +3517,7 @@
     <row r="129" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O129">
         <f t="shared" ca="1" si="31"/>
-        <v>0.80619017491800649</v>
+        <v>0.60495503284161145</v>
       </c>
       <c r="P129" s="1">
         <v>128</v>
@@ -3506,7 +3526,7 @@
     <row r="130" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O130">
         <f t="shared" ca="1" si="31"/>
-        <v>0.88937169748392508</v>
+        <v>0.44274706306232103</v>
       </c>
       <c r="P130" s="1">
         <v>129</v>
@@ -3515,7 +3535,7 @@
     <row r="131" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O131">
         <f t="shared" ref="O131:O194" ca="1" si="32">RAND()</f>
-        <v>0.91360495458345903</v>
+        <v>0.35196722874369657</v>
       </c>
       <c r="P131" s="1">
         <v>130</v>
@@ -3524,7 +3544,7 @@
     <row r="132" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O132">
         <f t="shared" ca="1" si="32"/>
-        <v>0.13590340049749461</v>
+        <v>0.70528369745677877</v>
       </c>
       <c r="P132" s="1">
         <v>131</v>
@@ -3533,7 +3553,7 @@
     <row r="133" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O133">
         <f t="shared" ca="1" si="32"/>
-        <v>0.74313728919014388</v>
+        <v>0.67262272412633217</v>
       </c>
       <c r="P133" s="1">
         <v>132</v>
@@ -3542,7 +3562,7 @@
     <row r="134" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O134">
         <f t="shared" ca="1" si="32"/>
-        <v>6.7693913975196085E-2</v>
+        <v>0.31019658883370549</v>
       </c>
       <c r="P134" s="1">
         <v>133</v>
@@ -3551,7 +3571,7 @@
     <row r="135" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O135">
         <f t="shared" ca="1" si="32"/>
-        <v>0.34985113098801024</v>
+        <v>0.96678661400499066</v>
       </c>
       <c r="P135" s="1">
         <v>134</v>
@@ -3560,7 +3580,7 @@
     <row r="136" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O136">
         <f t="shared" ca="1" si="32"/>
-        <v>0.13053879120432443</v>
+        <v>0.85906860087074066</v>
       </c>
       <c r="P136" s="1">
         <v>135</v>
@@ -3569,7 +3589,7 @@
     <row r="137" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O137">
         <f t="shared" ca="1" si="32"/>
-        <v>0.45393978153729653</v>
+        <v>0.75896553026846625</v>
       </c>
       <c r="P137" s="1">
         <v>136</v>
@@ -3578,7 +3598,7 @@
     <row r="138" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O138">
         <f t="shared" ca="1" si="32"/>
-        <v>0.40748981448083199</v>
+        <v>5.7108499154303272E-2</v>
       </c>
       <c r="P138" s="1">
         <v>137</v>
@@ -3587,7 +3607,7 @@
     <row r="139" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O139">
         <f t="shared" ca="1" si="32"/>
-        <v>0.44370684567356355</v>
+        <v>0.36255180480669624</v>
       </c>
       <c r="P139" s="1">
         <v>138</v>
@@ -3596,7 +3616,7 @@
     <row r="140" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O140">
         <f t="shared" ca="1" si="32"/>
-        <v>0.48090234606999505</v>
+        <v>0.10250334862150412</v>
       </c>
       <c r="P140" s="1">
         <v>139</v>
@@ -3605,7 +3625,7 @@
     <row r="141" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O141">
         <f t="shared" ca="1" si="32"/>
-        <v>0.19651211889007258</v>
+        <v>0.13608167162239948</v>
       </c>
       <c r="P141" s="1">
         <v>140</v>
@@ -3614,7 +3634,7 @@
     <row r="142" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O142">
         <f t="shared" ca="1" si="32"/>
-        <v>0.98829333443670875</v>
+        <v>2.496026590579703E-2</v>
       </c>
       <c r="P142" s="1">
         <v>141</v>
@@ -3623,7 +3643,7 @@
     <row r="143" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O143">
         <f t="shared" ca="1" si="32"/>
-        <v>0.2443588464917128</v>
+        <v>0.33787865183972765</v>
       </c>
       <c r="P143" s="1">
         <v>142</v>
@@ -3632,7 +3652,7 @@
     <row r="144" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O144">
         <f t="shared" ca="1" si="32"/>
-        <v>0.20128730224020519</v>
+        <v>0.32122947831847681</v>
       </c>
       <c r="P144" s="1">
         <v>143</v>
@@ -3641,7 +3661,7 @@
     <row r="145" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O145">
         <f t="shared" ca="1" si="32"/>
-        <v>0.68834154665341218</v>
+        <v>0.21570467384455738</v>
       </c>
       <c r="P145" s="1">
         <v>144</v>
@@ -3650,7 +3670,7 @@
     <row r="146" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O146">
         <f t="shared" ca="1" si="32"/>
-        <v>0.17332366166269975</v>
+        <v>8.3187238755551896E-2</v>
       </c>
       <c r="P146" s="1">
         <v>145</v>
@@ -3659,7 +3679,7 @@
     <row r="147" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O147">
         <f t="shared" ca="1" si="32"/>
-        <v>0.61906902627557892</v>
+        <v>0.10216043399934338</v>
       </c>
       <c r="P147" s="1">
         <v>146</v>
@@ -3668,7 +3688,7 @@
     <row r="148" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O148">
         <f t="shared" ca="1" si="32"/>
-        <v>0.85970476484852898</v>
+        <v>0.57068108631110903</v>
       </c>
       <c r="P148" s="1">
         <v>147</v>
@@ -3677,7 +3697,7 @@
     <row r="149" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O149">
         <f t="shared" ca="1" si="32"/>
-        <v>0.11031244990629929</v>
+        <v>0.42405091624656033</v>
       </c>
       <c r="P149" s="1">
         <v>148</v>
@@ -3686,7 +3706,7 @@
     <row r="150" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O150">
         <f t="shared" ca="1" si="32"/>
-        <v>0.86765787775677261</v>
+        <v>0.48323474957528911</v>
       </c>
       <c r="P150" s="1">
         <v>149</v>
@@ -3695,7 +3715,7 @@
     <row r="151" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O151">
         <f t="shared" ca="1" si="32"/>
-        <v>0.99996062424347976</v>
+        <v>0.66228742058501477</v>
       </c>
       <c r="P151" s="1">
         <v>150</v>
@@ -3704,7 +3724,7 @@
     <row r="152" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O152">
         <f t="shared" ca="1" si="32"/>
-        <v>0.46469506229876201</v>
+        <v>0.66453772645222686</v>
       </c>
       <c r="P152" s="1">
         <v>151</v>
@@ -3713,7 +3733,7 @@
     <row r="153" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O153">
         <f t="shared" ca="1" si="32"/>
-        <v>0.52549761337875267</v>
+        <v>0.10796709734928545</v>
       </c>
       <c r="P153" s="1">
         <v>152</v>
@@ -3722,7 +3742,7 @@
     <row r="154" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O154">
         <f t="shared" ca="1" si="32"/>
-        <v>0.27103978973304332</v>
+        <v>0.65901473406715105</v>
       </c>
       <c r="P154" s="1">
         <v>153</v>
@@ -3731,7 +3751,7 @@
     <row r="155" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O155">
         <f t="shared" ca="1" si="32"/>
-        <v>0.12805159551643286</v>
+        <v>0.11710923897490855</v>
       </c>
       <c r="P155" s="1">
         <v>154</v>
@@ -3740,7 +3760,7 @@
     <row r="156" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O156">
         <f t="shared" ca="1" si="32"/>
-        <v>0.3367617539457517</v>
+        <v>0.78409418665093511</v>
       </c>
       <c r="P156" s="1">
         <v>155</v>
@@ -3749,7 +3769,7 @@
     <row r="157" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O157">
         <f t="shared" ca="1" si="32"/>
-        <v>0.34137921215327627</v>
+        <v>0.22717806886817848</v>
       </c>
       <c r="P157" s="1">
         <v>156</v>
@@ -3758,7 +3778,7 @@
     <row r="158" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O158">
         <f t="shared" ca="1" si="32"/>
-        <v>0.47467323627733904</v>
+        <v>0.37318065322452665</v>
       </c>
       <c r="P158" s="1">
         <v>157</v>
@@ -3767,7 +3787,7 @@
     <row r="159" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O159">
         <f t="shared" ca="1" si="32"/>
-        <v>0.28182369379748706</v>
+        <v>0.63173651668483621</v>
       </c>
       <c r="P159" s="1">
         <v>158</v>
@@ -3776,7 +3796,7 @@
     <row r="160" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O160">
         <f t="shared" ca="1" si="32"/>
-        <v>0.45503916013615964</v>
+        <v>0.70136634820263954</v>
       </c>
       <c r="P160" s="1">
         <v>159</v>
@@ -3785,7 +3805,7 @@
     <row r="161" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O161">
         <f t="shared" ca="1" si="32"/>
-        <v>0.55870686596526209</v>
+        <v>0.68384226068898579</v>
       </c>
       <c r="P161" s="1">
         <v>160</v>
@@ -3794,7 +3814,7 @@
     <row r="162" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O162">
         <f t="shared" ca="1" si="32"/>
-        <v>0.10188684598566011</v>
+        <v>0.33547050111315546</v>
       </c>
       <c r="P162" s="1">
         <v>161</v>
@@ -3803,7 +3823,7 @@
     <row r="163" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O163">
         <f t="shared" ca="1" si="32"/>
-        <v>3.3032987152778914E-2</v>
+        <v>7.5723221467644986E-2</v>
       </c>
       <c r="P163" s="1">
         <v>162</v>
@@ -3812,7 +3832,7 @@
     <row r="164" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O164">
         <f t="shared" ca="1" si="32"/>
-        <v>0.64223574466037048</v>
+        <v>0.96219244612567145</v>
       </c>
       <c r="P164" s="1">
         <v>163</v>
@@ -3821,7 +3841,7 @@
     <row r="165" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O165">
         <f t="shared" ca="1" si="32"/>
-        <v>0.79563789175618305</v>
+        <v>0.24420794448505045</v>
       </c>
       <c r="P165" s="1">
         <v>164</v>
@@ -3830,7 +3850,7 @@
     <row r="166" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O166">
         <f t="shared" ca="1" si="32"/>
-        <v>0.7019460232483179</v>
+        <v>0.41897911496815832</v>
       </c>
       <c r="P166" s="1">
         <v>165</v>
@@ -3839,7 +3859,7 @@
     <row r="167" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O167">
         <f t="shared" ca="1" si="32"/>
-        <v>0.3761163117843993</v>
+        <v>0.62292861889822304</v>
       </c>
       <c r="P167" s="1">
         <v>166</v>
@@ -3848,7 +3868,7 @@
     <row r="168" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O168">
         <f t="shared" ca="1" si="32"/>
-        <v>0.25768635707597953</v>
+        <v>0.45457631236544649</v>
       </c>
       <c r="P168" s="1">
         <v>167</v>
@@ -3857,7 +3877,7 @@
     <row r="169" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O169">
         <f t="shared" ca="1" si="32"/>
-        <v>0.7661330086216831</v>
+        <v>0.62317720230498452</v>
       </c>
       <c r="P169" s="1">
         <v>168</v>
@@ -3866,7 +3886,7 @@
     <row r="170" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O170">
         <f t="shared" ca="1" si="32"/>
-        <v>0.97702183229142292</v>
+        <v>0.15211289797988026</v>
       </c>
       <c r="P170" s="1">
         <v>169</v>
@@ -3875,7 +3895,7 @@
     <row r="171" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O171">
         <f t="shared" ca="1" si="32"/>
-        <v>0.78415476202807399</v>
+        <v>0.53725297797994886</v>
       </c>
       <c r="P171" s="1">
         <v>170</v>
@@ -3884,7 +3904,7 @@
     <row r="172" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O172">
         <f t="shared" ca="1" si="32"/>
-        <v>1.6171736832217842E-2</v>
+        <v>2.043789116537853E-2</v>
       </c>
       <c r="P172" s="1">
         <v>171</v>
@@ -3893,7 +3913,7 @@
     <row r="173" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O173">
         <f t="shared" ca="1" si="32"/>
-        <v>0.31847964016325059</v>
+        <v>0.6112790838705594</v>
       </c>
       <c r="P173" s="1">
         <v>172</v>
@@ -3902,7 +3922,7 @@
     <row r="174" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O174">
         <f t="shared" ca="1" si="32"/>
-        <v>0.7174775101682429</v>
+        <v>0.83410146612990888</v>
       </c>
       <c r="P174" s="1">
         <v>173</v>
@@ -3911,7 +3931,7 @@
     <row r="175" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O175">
         <f t="shared" ca="1" si="32"/>
-        <v>0.8001432829386339</v>
+        <v>5.8647228006990515E-3</v>
       </c>
       <c r="P175" s="1">
         <v>174</v>
@@ -3920,7 +3940,7 @@
     <row r="176" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O176">
         <f t="shared" ca="1" si="32"/>
-        <v>0.79796584850678609</v>
+        <v>0.78804923752719824</v>
       </c>
       <c r="P176" s="1">
         <v>175</v>
@@ -3929,7 +3949,7 @@
     <row r="177" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O177">
         <f t="shared" ca="1" si="32"/>
-        <v>0.2960913236981414</v>
+        <v>0.26740644882034192</v>
       </c>
       <c r="P177" s="1">
         <v>176</v>
@@ -3938,7 +3958,7 @@
     <row r="178" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O178">
         <f t="shared" ca="1" si="32"/>
-        <v>3.5953968040543072E-2</v>
+        <v>0.83707383465372964</v>
       </c>
       <c r="P178" s="1">
         <v>177</v>
@@ -3947,7 +3967,7 @@
     <row r="179" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O179">
         <f t="shared" ca="1" si="32"/>
-        <v>0.50263720772207499</v>
+        <v>0.83856072580808427</v>
       </c>
       <c r="P179" s="1">
         <v>178</v>
@@ -3956,7 +3976,7 @@
     <row r="180" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O180">
         <f t="shared" ca="1" si="32"/>
-        <v>0.71341474546639516</v>
+        <v>0.20977321400085447</v>
       </c>
       <c r="P180" s="1">
         <v>179</v>
@@ -3965,7 +3985,7 @@
     <row r="181" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O181">
         <f t="shared" ca="1" si="32"/>
-        <v>0.19651296149016217</v>
+        <v>3.1969972690118031E-2</v>
       </c>
       <c r="P181" s="1">
         <v>180</v>
@@ -3974,7 +3994,7 @@
     <row r="182" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O182">
         <f t="shared" ca="1" si="32"/>
-        <v>0.31149736363107861</v>
+        <v>8.4487516497218973E-2</v>
       </c>
       <c r="P182" s="1">
         <v>181</v>
@@ -3983,7 +4003,7 @@
     <row r="183" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O183">
         <f t="shared" ca="1" si="32"/>
-        <v>0.47820668906520902</v>
+        <v>0.56820810750476936</v>
       </c>
       <c r="P183" s="1">
         <v>182</v>
@@ -3992,7 +4012,7 @@
     <row r="184" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O184">
         <f t="shared" ca="1" si="32"/>
-        <v>7.3327150105748529E-2</v>
+        <v>9.9997976703954938E-3</v>
       </c>
       <c r="P184" s="1">
         <v>183</v>
@@ -4001,7 +4021,7 @@
     <row r="185" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O185">
         <f t="shared" ca="1" si="32"/>
-        <v>0.87296691603802679</v>
+        <v>0.90727809459489406</v>
       </c>
       <c r="P185" s="1">
         <v>184</v>
@@ -4010,7 +4030,7 @@
     <row r="186" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O186">
         <f t="shared" ca="1" si="32"/>
-        <v>0.2621433456472857</v>
+        <v>0.74834157915915245</v>
       </c>
       <c r="P186" s="1">
         <v>185</v>
@@ -4019,7 +4039,7 @@
     <row r="187" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O187">
         <f t="shared" ca="1" si="32"/>
-        <v>0.77735308386116275</v>
+        <v>0.29790608789289774</v>
       </c>
       <c r="P187" s="1">
         <v>186</v>
@@ -4028,7 +4048,7 @@
     <row r="188" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O188">
         <f t="shared" ca="1" si="32"/>
-        <v>0.66051747745878453</v>
+        <v>0.99391878774475151</v>
       </c>
       <c r="P188" s="1">
         <v>187</v>
@@ -4037,7 +4057,7 @@
     <row r="189" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O189">
         <f t="shared" ca="1" si="32"/>
-        <v>0.43373529124001664</v>
+        <v>0.54302648229043893</v>
       </c>
       <c r="P189" s="1">
         <v>188</v>
@@ -4046,7 +4066,7 @@
     <row r="190" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O190">
         <f t="shared" ca="1" si="32"/>
-        <v>0.63177542849417012</v>
+        <v>0.64272566124523534</v>
       </c>
       <c r="P190" s="1">
         <v>189</v>
@@ -4055,7 +4075,7 @@
     <row r="191" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O191">
         <f t="shared" ca="1" si="32"/>
-        <v>0.18893264106591723</v>
+        <v>0.79947156716615819</v>
       </c>
       <c r="P191" s="1">
         <v>190</v>
@@ -4064,7 +4084,7 @@
     <row r="192" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O192">
         <f t="shared" ca="1" si="32"/>
-        <v>0.89353735790788724</v>
+        <v>0.35835189157138292</v>
       </c>
       <c r="P192" s="1">
         <v>191</v>
@@ -4073,7 +4093,7 @@
     <row r="193" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O193">
         <f t="shared" ca="1" si="32"/>
-        <v>0.98463689558035639</v>
+        <v>0.53584384500145554</v>
       </c>
       <c r="P193" s="1">
         <v>192</v>
@@ -4082,7 +4102,7 @@
     <row r="194" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O194">
         <f t="shared" ca="1" si="32"/>
-        <v>0.95948380626014818</v>
+        <v>0.28928949756728006</v>
       </c>
       <c r="P194" s="1">
         <v>193</v>
@@ -4091,7 +4111,7 @@
     <row r="195" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O195">
         <f t="shared" ref="O195:O222" ca="1" si="33">RAND()</f>
-        <v>0.77912411839284157</v>
+        <v>0.93940711727172299</v>
       </c>
       <c r="P195" s="1">
         <v>194</v>
@@ -4100,7 +4120,7 @@
     <row r="196" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O196">
         <f t="shared" ca="1" si="33"/>
-        <v>0.38832036879765675</v>
+        <v>0.48204445362154047</v>
       </c>
       <c r="P196" s="1">
         <v>195</v>
@@ -4109,7 +4129,7 @@
     <row r="197" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O197">
         <f t="shared" ca="1" si="33"/>
-        <v>0.42571819928483168</v>
+        <v>0.53030932643513662</v>
       </c>
       <c r="P197" s="1">
         <v>196</v>
@@ -4118,7 +4138,7 @@
     <row r="198" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O198">
         <f t="shared" ca="1" si="33"/>
-        <v>0.95686174378299749</v>
+        <v>0.98674010512214916</v>
       </c>
       <c r="P198" s="1">
         <v>197</v>
@@ -4127,7 +4147,7 @@
     <row r="199" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O199">
         <f t="shared" ca="1" si="33"/>
-        <v>0.45895264890073639</v>
+        <v>0.42339260450519434</v>
       </c>
       <c r="P199" s="1">
         <v>198</v>
@@ -4136,7 +4156,7 @@
     <row r="200" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O200">
         <f t="shared" ca="1" si="33"/>
-        <v>0.59308103963833159</v>
+        <v>0.67163720026758378</v>
       </c>
       <c r="P200" s="1">
         <v>199</v>
@@ -4145,7 +4165,7 @@
     <row r="201" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O201">
         <f t="shared" ca="1" si="33"/>
-        <v>0.82670842151480795</v>
+        <v>0.24441153209615374</v>
       </c>
       <c r="P201" s="1">
         <v>200</v>
@@ -4154,7 +4174,7 @@
     <row r="202" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O202">
         <f t="shared" ca="1" si="33"/>
-        <v>6.4091299653489253E-2</v>
+        <v>0.65738980248946821</v>
       </c>
       <c r="P202" s="1">
         <v>201</v>
@@ -4163,7 +4183,7 @@
     <row r="203" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O203">
         <f t="shared" ca="1" si="33"/>
-        <v>0.36571889827606141</v>
+        <v>0.84835050469506468</v>
       </c>
       <c r="P203" s="1">
         <v>202</v>
@@ -4172,7 +4192,7 @@
     <row r="204" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O204">
         <f t="shared" ca="1" si="33"/>
-        <v>0.82505557275192232</v>
+        <v>6.1949787275221713E-2</v>
       </c>
       <c r="P204" s="1">
         <v>203</v>
@@ -4181,7 +4201,7 @@
     <row r="205" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O205">
         <f t="shared" ca="1" si="33"/>
-        <v>0.75692635452008805</v>
+        <v>0.51926425677058929</v>
       </c>
       <c r="P205" s="1">
         <v>204</v>
@@ -4190,7 +4210,7 @@
     <row r="206" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O206">
         <f t="shared" ca="1" si="33"/>
-        <v>0.94689057364857376</v>
+        <v>0.45740207081125361</v>
       </c>
       <c r="P206" s="1">
         <v>205</v>
@@ -4199,7 +4219,7 @@
     <row r="207" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O207">
         <f t="shared" ca="1" si="33"/>
-        <v>0.30959224948986808</v>
+        <v>0.29277343059472505</v>
       </c>
       <c r="P207" s="1">
         <v>206</v>
@@ -4208,7 +4228,7 @@
     <row r="208" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O208">
         <f t="shared" ca="1" si="33"/>
-        <v>0.94179349063362061</v>
+        <v>5.9444428281968942E-2</v>
       </c>
       <c r="P208" s="1">
         <v>207</v>
@@ -4217,7 +4237,7 @@
     <row r="209" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O209">
         <f t="shared" ca="1" si="33"/>
-        <v>0.68209082935602383</v>
+        <v>0.26822387151998994</v>
       </c>
       <c r="P209" s="1">
         <v>208</v>
@@ -4226,7 +4246,7 @@
     <row r="210" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O210">
         <f t="shared" ca="1" si="33"/>
-        <v>7.6132729284736356E-2</v>
+        <v>0.92919533711423996</v>
       </c>
       <c r="P210" s="1">
         <v>209</v>
@@ -4235,7 +4255,7 @@
     <row r="211" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O211">
         <f t="shared" ca="1" si="33"/>
-        <v>0.74084724558143977</v>
+        <v>0.56699365043089933</v>
       </c>
       <c r="P211" s="1">
         <v>210</v>
@@ -4244,7 +4264,7 @@
     <row r="212" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O212">
         <f t="shared" ca="1" si="33"/>
-        <v>0.57299621573616732</v>
+        <v>0.62225103718860098</v>
       </c>
       <c r="P212" s="1">
         <v>211</v>
@@ -4253,7 +4273,7 @@
     <row r="213" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O213">
         <f t="shared" ca="1" si="33"/>
-        <v>0.68740315363088977</v>
+        <v>0.70040619839778429</v>
       </c>
       <c r="P213" s="1">
         <v>212</v>
@@ -4262,7 +4282,7 @@
     <row r="214" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O214">
         <f t="shared" ca="1" si="33"/>
-        <v>0.8664170371431551</v>
+        <v>0.93416932205974712</v>
       </c>
       <c r="P214" s="1">
         <v>213</v>
@@ -4271,7 +4291,7 @@
     <row r="215" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O215">
         <f t="shared" ca="1" si="33"/>
-        <v>0.48427006639179182</v>
+        <v>0.29767583571706757</v>
       </c>
       <c r="P215" s="1">
         <v>214</v>
@@ -4280,7 +4300,7 @@
     <row r="216" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O216">
         <f t="shared" ca="1" si="33"/>
-        <v>0.68833667082449601</v>
+        <v>3.6456132735434355E-2</v>
       </c>
       <c r="P216" s="1">
         <v>215</v>
@@ -4289,7 +4309,7 @@
     <row r="217" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O217">
         <f t="shared" ca="1" si="33"/>
-        <v>0.76836356832610087</v>
+        <v>0.57724486547908849</v>
       </c>
       <c r="P217" s="1">
         <v>216</v>
@@ -4298,7 +4318,7 @@
     <row r="218" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O218">
         <f t="shared" ca="1" si="33"/>
-        <v>5.0347954181646504E-3</v>
+        <v>0.11366185476222712</v>
       </c>
       <c r="P218" s="1">
         <v>217</v>
@@ -4307,7 +4327,7 @@
     <row r="219" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O219">
         <f t="shared" ca="1" si="33"/>
-        <v>7.5379555305693846E-2</v>
+        <v>0.96226551434339669</v>
       </c>
       <c r="P219" s="1">
         <v>218</v>
@@ -4316,7 +4336,7 @@
     <row r="220" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O220">
         <f t="shared" ca="1" si="33"/>
-        <v>6.8045744318372514E-2</v>
+        <v>5.6711937564035586E-2</v>
       </c>
       <c r="P220" s="1">
         <v>219</v>
@@ -4325,7 +4345,7 @@
     <row r="221" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O221">
         <f t="shared" ca="1" si="33"/>
-        <v>0.47800182442490946</v>
+        <v>0.8479141676931522</v>
       </c>
       <c r="P221" s="1">
         <v>220</v>
@@ -4334,7 +4354,7 @@
     <row r="222" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O222">
         <f t="shared" ca="1" si="33"/>
-        <v>2.8105359189493195E-2</v>
+        <v>0.90983261464045517</v>
       </c>
       <c r="P222" s="1">
         <v>221</v>
@@ -4342,7 +4362,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="V1:AH17">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="notEqual">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="notEqual">
       <formula>" "</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4352,7 +4372,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AI222"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4521,7 +4541,7 @@
       </c>
       <c r="O2">
         <f ca="1">RAND()+Q2-1</f>
-        <v>0.68614555894503404</v>
+        <v>0.70661561804824635</v>
       </c>
       <c r="P2" s="1">
         <v>1</v>
@@ -4531,11 +4551,11 @@
       </c>
       <c r="S2" s="1">
         <f ca="1">SMALL($O$2:$O$98,ROW(S1))</f>
-        <v>1.5344612091891641E-2</v>
+        <v>1.8104560211276155E-3</v>
       </c>
       <c r="T2">
         <f ca="1">VLOOKUP(S2,O$2:P$222,2,0)</f>
-        <v>69</v>
+        <v>132</v>
       </c>
       <c r="W2" s="3" t="str">
         <f t="shared" ref="W2:W17" ca="1" si="2">IF(ISNUMBER(MATCH(A2,$T$2:$T$13,0)),A2," ")</f>
@@ -4645,7 +4665,7 @@
       </c>
       <c r="O3">
         <f t="shared" ref="O3:O66" ca="1" si="16">RAND()+Q3-1</f>
-        <v>0.55234948188476451</v>
+        <v>0.66613182857729303</v>
       </c>
       <c r="P3" s="1">
         <v>2</v>
@@ -4655,23 +4675,23 @@
       </c>
       <c r="S3" s="1">
         <f t="shared" ref="S3:S5" ca="1" si="17">SMALL($O$2:$O$98,ROW(S2))</f>
-        <v>1.6685212554889972E-2</v>
+        <v>9.2462136276438844E-3</v>
       </c>
       <c r="T3">
         <f t="shared" ref="T3:T13" ca="1" si="18">VLOOKUP(S3,O$2:P$222,2,0)</f>
-        <v>132</v>
+        <v>29</v>
       </c>
       <c r="W3" s="3" t="str">
         <f t="shared" ca="1" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="X3" s="3" t="str">
+      <c r="X3" s="3">
         <f t="shared" ca="1" si="3"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="Y3" s="3" t="str">
+        <v>28</v>
+      </c>
+      <c r="Y3" s="3">
         <f t="shared" ca="1" si="4"/>
-        <v xml:space="preserve"> </v>
+        <v>29</v>
       </c>
       <c r="Z3" s="3" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -4769,7 +4789,7 @@
       </c>
       <c r="O4">
         <f t="shared" ca="1" si="16"/>
-        <v>3.7547442168033962E-2</v>
+        <v>0.88900533642096713</v>
       </c>
       <c r="P4" s="1">
         <v>3</v>
@@ -4779,11 +4799,11 @@
       </c>
       <c r="S4" s="1">
         <f t="shared" ca="1" si="17"/>
-        <v>2.2512073997921433E-2</v>
+        <v>9.8450800144562756E-3</v>
       </c>
       <c r="T4">
         <f t="shared" ca="1" si="18"/>
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="W4" s="3" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4805,9 +4825,9 @@
         <f t="shared" ca="1" si="6"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="AB4" s="3">
+      <c r="AB4" s="3" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>45</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="AC4" s="4" t="str">
         <f t="shared" ca="1" si="8"/>
@@ -4817,9 +4837,9 @@
         <f t="shared" ca="1" si="9"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="AE4" s="4" t="str">
+      <c r="AE4" s="4">
         <f t="shared" ca="1" si="10"/>
-        <v xml:space="preserve"> </v>
+        <v>48</v>
       </c>
       <c r="AF4" s="4" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -4893,7 +4913,7 @@
       </c>
       <c r="O5">
         <f t="shared" ca="1" si="16"/>
-        <v>0.10406364124403855</v>
+        <v>0.19426679070990271</v>
       </c>
       <c r="P5" s="1">
         <v>4</v>
@@ -4903,11 +4923,11 @@
       </c>
       <c r="S5" s="1">
         <f t="shared" ca="1" si="17"/>
-        <v>2.8458211777828479E-2</v>
+        <v>2.65951674308047E-2</v>
       </c>
       <c r="T5">
         <f t="shared" ca="1" si="18"/>
-        <v>188</v>
+        <v>28</v>
       </c>
       <c r="W5" s="3" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4917,9 +4937,9 @@
         <f t="shared" ca="1" si="3"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="Y5" s="3" t="str">
+      <c r="Y5" s="3">
         <f t="shared" ca="1" si="4"/>
-        <v xml:space="preserve"> </v>
+        <v>55</v>
       </c>
       <c r="Z5" s="3" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5017,7 +5037,7 @@
       </c>
       <c r="O6">
         <f t="shared" ca="1" si="16"/>
-        <v>0.60074734190893886</v>
+        <v>0.90579152326301071</v>
       </c>
       <c r="P6" s="1">
         <v>5</v>
@@ -5037,9 +5057,9 @@
         <f t="shared" ca="1" si="4"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="Z6" s="3">
+      <c r="Z6" s="3" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>69</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="AA6" s="3" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -5133,7 +5153,7 @@
       </c>
       <c r="O7">
         <f t="shared" ca="1" si="16"/>
-        <v>0.59932635567409021</v>
+        <v>0.35738493734063748</v>
       </c>
       <c r="P7" s="1">
         <v>6</v>
@@ -5143,11 +5163,11 @@
       </c>
       <c r="S7" s="1">
         <f ca="1">SMALL($O$99:$O$165,ROW(S1))</f>
-        <v>1.0186602474510518</v>
+        <v>1.0282975161509644</v>
       </c>
       <c r="T7">
         <f t="shared" ca="1" si="18"/>
-        <v>91</v>
+        <v>122</v>
       </c>
       <c r="W7" s="3" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -5197,9 +5217,9 @@
         <f t="shared" ca="1" si="13"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="AI7" s="4">
+      <c r="AI7" s="4" t="str">
         <f t="shared" ca="1" si="14"/>
-        <v>91</v>
+        <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="8" spans="1:35" x14ac:dyDescent="0.25">
@@ -5257,7 +5277,7 @@
       </c>
       <c r="O8">
         <f t="shared" ca="1" si="16"/>
-        <v>0.28373028139781509</v>
+        <v>0.31019268482105611</v>
       </c>
       <c r="P8" s="1">
         <v>7</v>
@@ -5267,11 +5287,11 @@
       </c>
       <c r="S8" s="1">
         <f t="shared" ref="S8:S9" ca="1" si="19">SMALL($O$99:$O$165,ROW(S2))</f>
-        <v>1.0252720796022219</v>
+        <v>1.0337386028857027</v>
       </c>
       <c r="T8">
         <f t="shared" ca="1" si="18"/>
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="W8" s="3" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -5313,9 +5333,9 @@
         <f t="shared" ca="1" si="11"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="AG8" s="4">
+      <c r="AG8" s="4" t="str">
         <f t="shared" ca="1" si="12"/>
-        <v>102</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="AH8" s="4" t="str">
         <f t="shared" ca="1" si="13"/>
@@ -5381,7 +5401,7 @@
       </c>
       <c r="O9">
         <f t="shared" ca="1" si="16"/>
-        <v>0.22109538573925303</v>
+        <v>3.5072532324097239E-2</v>
       </c>
       <c r="P9" s="1">
         <v>8</v>
@@ -5391,11 +5411,11 @@
       </c>
       <c r="S9" s="1">
         <f t="shared" ca="1" si="19"/>
-        <v>1.0464570308680066</v>
+        <v>1.0364116818047995</v>
       </c>
       <c r="T9">
         <f t="shared" ca="1" si="18"/>
-        <v>102</v>
+        <v>48</v>
       </c>
       <c r="W9" s="3" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -5437,9 +5457,9 @@
         <f t="shared" ca="1" si="11"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="AG9" s="4" t="str">
+      <c r="AG9" s="4">
         <f t="shared" ca="1" si="12"/>
-        <v xml:space="preserve"> </v>
+        <v>115</v>
       </c>
       <c r="AH9" s="4" t="str">
         <f t="shared" ca="1" si="13"/>
@@ -5505,7 +5525,7 @@
       </c>
       <c r="O10">
         <f t="shared" ca="1" si="16"/>
-        <v>0.55711782838413892</v>
+        <v>0.67948801189331309</v>
       </c>
       <c r="P10" s="1">
         <v>9</v>
@@ -5525,13 +5545,13 @@
         <f t="shared" ca="1" si="4"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="Z10" s="4">
+      <c r="Z10" s="4" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>121</v>
-      </c>
-      <c r="AA10" s="4" t="str">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="AA10" s="4">
         <f t="shared" ca="1" si="6"/>
-        <v xml:space="preserve"> </v>
+        <v>122</v>
       </c>
       <c r="AB10" s="4" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -5545,13 +5565,13 @@
         <f t="shared" ca="1" si="9"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="AE10" s="2">
+      <c r="AE10" s="2" t="str">
         <f t="shared" ca="1" si="10"/>
-        <v>126</v>
-      </c>
-      <c r="AF10" s="2" t="str">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="AF10" s="2">
         <f t="shared" ca="1" si="11"/>
-        <v xml:space="preserve"> </v>
+        <v>127</v>
       </c>
       <c r="AG10" s="2" t="str">
         <f t="shared" ca="1" si="12"/>
@@ -5621,7 +5641,7 @@
       </c>
       <c r="O11">
         <f t="shared" ca="1" si="16"/>
-        <v>0.78321504503719797</v>
+        <v>0.66848010648665124</v>
       </c>
       <c r="P11" s="1">
         <v>10</v>
@@ -5631,11 +5651,11 @@
       </c>
       <c r="S11" s="1">
         <f ca="1">SMALL($O$166:$O$222,ROW(S1))</f>
-        <v>2.0581760406189518</v>
+        <v>2.0035863748764622</v>
       </c>
       <c r="T11">
         <f t="shared" ca="1" si="18"/>
-        <v>126</v>
+        <v>150</v>
       </c>
       <c r="W11" s="3" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -5745,7 +5765,7 @@
       </c>
       <c r="O12">
         <f t="shared" ca="1" si="16"/>
-        <v>0.13852279436935744</v>
+        <v>0.80534536879258267</v>
       </c>
       <c r="P12" s="1">
         <v>14</v>
@@ -5755,11 +5775,11 @@
       </c>
       <c r="S12" s="1">
         <f t="shared" ref="S12:S13" ca="1" si="20">SMALL($O$166:$O$222,ROW(S2))</f>
-        <v>2.0960162682311019</v>
+        <v>2.0051640064158267</v>
       </c>
       <c r="T12">
         <f t="shared" ca="1" si="18"/>
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="W12" s="3" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -5785,13 +5805,13 @@
         <f t="shared" ca="1" si="7"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="AC12" s="2" t="str">
+      <c r="AC12" s="2">
         <f t="shared" ca="1" si="8"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="AD12" s="2">
+        <v>150</v>
+      </c>
+      <c r="AD12" s="2" t="str">
         <f t="shared" ca="1" si="9"/>
-        <v>151</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="AE12" s="2" t="str">
         <f t="shared" ca="1" si="10"/>
@@ -5801,9 +5821,9 @@
         <f t="shared" ca="1" si="11"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="AG12" s="2">
+      <c r="AG12" s="2" t="str">
         <f t="shared" ca="1" si="12"/>
-        <v>154</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="AH12" s="2" t="str">
         <f t="shared" ca="1" si="13"/>
@@ -5869,7 +5889,7 @@
       </c>
       <c r="O13">
         <f t="shared" ca="1" si="16"/>
-        <v>0.87364111312796711</v>
+        <v>0.98080433451040294</v>
       </c>
       <c r="P13" s="1">
         <v>15</v>
@@ -5879,11 +5899,11 @@
       </c>
       <c r="S13" s="1">
         <f t="shared" ca="1" si="20"/>
-        <v>2.1052992335097009</v>
+        <v>2.0451219544345527</v>
       </c>
       <c r="T13">
         <f t="shared" ca="1" si="18"/>
-        <v>151</v>
+        <v>127</v>
       </c>
       <c r="W13" s="3" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -5905,9 +5925,9 @@
         <f t="shared" ca="1" si="6"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="AB13" s="2" t="str">
+      <c r="AB13" s="2">
         <f t="shared" ca="1" si="7"/>
-        <v xml:space="preserve"> </v>
+        <v>162</v>
       </c>
       <c r="AC13" s="2" t="str">
         <f t="shared" ca="1" si="8"/>
@@ -5993,7 +6013,7 @@
       </c>
       <c r="O14">
         <f t="shared" ca="1" si="16"/>
-        <v>0.50969330257167966</v>
+        <v>0.99105427683577929</v>
       </c>
       <c r="P14" s="1">
         <v>16</v>
@@ -6109,7 +6129,7 @@
       </c>
       <c r="O15">
         <f t="shared" ca="1" si="16"/>
-        <v>0.16530368587266131</v>
+        <v>0.41633572348529668</v>
       </c>
       <c r="P15" s="1">
         <v>17</v>
@@ -6137,9 +6157,9 @@
         <f t="shared" ca="1" si="6"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AB15" s="3" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>188</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="AC15" s="3" t="str">
         <f t="shared" ca="1" si="8"/>
@@ -6225,7 +6245,7 @@
       </c>
       <c r="O16">
         <f t="shared" ca="1" si="16"/>
-        <v>0.57936465332884191</v>
+        <v>0.25494546541157881</v>
       </c>
       <c r="P16" s="1">
         <v>18</v>
@@ -6341,7 +6361,7 @@
       </c>
       <c r="O17">
         <f t="shared" ca="1" si="16"/>
-        <v>0.76072411587721556</v>
+        <v>0.57488383472423177</v>
       </c>
       <c r="P17" s="1">
         <v>19</v>
@@ -6405,7 +6425,7 @@
     <row r="18" spans="1:35" x14ac:dyDescent="0.25">
       <c r="O18">
         <f t="shared" ca="1" si="16"/>
-        <v>0.53770584000489174</v>
+        <v>0.35152353120206903</v>
       </c>
       <c r="P18" s="1">
         <v>20</v>
@@ -6417,7 +6437,7 @@
     <row r="19" spans="1:35" x14ac:dyDescent="0.25">
       <c r="O19">
         <f t="shared" ca="1" si="16"/>
-        <v>0.50936842967097284</v>
+        <v>0.49553129263636175</v>
       </c>
       <c r="P19" s="1">
         <v>21</v>
@@ -6429,7 +6449,7 @@
     <row r="20" spans="1:35" x14ac:dyDescent="0.25">
       <c r="O20">
         <f t="shared" ca="1" si="16"/>
-        <v>0.34684443126509534</v>
+        <v>0.89012964952931917</v>
       </c>
       <c r="P20" s="1">
         <v>22</v>
@@ -6441,7 +6461,7 @@
     <row r="21" spans="1:35" x14ac:dyDescent="0.25">
       <c r="O21">
         <f t="shared" ca="1" si="16"/>
-        <v>0.85540683210443857</v>
+        <v>7.940302147731515E-2</v>
       </c>
       <c r="P21" s="1">
         <v>23</v>
@@ -6453,7 +6473,7 @@
     <row r="22" spans="1:35" x14ac:dyDescent="0.25">
       <c r="O22">
         <f t="shared" ca="1" si="16"/>
-        <v>0.95139227612591881</v>
+        <v>0.44071433118763226</v>
       </c>
       <c r="P22" s="1">
         <v>27</v>
@@ -6465,7 +6485,7 @@
     <row r="23" spans="1:35" x14ac:dyDescent="0.25">
       <c r="O23">
         <f t="shared" ca="1" si="16"/>
-        <v>0.41192030615271991</v>
+        <v>2.65951674308047E-2</v>
       </c>
       <c r="P23" s="1">
         <v>28</v>
@@ -6477,7 +6497,7 @@
     <row r="24" spans="1:35" x14ac:dyDescent="0.25">
       <c r="O24">
         <f t="shared" ca="1" si="16"/>
-        <v>0.51961659967577667</v>
+        <v>9.2462136276438844E-3</v>
       </c>
       <c r="P24" s="1">
         <v>29</v>
@@ -6489,7 +6509,7 @@
     <row r="25" spans="1:35" x14ac:dyDescent="0.25">
       <c r="O25">
         <f t="shared" ca="1" si="16"/>
-        <v>0.81125831956557293</v>
+        <v>0.64136126004207306</v>
       </c>
       <c r="P25" s="1">
         <v>30</v>
@@ -6501,7 +6521,7 @@
     <row r="26" spans="1:35" x14ac:dyDescent="0.25">
       <c r="O26">
         <f t="shared" ca="1" si="16"/>
-        <v>0.10587561849055627</v>
+        <v>0.35487937371985678</v>
       </c>
       <c r="P26" s="1">
         <v>31</v>
@@ -6513,7 +6533,7 @@
     <row r="27" spans="1:35" x14ac:dyDescent="0.25">
       <c r="O27">
         <f t="shared" ca="1" si="16"/>
-        <v>0.33954802091039271</v>
+        <v>0.19158553260641531</v>
       </c>
       <c r="P27" s="1">
         <v>32</v>
@@ -6525,7 +6545,7 @@
     <row r="28" spans="1:35" x14ac:dyDescent="0.25">
       <c r="O28">
         <f t="shared" ca="1" si="16"/>
-        <v>6.129035702570329E-2</v>
+        <v>0.25318950848080313</v>
       </c>
       <c r="P28" s="1">
         <v>33</v>
@@ -6537,7 +6557,7 @@
     <row r="29" spans="1:35" x14ac:dyDescent="0.25">
       <c r="O29">
         <f t="shared" ca="1" si="16"/>
-        <v>0.12855946903364046</v>
+        <v>0.566848489086347</v>
       </c>
       <c r="P29" s="1">
         <v>34</v>
@@ -6549,7 +6569,7 @@
     <row r="30" spans="1:35" x14ac:dyDescent="0.25">
       <c r="O30">
         <f t="shared" ca="1" si="16"/>
-        <v>0.25643646158107325</v>
+        <v>0.41900819200952322</v>
       </c>
       <c r="P30" s="1">
         <v>35</v>
@@ -6561,7 +6581,7 @@
     <row r="31" spans="1:35" x14ac:dyDescent="0.25">
       <c r="O31">
         <f t="shared" ca="1" si="16"/>
-        <v>0.91258838698969424</v>
+        <v>0.22392565973468193</v>
       </c>
       <c r="P31" s="1">
         <v>36</v>
@@ -6573,7 +6593,7 @@
     <row r="32" spans="1:35" x14ac:dyDescent="0.25">
       <c r="O32">
         <f t="shared" ca="1" si="16"/>
-        <v>8.2660203608272642E-2</v>
+        <v>0.67733897500504003</v>
       </c>
       <c r="P32" s="1">
         <v>40</v>
@@ -6585,7 +6605,7 @@
     <row r="33" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O33">
         <f t="shared" ca="1" si="16"/>
-        <v>0.40397699959401479</v>
+        <v>0.25578096126918437</v>
       </c>
       <c r="P33" s="1">
         <v>41</v>
@@ -6597,7 +6617,7 @@
     <row r="34" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O34">
         <f t="shared" ca="1" si="16"/>
-        <v>6.3405819548214559E-2</v>
+        <v>0.61086774940585897</v>
       </c>
       <c r="P34" s="1">
         <v>42</v>
@@ -6609,7 +6629,7 @@
     <row r="35" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O35">
         <f t="shared" ca="1" si="16"/>
-        <v>0.62080921638359543</v>
+        <v>0.60199293957647093</v>
       </c>
       <c r="P35" s="1">
         <v>43</v>
@@ -6621,7 +6641,7 @@
     <row r="36" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O36">
         <f t="shared" ca="1" si="16"/>
-        <v>0.79532425246869276</v>
+        <v>0.80273518874798433</v>
       </c>
       <c r="P36" s="1">
         <v>44</v>
@@ -6633,7 +6653,7 @@
     <row r="37" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O37">
         <f t="shared" ca="1" si="16"/>
-        <v>2.2512073997921433E-2</v>
+        <v>0.25896135543046062</v>
       </c>
       <c r="P37" s="1">
         <v>45</v>
@@ -6645,7 +6665,7 @@
     <row r="38" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O38">
         <f t="shared" ca="1" si="16"/>
-        <v>9.9758198847452961E-2</v>
+        <v>0.3080171192421024</v>
       </c>
       <c r="P38" s="1">
         <v>53</v>
@@ -6657,7 +6677,7 @@
     <row r="39" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O39">
         <f t="shared" ca="1" si="16"/>
-        <v>0.60686266950128731</v>
+        <v>3.7626490271922552E-2</v>
       </c>
       <c r="P39" s="1">
         <v>54</v>
@@ -6669,7 +6689,7 @@
     <row r="40" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O40">
         <f t="shared" ca="1" si="16"/>
-        <v>0.80193690914572735</v>
+        <v>9.8450800144562756E-3</v>
       </c>
       <c r="P40" s="1">
         <v>55</v>
@@ -6681,7 +6701,7 @@
     <row r="41" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O41">
         <f t="shared" ca="1" si="16"/>
-        <v>0.86257522771273232</v>
+        <v>8.4423758698035201E-2</v>
       </c>
       <c r="P41" s="1">
         <v>56</v>
@@ -6693,7 +6713,7 @@
     <row r="42" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O42">
         <f t="shared" ca="1" si="16"/>
-        <v>0.90168841194881599</v>
+        <v>0.38211139433740815</v>
       </c>
       <c r="P42" s="1">
         <v>57</v>
@@ -6705,7 +6725,7 @@
     <row r="43" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O43">
         <f t="shared" ca="1" si="16"/>
-        <v>0.83611235227744718</v>
+        <v>0.5276434350633028</v>
       </c>
       <c r="P43" s="1">
         <v>58</v>
@@ -6717,7 +6737,7 @@
     <row r="44" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O44">
         <f t="shared" ca="1" si="16"/>
-        <v>0.64447899951825516</v>
+        <v>0.89028373085397816</v>
       </c>
       <c r="P44" s="1">
         <v>66</v>
@@ -6729,7 +6749,7 @@
     <row r="45" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O45">
         <f t="shared" ca="1" si="16"/>
-        <v>0.99903620359082668</v>
+        <v>0.57950284345104874</v>
       </c>
       <c r="P45" s="1">
         <v>67</v>
@@ -6741,7 +6761,7 @@
     <row r="46" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O46">
         <f t="shared" ca="1" si="16"/>
-        <v>0.4060029041921287</v>
+        <v>0.52803310394443104</v>
       </c>
       <c r="P46" s="1">
         <v>68</v>
@@ -6753,7 +6773,7 @@
     <row r="47" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O47">
         <f t="shared" ca="1" si="16"/>
-        <v>1.5344612091891641E-2</v>
+        <v>0.28898544951846872</v>
       </c>
       <c r="P47" s="1">
         <v>69</v>
@@ -6765,7 +6785,7 @@
     <row r="48" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O48">
         <f t="shared" ca="1" si="16"/>
-        <v>0.35354231743302744</v>
+        <v>0.73090959491613372</v>
       </c>
       <c r="P48" s="1">
         <v>70</v>
@@ -6777,7 +6797,7 @@
     <row r="49" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O49">
         <f t="shared" ca="1" si="16"/>
-        <v>0.14102239922609749</v>
+        <v>0.87610573860335839</v>
       </c>
       <c r="P49" s="1">
         <v>71</v>
@@ -6789,7 +6809,7 @@
     <row r="50" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O50">
         <f t="shared" ca="1" si="16"/>
-        <v>0.23184740963967432</v>
+        <v>0.80492267402790341</v>
       </c>
       <c r="P50" s="1">
         <v>79</v>
@@ -6801,7 +6821,7 @@
     <row r="51" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O51">
         <f t="shared" ca="1" si="16"/>
-        <v>0.55593296990267049</v>
+        <v>0.24451907312305021</v>
       </c>
       <c r="P51" s="1">
         <v>80</v>
@@ -6813,7 +6833,7 @@
     <row r="52" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O52">
         <f t="shared" ca="1" si="16"/>
-        <v>3.7920205328907386E-2</v>
+        <v>0.35234866330813186</v>
       </c>
       <c r="P52" s="1">
         <v>81</v>
@@ -6825,7 +6845,7 @@
     <row r="53" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O53">
         <f t="shared" ca="1" si="16"/>
-        <v>0.18452764563648372</v>
+        <v>0.66281703870446584</v>
       </c>
       <c r="P53" s="1">
         <v>82</v>
@@ -6837,7 +6857,7 @@
     <row r="54" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O54">
         <f t="shared" ca="1" si="16"/>
-        <v>0.40974699180550167</v>
+        <v>0.77916915066249759</v>
       </c>
       <c r="P54" s="1">
         <v>83</v>
@@ -6849,7 +6869,7 @@
     <row r="55" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O55">
         <f t="shared" ca="1" si="16"/>
-        <v>0.84669626674797227</v>
+        <v>0.46701535927808235</v>
       </c>
       <c r="P55" s="1">
         <v>84</v>
@@ -6861,7 +6881,7 @@
     <row r="56" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O56">
         <f t="shared" ca="1" si="16"/>
-        <v>9.144342329704136E-2</v>
+        <v>0.95170743321131157</v>
       </c>
       <c r="P56" s="1">
         <v>92</v>
@@ -6873,7 +6893,7 @@
     <row r="57" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O57">
         <f t="shared" ca="1" si="16"/>
-        <v>0.18794381095618373</v>
+        <v>0.92871826631246046</v>
       </c>
       <c r="P57" s="1">
         <v>93</v>
@@ -6885,7 +6905,7 @@
     <row r="58" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O58">
         <f t="shared" ca="1" si="16"/>
-        <v>0.29870443843284011</v>
+        <v>0.44957255588532519</v>
       </c>
       <c r="P58" s="1">
         <v>94</v>
@@ -6897,7 +6917,7 @@
     <row r="59" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O59">
         <f t="shared" ca="1" si="16"/>
-        <v>0.89997898979623558</v>
+        <v>5.0810597016182957E-2</v>
       </c>
       <c r="P59" s="1">
         <v>105</v>
@@ -6909,7 +6929,7 @@
     <row r="60" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O60">
         <f t="shared" ca="1" si="16"/>
-        <v>0.35792669818749134</v>
+        <v>0.10407822390821897</v>
       </c>
       <c r="P60" s="1">
         <v>106</v>
@@ -6921,7 +6941,7 @@
     <row r="61" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O61">
         <f t="shared" ca="1" si="16"/>
-        <v>0.28253002346956979</v>
+        <v>0.69325195329346645</v>
       </c>
       <c r="P61" s="1">
         <v>107</v>
@@ -6933,7 +6953,7 @@
     <row r="62" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O62">
         <f t="shared" ca="1" si="16"/>
-        <v>0.64336896777645602</v>
+        <v>0.71308314454489397</v>
       </c>
       <c r="P62" s="1">
         <v>118</v>
@@ -6945,7 +6965,7 @@
     <row r="63" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O63">
         <f t="shared" ca="1" si="16"/>
-        <v>0.4876375854791497</v>
+        <v>0.63980282147290013</v>
       </c>
       <c r="P63" s="1">
         <v>119</v>
@@ -6957,7 +6977,7 @@
     <row r="64" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O64">
         <f t="shared" ca="1" si="16"/>
-        <v>0.22348162649037739</v>
+        <v>0.49721298764043809</v>
       </c>
       <c r="P64" s="1">
         <v>120</v>
@@ -6969,7 +6989,7 @@
     <row r="65" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O65">
         <f t="shared" ca="1" si="16"/>
-        <v>0.19159367291487683</v>
+        <v>0.59727505671690562</v>
       </c>
       <c r="P65" s="1">
         <v>131</v>
@@ -6981,7 +7001,7 @@
     <row r="66" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O66">
         <f t="shared" ca="1" si="16"/>
-        <v>1.6685212554889972E-2</v>
+        <v>1.8104560211276155E-3</v>
       </c>
       <c r="P66" s="1">
         <v>132</v>
@@ -6993,7 +7013,7 @@
     <row r="67" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O67">
         <f t="shared" ref="O67:O130" ca="1" si="21">RAND()+Q67-1</f>
-        <v>0.89379074304977557</v>
+        <v>0.84947665531298444</v>
       </c>
       <c r="P67" s="1">
         <v>133</v>
@@ -7005,7 +7025,7 @@
     <row r="68" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O68">
         <f t="shared" ca="1" si="21"/>
-        <v>0.58784028059158011</v>
+        <v>0.64407509380125161</v>
       </c>
       <c r="P68" s="1">
         <v>144</v>
@@ -7017,7 +7037,7 @@
     <row r="69" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O69">
         <f t="shared" ca="1" si="21"/>
-        <v>0.39441349288340288</v>
+        <v>4.9107292164731753E-2</v>
       </c>
       <c r="P69" s="1">
         <v>145</v>
@@ -7029,7 +7049,7 @@
     <row r="70" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O70">
         <f t="shared" ca="1" si="21"/>
-        <v>0.37206184159256761</v>
+        <v>0.55329794899101992</v>
       </c>
       <c r="P70" s="1">
         <v>146</v>
@@ -7041,7 +7061,7 @@
     <row r="71" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O71">
         <f t="shared" ca="1" si="21"/>
-        <v>0.64088724354343674</v>
+        <v>0.69070212832337763</v>
       </c>
       <c r="P71" s="1">
         <v>157</v>
@@ -7053,7 +7073,7 @@
     <row r="72" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O72">
         <f t="shared" ca="1" si="21"/>
-        <v>0.11994295911093689</v>
+        <v>0.59773455298464229</v>
       </c>
       <c r="P72" s="1">
         <v>158</v>
@@ -7065,7 +7085,7 @@
     <row r="73" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O73">
         <f t="shared" ca="1" si="21"/>
-        <v>0.86935964752256645</v>
+        <v>0.21228756527964299</v>
       </c>
       <c r="P73" s="1">
         <v>159</v>
@@ -7077,7 +7097,7 @@
     <row r="74" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O74">
         <f t="shared" ca="1" si="21"/>
-        <v>3.6942562687284797E-2</v>
+        <v>0.6078022658518778</v>
       </c>
       <c r="P74" s="1">
         <v>170</v>
@@ -7089,7 +7109,7 @@
     <row r="75" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O75">
         <f t="shared" ca="1" si="21"/>
-        <v>0.59510746283062632</v>
+        <v>0.36374682144973991</v>
       </c>
       <c r="P75" s="1">
         <v>171</v>
@@ -7101,7 +7121,7 @@
     <row r="76" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O76">
         <f t="shared" ca="1" si="21"/>
-        <v>4.3986885064886572E-2</v>
+        <v>0.94352576244291386</v>
       </c>
       <c r="P76" s="1">
         <v>172</v>
@@ -7113,7 +7133,7 @@
     <row r="77" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O77">
         <f t="shared" ca="1" si="21"/>
-        <v>0.14163695114320363</v>
+        <v>0.80291962948725892</v>
       </c>
       <c r="P77" s="1">
         <v>173</v>
@@ -7125,7 +7145,7 @@
     <row r="78" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O78">
         <f t="shared" ca="1" si="21"/>
-        <v>0.1945014256190909</v>
+        <v>0.42701699396168369</v>
       </c>
       <c r="P78" s="1">
         <v>183</v>
@@ -7137,7 +7157,7 @@
     <row r="79" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O79">
         <f t="shared" ca="1" si="21"/>
-        <v>0.89773352436288989</v>
+        <v>0.92360286597141683</v>
       </c>
       <c r="P79" s="1">
         <v>184</v>
@@ -7149,7 +7169,7 @@
     <row r="80" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O80">
         <f t="shared" ca="1" si="21"/>
-        <v>0.35372044834967764</v>
+        <v>0.73350046627032461</v>
       </c>
       <c r="P80" s="1">
         <v>185</v>
@@ -7161,7 +7181,7 @@
     <row r="81" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O81">
         <f t="shared" ca="1" si="21"/>
-        <v>0.22478765370648324</v>
+        <v>0.98692115766644739</v>
       </c>
       <c r="P81" s="1">
         <v>186</v>
@@ -7173,7 +7193,7 @@
     <row r="82" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O82">
         <f t="shared" ca="1" si="21"/>
-        <v>6.7990295458498995E-2</v>
+        <v>0.88822633439651355</v>
       </c>
       <c r="P82" s="1">
         <v>187</v>
@@ -7185,7 +7205,7 @@
     <row r="83" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O83">
         <f t="shared" ca="1" si="21"/>
-        <v>2.8458211777828479E-2</v>
+        <v>0.69461857625521972</v>
       </c>
       <c r="P83" s="1">
         <v>188</v>
@@ -7197,7 +7217,7 @@
     <row r="84" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O84">
         <f t="shared" ca="1" si="21"/>
-        <v>0.42271759243572982</v>
+        <v>0.75301507474924723</v>
       </c>
       <c r="P84" s="1">
         <v>189</v>
@@ -7209,7 +7229,7 @@
     <row r="85" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O85">
         <f t="shared" ca="1" si="21"/>
-        <v>0.77695395240278442</v>
+        <v>0.43640896114493755</v>
       </c>
       <c r="P85" s="1">
         <v>196</v>
@@ -7221,7 +7241,7 @@
     <row r="86" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O86">
         <f t="shared" ca="1" si="21"/>
-        <v>0.20038141752320637</v>
+        <v>0.18642515046723007</v>
       </c>
       <c r="P86" s="1">
         <v>197</v>
@@ -7233,7 +7253,7 @@
     <row r="87" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O87">
         <f t="shared" ca="1" si="21"/>
-        <v>0.77604051234472982</v>
+        <v>0.1565098515049228</v>
       </c>
       <c r="P87" s="1">
         <v>198</v>
@@ -7245,7 +7265,7 @@
     <row r="88" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O88">
         <f t="shared" ca="1" si="21"/>
-        <v>0.31503793304031902</v>
+        <v>0.67945331156915012</v>
       </c>
       <c r="P88" s="1">
         <v>199</v>
@@ -7257,7 +7277,7 @@
     <row r="89" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O89">
         <f t="shared" ca="1" si="21"/>
-        <v>0.85525966216671723</v>
+        <v>0.27239964939965278</v>
       </c>
       <c r="P89" s="1">
         <v>200</v>
@@ -7269,7 +7289,7 @@
     <row r="90" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O90">
         <f t="shared" ca="1" si="21"/>
-        <v>0.54603995947524764</v>
+        <v>0.70104231037932752</v>
       </c>
       <c r="P90" s="1">
         <v>201</v>
@@ -7281,7 +7301,7 @@
     <row r="91" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O91">
         <f t="shared" ca="1" si="21"/>
-        <v>0.28703873860485896</v>
+        <v>0.80265544059482918</v>
       </c>
       <c r="P91" s="1">
         <v>202</v>
@@ -7293,7 +7313,7 @@
     <row r="92" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O92">
         <f t="shared" ca="1" si="21"/>
-        <v>0.58330165702403436</v>
+        <v>0.14542478167282269</v>
       </c>
       <c r="P92" s="1">
         <v>209</v>
@@ -7305,7 +7325,7 @@
     <row r="93" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O93">
         <f t="shared" ca="1" si="21"/>
-        <v>0.7016139846394176</v>
+        <v>0.95422235850352255</v>
       </c>
       <c r="P93" s="1">
         <v>210</v>
@@ -7317,7 +7337,7 @@
     <row r="94" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O94">
         <f t="shared" ca="1" si="21"/>
-        <v>0.14136062967043106</v>
+        <v>0.31502148588586287</v>
       </c>
       <c r="P94" s="1">
         <v>211</v>
@@ -7329,7 +7349,7 @@
     <row r="95" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O95">
         <f t="shared" ca="1" si="21"/>
-        <v>0.42613965167772982</v>
+        <v>0.24527061838256792</v>
       </c>
       <c r="P95" s="1">
         <v>212</v>
@@ -7341,7 +7361,7 @@
     <row r="96" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O96">
         <f t="shared" ca="1" si="21"/>
-        <v>0.63432771315845482</v>
+        <v>0.35225017668555214</v>
       </c>
       <c r="P96" s="1">
         <v>213</v>
@@ -7353,7 +7373,7 @@
     <row r="97" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O97">
         <f t="shared" ca="1" si="21"/>
-        <v>0.37115642884514788</v>
+        <v>0.2979597341318867</v>
       </c>
       <c r="P97" s="1">
         <v>214</v>
@@ -7365,7 +7385,7 @@
     <row r="98" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O98">
         <f t="shared" ca="1" si="21"/>
-        <v>0.52982358844523381</v>
+        <v>0.54847389707238969</v>
       </c>
       <c r="P98" s="1">
         <v>215</v>
@@ -7377,7 +7397,7 @@
     <row r="99" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O99">
         <f t="shared" ca="1" si="21"/>
-        <v>1.2264563124566852</v>
+        <v>1.2585297617521407</v>
       </c>
       <c r="P99" s="1">
         <v>11</v>
@@ -7389,7 +7409,7 @@
     <row r="100" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O100">
         <f t="shared" ca="1" si="21"/>
-        <v>1.8697778924081021</v>
+        <v>1.6363983916083455</v>
       </c>
       <c r="P100" s="1">
         <v>12</v>
@@ -7401,7 +7421,7 @@
     <row r="101" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O101">
         <f t="shared" ca="1" si="21"/>
-        <v>1.7052090994565683</v>
+        <v>1.1812661961459936</v>
       </c>
       <c r="P101" s="1">
         <v>13</v>
@@ -7413,7 +7433,7 @@
     <row r="102" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O102">
         <f t="shared" ca="1" si="21"/>
-        <v>1.2306110759250286</v>
+        <v>1.3910786005248337</v>
       </c>
       <c r="P102" s="1">
         <v>24</v>
@@ -7425,7 +7445,7 @@
     <row r="103" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O103">
         <f t="shared" ca="1" si="21"/>
-        <v>1.1209014924247449</v>
+        <v>1.2077592177944787</v>
       </c>
       <c r="P103" s="1">
         <v>25</v>
@@ -7437,7 +7457,7 @@
     <row r="104" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O104">
         <f t="shared" ca="1" si="21"/>
-        <v>1.8929344666433372</v>
+        <v>1.2068238342177939</v>
       </c>
       <c r="P104" s="1">
         <v>26</v>
@@ -7449,7 +7469,7 @@
     <row r="105" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O105">
         <f t="shared" ca="1" si="21"/>
-        <v>1.7953160845762839</v>
+        <v>1.6384633430345192</v>
       </c>
       <c r="P105" s="1">
         <v>37</v>
@@ -7461,7 +7481,7 @@
     <row r="106" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O106">
         <f t="shared" ca="1" si="21"/>
-        <v>1.6100083830227918</v>
+        <v>1.7190110131832954</v>
       </c>
       <c r="P106" s="1">
         <v>38</v>
@@ -7473,7 +7493,7 @@
     <row r="107" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O107">
         <f t="shared" ca="1" si="21"/>
-        <v>1.4715621483950372</v>
+        <v>1.3731805236336037</v>
       </c>
       <c r="P107" s="1">
         <v>39</v>
@@ -7485,7 +7505,7 @@
     <row r="108" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O108">
         <f t="shared" ca="1" si="21"/>
-        <v>1.5860900299663072</v>
+        <v>1.8608398024382726</v>
       </c>
       <c r="P108" s="1">
         <v>46</v>
@@ -7497,7 +7517,7 @@
     <row r="109" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O109">
         <f t="shared" ca="1" si="21"/>
-        <v>1.9639488320653236</v>
+        <v>1.3155673087004951</v>
       </c>
       <c r="P109" s="1">
         <v>47</v>
@@ -7509,7 +7529,7 @@
     <row r="110" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O110">
         <f t="shared" ca="1" si="21"/>
-        <v>1.1128629016922851</v>
+        <v>1.0364116818047995</v>
       </c>
       <c r="P110" s="1">
         <v>48</v>
@@ -7521,7 +7541,7 @@
     <row r="111" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O111">
         <f t="shared" ca="1" si="21"/>
-        <v>1.2567256766867105</v>
+        <v>1.7180657292667565</v>
       </c>
       <c r="P111" s="1">
         <v>49</v>
@@ -7533,7 +7553,7 @@
     <row r="112" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O112">
         <f t="shared" ca="1" si="21"/>
-        <v>1.1028356587844672</v>
+        <v>1.9509645473745736</v>
       </c>
       <c r="P112" s="1">
         <v>50</v>
@@ -7545,7 +7565,7 @@
     <row r="113" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O113">
         <f t="shared" ca="1" si="21"/>
-        <v>1.3373864659474659</v>
+        <v>1.7159799320421758</v>
       </c>
       <c r="P113" s="1">
         <v>51</v>
@@ -7557,7 +7577,7 @@
     <row r="114" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O114">
         <f t="shared" ca="1" si="21"/>
-        <v>1.0951458790959467</v>
+        <v>1.8809216667669544</v>
       </c>
       <c r="P114" s="1">
         <v>52</v>
@@ -7569,7 +7589,7 @@
     <row r="115" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O115">
         <f t="shared" ca="1" si="21"/>
-        <v>1.3541595646435258</v>
+        <v>1.0915648492672125</v>
       </c>
       <c r="P115" s="1">
         <v>59</v>
@@ -7581,7 +7601,7 @@
     <row r="116" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O116">
         <f t="shared" ca="1" si="21"/>
-        <v>1.1070786608925807</v>
+        <v>1.5282050835086989</v>
       </c>
       <c r="P116" s="1">
         <v>60</v>
@@ -7593,7 +7613,7 @@
     <row r="117" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O117">
         <f t="shared" ca="1" si="21"/>
-        <v>1.6129219257167389</v>
+        <v>1.1424864700765518</v>
       </c>
       <c r="P117" s="1">
         <v>61</v>
@@ -7605,7 +7625,7 @@
     <row r="118" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O118">
         <f t="shared" ca="1" si="21"/>
-        <v>1.2104865887175813</v>
+        <v>1.5572924803033561</v>
       </c>
       <c r="P118" s="1">
         <v>62</v>
@@ -7617,7 +7637,7 @@
     <row r="119" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O119">
         <f t="shared" ca="1" si="21"/>
-        <v>1.9548188422381072</v>
+        <v>1.3314108293703888</v>
       </c>
       <c r="P119" s="1">
         <v>63</v>
@@ -7629,7 +7649,7 @@
     <row r="120" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O120">
         <f t="shared" ca="1" si="21"/>
-        <v>1.4483945723351321</v>
+        <v>1.4821240292389852</v>
       </c>
       <c r="P120" s="1">
         <v>64</v>
@@ -7641,7 +7661,7 @@
     <row r="121" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O121">
         <f t="shared" ca="1" si="21"/>
-        <v>1.4251212645815752</v>
+        <v>1.8246372488912042</v>
       </c>
       <c r="P121" s="1">
         <v>65</v>
@@ -7653,7 +7673,7 @@
     <row r="122" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O122">
         <f t="shared" ca="1" si="21"/>
-        <v>1.3582119512045345</v>
+        <v>1.4818406953963015</v>
       </c>
       <c r="P122" s="1">
         <v>72</v>
@@ -7665,7 +7685,7 @@
     <row r="123" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O123">
         <f t="shared" ca="1" si="21"/>
-        <v>1.1606667953748948</v>
+        <v>1.8176242648010961</v>
       </c>
       <c r="P123" s="1">
         <v>73</v>
@@ -7677,7 +7697,7 @@
     <row r="124" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O124">
         <f t="shared" ca="1" si="21"/>
-        <v>1.4675591695030228</v>
+        <v>1.2140899859246446</v>
       </c>
       <c r="P124" s="1">
         <v>74</v>
@@ -7689,7 +7709,7 @@
     <row r="125" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O125">
         <f t="shared" ca="1" si="21"/>
-        <v>1.9977066461388686</v>
+        <v>1.5309802672590975</v>
       </c>
       <c r="P125" s="1">
         <v>75</v>
@@ -7701,7 +7721,7 @@
     <row r="126" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O126">
         <f t="shared" ca="1" si="21"/>
-        <v>1.7648990415959291</v>
+        <v>1.8037149238307864</v>
       </c>
       <c r="P126" s="1">
         <v>76</v>
@@ -7713,7 +7733,7 @@
     <row r="127" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O127">
         <f t="shared" ca="1" si="21"/>
-        <v>1.2730320706917073</v>
+        <v>1.790318452959049</v>
       </c>
       <c r="P127" s="1">
         <v>77</v>
@@ -7725,7 +7745,7 @@
     <row r="128" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O128">
         <f t="shared" ca="1" si="21"/>
-        <v>1.8167629157209477</v>
+        <v>1.3963170625976833</v>
       </c>
       <c r="P128" s="1">
         <v>78</v>
@@ -7737,7 +7757,7 @@
     <row r="129" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O129">
         <f t="shared" ca="1" si="21"/>
-        <v>1.8408106184576836</v>
+        <v>1.3427501354840645</v>
       </c>
       <c r="P129" s="1">
         <v>85</v>
@@ -7749,7 +7769,7 @@
     <row r="130" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O130">
         <f t="shared" ca="1" si="21"/>
-        <v>1.1262115092376579</v>
+        <v>1.6448935666569864</v>
       </c>
       <c r="P130" s="1">
         <v>86</v>
@@ -7761,7 +7781,7 @@
     <row r="131" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O131">
         <f t="shared" ref="O131:O194" ca="1" si="22">RAND()+Q131-1</f>
-        <v>1.692419483012932</v>
+        <v>1.1897816813050004</v>
       </c>
       <c r="P131" s="1">
         <v>87</v>
@@ -7773,7 +7793,7 @@
     <row r="132" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O132">
         <f t="shared" ca="1" si="22"/>
-        <v>1.6357137286561532</v>
+        <v>1.0758465046529055</v>
       </c>
       <c r="P132" s="1">
         <v>88</v>
@@ -7785,7 +7805,7 @@
     <row r="133" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O133">
         <f t="shared" ca="1" si="22"/>
-        <v>1.9559123335824475</v>
+        <v>1.4588280294557574</v>
       </c>
       <c r="P133" s="1">
         <v>89</v>
@@ -7797,7 +7817,7 @@
     <row r="134" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O134">
         <f t="shared" ca="1" si="22"/>
-        <v>1.2647877386932462</v>
+        <v>1.0528382741772</v>
       </c>
       <c r="P134" s="1">
         <v>90</v>
@@ -7809,7 +7829,7 @@
     <row r="135" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O135">
         <f t="shared" ca="1" si="22"/>
-        <v>1.0186602474510518</v>
+        <v>1.4396840842748393</v>
       </c>
       <c r="P135" s="1">
         <v>91</v>
@@ -7821,7 +7841,7 @@
     <row r="136" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O136">
         <f t="shared" ca="1" si="22"/>
-        <v>1.7425796981118968</v>
+        <v>1.8685548660244633</v>
       </c>
       <c r="P136" s="1">
         <v>95</v>
@@ -7833,7 +7853,7 @@
     <row r="137" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O137">
         <f t="shared" ca="1" si="22"/>
-        <v>1.5064065937365725</v>
+        <v>1.6727284267035523</v>
       </c>
       <c r="P137" s="1">
         <v>96</v>
@@ -7845,7 +7865,7 @@
     <row r="138" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O138">
         <f t="shared" ca="1" si="22"/>
-        <v>1.8886867705368937</v>
+        <v>1.9090171102642071</v>
       </c>
       <c r="P138" s="1">
         <v>97</v>
@@ -7857,7 +7877,7 @@
     <row r="139" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O139">
         <f t="shared" ca="1" si="22"/>
-        <v>1.9082020123309138</v>
+        <v>1.7815679531806126</v>
       </c>
       <c r="P139" s="1">
         <v>98</v>
@@ -7869,7 +7889,7 @@
     <row r="140" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O140">
         <f t="shared" ca="1" si="22"/>
-        <v>1.8748786125071391</v>
+        <v>1.1062891131235673</v>
       </c>
       <c r="P140" s="1">
         <v>99</v>
@@ -7881,7 +7901,7 @@
     <row r="141" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O141">
         <f t="shared" ca="1" si="22"/>
-        <v>1.5767480272023948</v>
+        <v>1.160159861405528</v>
       </c>
       <c r="P141" s="1">
         <v>100</v>
@@ -7893,7 +7913,7 @@
     <row r="142" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O142">
         <f t="shared" ca="1" si="22"/>
-        <v>1.2488507390426395</v>
+        <v>1.1832418227163739</v>
       </c>
       <c r="P142" s="1">
         <v>101</v>
@@ -7905,7 +7925,7 @@
     <row r="143" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O143">
         <f t="shared" ca="1" si="22"/>
-        <v>1.0464570308680066</v>
+        <v>1.2874368359733479</v>
       </c>
       <c r="P143" s="1">
         <v>102</v>
@@ -7917,7 +7937,7 @@
     <row r="144" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O144">
         <f t="shared" ca="1" si="22"/>
-        <v>1.7979278592583254</v>
+        <v>1.4377800819938606</v>
       </c>
       <c r="P144" s="1">
         <v>103</v>
@@ -7929,7 +7949,7 @@
     <row r="145" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O145">
         <f t="shared" ca="1" si="22"/>
-        <v>1.1557691192491815</v>
+        <v>1.4335483237838909</v>
       </c>
       <c r="P145" s="1">
         <v>104</v>
@@ -7941,7 +7961,7 @@
     <row r="146" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O146">
         <f t="shared" ca="1" si="22"/>
-        <v>1.4843138579357733</v>
+        <v>1.7538105238574682</v>
       </c>
       <c r="P146" s="1">
         <v>108</v>
@@ -7953,7 +7973,7 @@
     <row r="147" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O147">
         <f t="shared" ca="1" si="22"/>
-        <v>1.9290909106924126</v>
+        <v>1.6171071242309241</v>
       </c>
       <c r="P147" s="1">
         <v>109</v>
@@ -7965,7 +7985,7 @@
     <row r="148" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O148">
         <f t="shared" ca="1" si="22"/>
-        <v>1.2793903721012123</v>
+        <v>1.0461073443884419</v>
       </c>
       <c r="P148" s="1">
         <v>110</v>
@@ -7977,7 +7997,7 @@
     <row r="149" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O149">
         <f t="shared" ca="1" si="22"/>
-        <v>1.8709817252398904</v>
+        <v>1.9483988670150691</v>
       </c>
       <c r="P149" s="1">
         <v>111</v>
@@ -7989,7 +8009,7 @@
     <row r="150" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O150">
         <f t="shared" ca="1" si="22"/>
-        <v>1.3469833523722863</v>
+        <v>1.0493398153445495</v>
       </c>
       <c r="P150" s="1">
         <v>112</v>
@@ -8001,7 +8021,7 @@
     <row r="151" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O151">
         <f t="shared" ca="1" si="22"/>
-        <v>1.0526631986712394</v>
+        <v>1.1760113813311679</v>
       </c>
       <c r="P151" s="1">
         <v>113</v>
@@ -8013,7 +8033,7 @@
     <row r="152" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O152">
         <f t="shared" ca="1" si="22"/>
-        <v>1.2240824029662321</v>
+        <v>1.908493416413017</v>
       </c>
       <c r="P152" s="1">
         <v>114</v>
@@ -8025,7 +8045,7 @@
     <row r="153" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O153">
         <f t="shared" ca="1" si="22"/>
-        <v>1.6057510312672569</v>
+        <v>1.0337386028857027</v>
       </c>
       <c r="P153" s="1">
         <v>115</v>
@@ -8037,7 +8057,7 @@
     <row r="154" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O154">
         <f t="shared" ca="1" si="22"/>
-        <v>1.1096668262776137</v>
+        <v>1.9732811488212318</v>
       </c>
       <c r="P154" s="1">
         <v>116</v>
@@ -8049,7 +8069,7 @@
     <row r="155" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O155">
         <f t="shared" ca="1" si="22"/>
-        <v>1.9274051784706123</v>
+        <v>1.7769085476308795</v>
       </c>
       <c r="P155" s="1">
         <v>117</v>
@@ -8061,7 +8081,7 @@
     <row r="156" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O156">
         <f t="shared" ca="1" si="22"/>
-        <v>1.0252720796022219</v>
+        <v>1.5683651710770388</v>
       </c>
       <c r="P156" s="1">
         <v>121</v>
@@ -8073,7 +8093,7 @@
     <row r="157" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O157">
         <f t="shared" ca="1" si="22"/>
-        <v>1.3690257570701911</v>
+        <v>1.0282975161509644</v>
       </c>
       <c r="P157" s="1">
         <v>122</v>
@@ -8085,7 +8105,7 @@
     <row r="158" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O158">
         <f t="shared" ca="1" si="22"/>
-        <v>1.2017144071798578</v>
+        <v>1.688364997666655</v>
       </c>
       <c r="P158" s="1">
         <v>123</v>
@@ -8097,7 +8117,7 @@
     <row r="159" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O159">
         <f t="shared" ca="1" si="22"/>
-        <v>1.2818165076408752</v>
+        <v>1.2080017843691748</v>
       </c>
       <c r="P159" s="1">
         <v>124</v>
@@ -8109,7 +8129,7 @@
     <row r="160" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O160">
         <f t="shared" ca="1" si="22"/>
-        <v>1.546261454326844</v>
+        <v>1.6425331745764264</v>
       </c>
       <c r="P160" s="1">
         <v>134</v>
@@ -8121,7 +8141,7 @@
     <row r="161" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O161">
         <f t="shared" ca="1" si="22"/>
-        <v>1.7910191422865598</v>
+        <v>1.8713126635952637</v>
       </c>
       <c r="P161" s="1">
         <v>135</v>
@@ -8133,7 +8153,7 @@
     <row r="162" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O162">
         <f t="shared" ca="1" si="22"/>
-        <v>1.9391486286869566</v>
+        <v>1.9207436647612721</v>
       </c>
       <c r="P162" s="1">
         <v>136</v>
@@ -8145,7 +8165,7 @@
     <row r="163" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O163">
         <f t="shared" ca="1" si="22"/>
-        <v>1.8647223378998445</v>
+        <v>1.426463804652113</v>
       </c>
       <c r="P163" s="1">
         <v>137</v>
@@ -8157,7 +8177,7 @@
     <row r="164" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O164">
         <f t="shared" ca="1" si="22"/>
-        <v>1.1755458952180735</v>
+        <v>1.0559011448667852</v>
       </c>
       <c r="P164" s="1">
         <v>147</v>
@@ -8169,7 +8189,7 @@
     <row r="165" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O165">
         <f t="shared" ca="1" si="22"/>
-        <v>1.2676974073430998</v>
+        <v>1.3912194474467752</v>
       </c>
       <c r="P165" s="1">
         <v>160</v>
@@ -8181,7 +8201,7 @@
     <row r="166" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O166">
         <f t="shared" ca="1" si="22"/>
-        <v>2.6781093825920865</v>
+        <v>2.4074659942086143</v>
       </c>
       <c r="P166" s="1">
         <v>125</v>
@@ -8193,7 +8213,7 @@
     <row r="167" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O167">
         <f t="shared" ca="1" si="22"/>
-        <v>2.0581760406189518</v>
+        <v>2.2609931943446018</v>
       </c>
       <c r="P167" s="1">
         <v>126</v>
@@ -8205,7 +8225,7 @@
     <row r="168" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O168">
         <f t="shared" ca="1" si="22"/>
-        <v>2.8357504385127821</v>
+        <v>2.0451219544345527</v>
       </c>
       <c r="P168" s="1">
         <v>127</v>
@@ -8217,7 +8237,7 @@
     <row r="169" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O169">
         <f t="shared" ca="1" si="22"/>
-        <v>2.9295410924946581</v>
+        <v>2.920409239780271</v>
       </c>
       <c r="P169" s="1">
         <v>128</v>
@@ -8229,7 +8249,7 @@
     <row r="170" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O170">
         <f t="shared" ca="1" si="22"/>
-        <v>2.8763111137093991</v>
+        <v>2.5804636789270066</v>
       </c>
       <c r="P170" s="1">
         <v>129</v>
@@ -8241,7 +8261,7 @@
     <row r="171" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O171">
         <f t="shared" ca="1" si="22"/>
-        <v>2.5356229484222661</v>
+        <v>2.7206069086465581</v>
       </c>
       <c r="P171" s="1">
         <v>130</v>
@@ -8253,7 +8273,7 @@
     <row r="172" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O172">
         <f t="shared" ca="1" si="22"/>
-        <v>2.607787107267499</v>
+        <v>2.2976429030775858</v>
       </c>
       <c r="P172" s="1">
         <v>138</v>
@@ -8265,7 +8285,7 @@
     <row r="173" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O173">
         <f t="shared" ca="1" si="22"/>
-        <v>2.3730608657995753</v>
+        <v>2.0513317477575139</v>
       </c>
       <c r="P173" s="1">
         <v>139</v>
@@ -8277,7 +8297,7 @@
     <row r="174" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O174">
         <f t="shared" ca="1" si="22"/>
-        <v>2.9460962727878548</v>
+        <v>2.3716948860138327</v>
       </c>
       <c r="P174" s="1">
         <v>140</v>
@@ -8289,7 +8309,7 @@
     <row r="175" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O175">
         <f t="shared" ca="1" si="22"/>
-        <v>2.1099755324546337</v>
+        <v>2.154310377636953</v>
       </c>
       <c r="P175" s="1">
         <v>141</v>
@@ -8301,7 +8321,7 @@
     <row r="176" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O176">
         <f t="shared" ca="1" si="22"/>
-        <v>2.6010480042632151</v>
+        <v>2.2798447201759897</v>
       </c>
       <c r="P176" s="1">
         <v>142</v>
@@ -8313,7 +8333,7 @@
     <row r="177" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O177">
         <f t="shared" ca="1" si="22"/>
-        <v>2.2046560491525371</v>
+        <v>2.59249056135334</v>
       </c>
       <c r="P177" s="1">
         <v>143</v>
@@ -8325,7 +8345,7 @@
     <row r="178" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O178">
         <f t="shared" ca="1" si="22"/>
-        <v>2.8110023652895055</v>
+        <v>2.4219336762809256</v>
       </c>
       <c r="P178" s="1">
         <v>148</v>
@@ -8337,7 +8357,7 @@
     <row r="179" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O179">
         <f t="shared" ca="1" si="22"/>
-        <v>2.1703094610849503</v>
+        <v>2.2432041153425679</v>
       </c>
       <c r="P179" s="1">
         <v>149</v>
@@ -8349,7 +8369,7 @@
     <row r="180" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O180">
         <f t="shared" ca="1" si="22"/>
-        <v>2.3776880514621848</v>
+        <v>2.0035863748764622</v>
       </c>
       <c r="P180" s="1">
         <v>150</v>
@@ -8361,7 +8381,7 @@
     <row r="181" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O181">
         <f t="shared" ca="1" si="22"/>
-        <v>2.1052992335097009</v>
+        <v>2.2951147206237805</v>
       </c>
       <c r="P181" s="1">
         <v>151</v>
@@ -8373,7 +8393,7 @@
     <row r="182" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O182">
         <f t="shared" ca="1" si="22"/>
-        <v>2.1414549808871808</v>
+        <v>2.4240468289836934</v>
       </c>
       <c r="P182" s="1">
         <v>152</v>
@@ -8385,7 +8405,7 @@
     <row r="183" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O183">
         <f t="shared" ca="1" si="22"/>
-        <v>2.3242570641645361</v>
+        <v>2.9535892771474339</v>
       </c>
       <c r="P183" s="1">
         <v>153</v>
@@ -8397,7 +8417,7 @@
     <row r="184" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O184">
         <f t="shared" ca="1" si="22"/>
-        <v>2.0960162682311019</v>
+        <v>2.4557711525468302</v>
       </c>
       <c r="P184" s="1">
         <v>154</v>
@@ -8409,7 +8429,7 @@
     <row r="185" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O185">
         <f t="shared" ca="1" si="22"/>
-        <v>2.2969527004180494</v>
+        <v>2.2187880304122647</v>
       </c>
       <c r="P185" s="1">
         <v>155</v>
@@ -8421,7 +8441,7 @@
     <row r="186" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O186">
         <f t="shared" ca="1" si="22"/>
-        <v>2.7410115535018864</v>
+        <v>2.6071711637420161</v>
       </c>
       <c r="P186" s="1">
         <v>156</v>
@@ -8433,7 +8453,7 @@
     <row r="187" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O187">
         <f t="shared" ca="1" si="22"/>
-        <v>2.3526520868407186</v>
+        <v>2.918795360878562</v>
       </c>
       <c r="P187" s="1">
         <v>161</v>
@@ -8445,7 +8465,7 @@
     <row r="188" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O188">
         <f t="shared" ca="1" si="22"/>
-        <v>2.1265541847284384</v>
+        <v>2.0051640064158267</v>
       </c>
       <c r="P188" s="1">
         <v>162</v>
@@ -8457,7 +8477,7 @@
     <row r="189" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O189">
         <f t="shared" ca="1" si="22"/>
-        <v>2.2983101741056586</v>
+        <v>2.7284151418549198</v>
       </c>
       <c r="P189" s="1">
         <v>163</v>
@@ -8469,7 +8489,7 @@
     <row r="190" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O190">
         <f t="shared" ca="1" si="22"/>
-        <v>2.418537228207402</v>
+        <v>2.2471350941225352</v>
       </c>
       <c r="P190" s="1">
         <v>164</v>
@@ -8481,7 +8501,7 @@
     <row r="191" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O191">
         <f t="shared" ca="1" si="22"/>
-        <v>2.216766472627214</v>
+        <v>2.5237400587844681</v>
       </c>
       <c r="P191" s="1">
         <v>165</v>
@@ -8493,7 +8513,7 @@
     <row r="192" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O192">
         <f t="shared" ca="1" si="22"/>
-        <v>2.6003772769955233</v>
+        <v>2.280873054801873</v>
       </c>
       <c r="P192" s="1">
         <v>166</v>
@@ -8505,7 +8525,7 @@
     <row r="193" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O193">
         <f t="shared" ca="1" si="22"/>
-        <v>2.7465180635470738</v>
+        <v>2.618665176201481</v>
       </c>
       <c r="P193" s="1">
         <v>167</v>
@@ -8517,7 +8537,7 @@
     <row r="194" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O194">
         <f t="shared" ca="1" si="22"/>
-        <v>2.8168021823971277</v>
+        <v>2.5553603395948414</v>
       </c>
       <c r="P194" s="1">
         <v>168</v>
@@ -8529,7 +8549,7 @@
     <row r="195" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O195">
         <f t="shared" ref="O195:O222" ca="1" si="23">RAND()+Q195-1</f>
-        <v>2.5104849011894022</v>
+        <v>2.3097852014917875</v>
       </c>
       <c r="P195" s="1">
         <v>169</v>
@@ -8541,7 +8561,7 @@
     <row r="196" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O196">
         <f t="shared" ca="1" si="23"/>
-        <v>2.9717246257819823</v>
+        <v>2.5489449771962551</v>
       </c>
       <c r="P196" s="1">
         <v>174</v>
@@ -8553,7 +8573,7 @@
     <row r="197" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O197">
         <f t="shared" ca="1" si="23"/>
-        <v>2.9683072192580315</v>
+        <v>2.1483745327361938</v>
       </c>
       <c r="P197" s="1">
         <v>175</v>
@@ -8565,7 +8585,7 @@
     <row r="198" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O198">
         <f t="shared" ca="1" si="23"/>
-        <v>2.4944042367077661</v>
+        <v>2.2985162155148013</v>
       </c>
       <c r="P198" s="1">
         <v>176</v>
@@ -8577,7 +8597,7 @@
     <row r="199" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O199">
         <f t="shared" ca="1" si="23"/>
-        <v>2.6171207658293034</v>
+        <v>2.6817322971690478</v>
       </c>
       <c r="P199" s="1">
         <v>177</v>
@@ -8589,7 +8609,7 @@
     <row r="200" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O200">
         <f t="shared" ca="1" si="23"/>
-        <v>2.2120275442016162</v>
+        <v>2.5968313429970582</v>
       </c>
       <c r="P200" s="1">
         <v>178</v>
@@ -8601,7 +8621,7 @@
     <row r="201" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O201">
         <f t="shared" ca="1" si="23"/>
-        <v>2.4039666986609745</v>
+        <v>2.4236829171693546</v>
       </c>
       <c r="P201" s="1">
         <v>179</v>
@@ -8613,7 +8633,7 @@
     <row r="202" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O202">
         <f t="shared" ca="1" si="23"/>
-        <v>2.5705073324065344</v>
+        <v>2.9008393659041851</v>
       </c>
       <c r="P202" s="1">
         <v>180</v>
@@ -8625,7 +8645,7 @@
     <row r="203" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O203">
         <f t="shared" ca="1" si="23"/>
-        <v>2.443916764163875</v>
+        <v>2.6275655462014154</v>
       </c>
       <c r="P203" s="1">
         <v>181</v>
@@ -8637,7 +8657,7 @@
     <row r="204" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O204">
         <f t="shared" ca="1" si="23"/>
-        <v>2.9672048099377335</v>
+        <v>2.0889356528317715</v>
       </c>
       <c r="P204" s="1">
         <v>182</v>
@@ -8649,7 +8669,7 @@
     <row r="205" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O205">
         <f t="shared" ca="1" si="23"/>
-        <v>2.8481736933131541</v>
+        <v>2.2671625451645268</v>
       </c>
       <c r="P205" s="1">
         <v>190</v>
@@ -8661,7 +8681,7 @@
     <row r="206" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O206">
         <f t="shared" ca="1" si="23"/>
-        <v>2.1169736507195438</v>
+        <v>2.6407324537158732</v>
       </c>
       <c r="P206" s="1">
         <v>191</v>
@@ -8673,7 +8693,7 @@
     <row r="207" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O207">
         <f t="shared" ca="1" si="23"/>
-        <v>2.4837917259840863</v>
+        <v>2.6014973395768761</v>
       </c>
       <c r="P207" s="1">
         <v>192</v>
@@ -8685,7 +8705,7 @@
     <row r="208" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O208">
         <f t="shared" ca="1" si="23"/>
-        <v>2.5128003109067523</v>
+        <v>2.6422437600098814</v>
       </c>
       <c r="P208" s="1">
         <v>193</v>
@@ -8697,7 +8717,7 @@
     <row r="209" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O209">
         <f t="shared" ca="1" si="23"/>
-        <v>2.4342462281492554</v>
+        <v>2.9532412561146359</v>
       </c>
       <c r="P209" s="1">
         <v>194</v>
@@ -8709,7 +8729,7 @@
     <row r="210" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O210">
         <f t="shared" ca="1" si="23"/>
-        <v>2.7383764677876434</v>
+        <v>2.317509813795148</v>
       </c>
       <c r="P210" s="1">
         <v>195</v>
@@ -8721,7 +8741,7 @@
     <row r="211" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O211">
         <f t="shared" ca="1" si="23"/>
-        <v>2.8361830382260065</v>
+        <v>2.2636384952618229</v>
       </c>
       <c r="P211" s="1">
         <v>203</v>
@@ -8733,7 +8753,7 @@
     <row r="212" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O212">
         <f t="shared" ca="1" si="23"/>
-        <v>2.6200229756405959</v>
+        <v>2.547011214009562</v>
       </c>
       <c r="P212" s="1">
         <v>204</v>
@@ -8745,7 +8765,7 @@
     <row r="213" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O213">
         <f t="shared" ca="1" si="23"/>
-        <v>2.9415618732437339</v>
+        <v>2.7658140613647948</v>
       </c>
       <c r="P213" s="1">
         <v>205</v>
@@ -8757,7 +8777,7 @@
     <row r="214" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O214">
         <f t="shared" ca="1" si="23"/>
-        <v>2.2496629670219694</v>
+        <v>2.4273060109489082</v>
       </c>
       <c r="P214" s="1">
         <v>206</v>
@@ -8769,7 +8789,7 @@
     <row r="215" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O215">
         <f t="shared" ca="1" si="23"/>
-        <v>2.9121011433367125</v>
+        <v>2.3756147398347838</v>
       </c>
       <c r="P215" s="1">
         <v>207</v>
@@ -8781,7 +8801,7 @@
     <row r="216" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O216">
         <f t="shared" ca="1" si="23"/>
-        <v>2.7195378087239632</v>
+        <v>2.5733191645225881</v>
       </c>
       <c r="P216" s="1">
         <v>208</v>
@@ -8793,7 +8813,7 @@
     <row r="217" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O217">
         <f t="shared" ca="1" si="23"/>
-        <v>2.2692833872392892</v>
+        <v>2.371562636394724</v>
       </c>
       <c r="P217" s="1">
         <v>216</v>
@@ -8805,7 +8825,7 @@
     <row r="218" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O218">
         <f t="shared" ca="1" si="23"/>
-        <v>2.9384836016708826</v>
+        <v>2.9233594739757156</v>
       </c>
       <c r="P218" s="1">
         <v>217</v>
@@ -8817,7 +8837,7 @@
     <row r="219" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O219">
         <f t="shared" ca="1" si="23"/>
-        <v>2.5645585143042671</v>
+        <v>2.3710708568553396</v>
       </c>
       <c r="P219" s="1">
         <v>218</v>
@@ -8829,7 +8849,7 @@
     <row r="220" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O220">
         <f t="shared" ca="1" si="23"/>
-        <v>2.9219175426237802</v>
+        <v>2.3581203636957091</v>
       </c>
       <c r="P220" s="1">
         <v>219</v>
@@ -8841,7 +8861,7 @@
     <row r="221" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O221">
         <f t="shared" ca="1" si="23"/>
-        <v>2.6166797704830755</v>
+        <v>2.0741894238366507</v>
       </c>
       <c r="P221" s="1">
         <v>220</v>
@@ -8853,7 +8873,7 @@
     <row r="222" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O222">
         <f t="shared" ca="1" si="23"/>
-        <v>2.434149399008918</v>
+        <v>2.1652813875890606</v>
       </c>
       <c r="P222" s="1">
         <v>221</v>
@@ -8863,12 +8883,12 @@
       </c>
     </row>
   </sheetData>
-  <sortState ref="P2:Q222">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="P2:Q222">
     <sortCondition ref="Q2:Q222"/>
     <sortCondition ref="P2:P222"/>
   </sortState>
   <conditionalFormatting sqref="W1:AI17">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="notEqual">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="notEqual">
       <formula>" "</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8877,7 +8897,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AG23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -11010,7 +11030,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="U1:AG17">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="notEqual">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="notEqual">
       <formula>" "</formula>
     </cfRule>
   </conditionalFormatting>

--- a/xls/Amostragem.xlsx
+++ b/xls/Amostragem.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/eac9aab033b2f962/Documentos/estatistica2025/xls/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/eac9aab033b2f962/Documentos/estatistica2026/xls/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="11_4E7C30BA6A8916509F05B54A2979D2F4DD3A67BB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9ACEF6E1-557B-417F-9AF4-E104C6FC6F1E}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="11_4E7C30BA6A8916509F05B54A2979D2F4DD3A67BB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3CAC5C1F-722D-4539-A936-7CD23AD87ACB}"/>
   <bookViews>
-    <workbookView xWindow="330" yWindow="1740" windowWidth="26610" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Simples" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="12">
   <si>
     <t>ID</t>
   </si>
@@ -67,13 +67,10 @@
     <t>nrows</t>
   </si>
   <si>
-    <t>#http://urlib.net/8JMKD2USNRW34T/4D6DMD2</t>
-  </si>
-  <si>
     <t>#https://cdrenno.github.io/Estatistica/</t>
   </si>
   <si>
-    <t>#Estatística: Aplicação ao Sensoriamento Remoto - SER204, INPE, 2025</t>
+    <t>#Estatística: Aplicação ao Sensoriamento Remoto - SER204, INPE, 2026</t>
   </si>
 </sst>
 </file>
@@ -569,9 +566,9 @@
         <f ca="1">IF(ISNUMBER(MATCH(A1,$S$2:$S$11,0)),A1," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="W1" s="2" t="str">
+      <c r="W1" s="2">
         <f t="shared" ref="W1:AH1" ca="1" si="0">IF(ISNUMBER(MATCH(B1,$S$2:$S$11,0)),B1," ")</f>
-        <v xml:space="preserve"> </v>
+        <v>2</v>
       </c>
       <c r="X1" s="2" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -673,18 +670,18 @@
       </c>
       <c r="O2">
         <f ca="1">RAND()</f>
-        <v>0.37102966958355255</v>
+        <v>0.85260464437160222</v>
       </c>
       <c r="P2" s="1">
         <v>1</v>
       </c>
       <c r="R2" s="1">
         <f ca="1">SMALL(O:O,ROW(R1))</f>
-        <v>2.0191793424561011E-3</v>
+        <v>4.0241779871056371E-3</v>
       </c>
       <c r="S2">
         <f ca="1">VLOOKUP(R2,O$2:P$222,2,0)</f>
-        <v>47</v>
+        <v>186</v>
       </c>
       <c r="V2" s="2" t="str">
         <f t="shared" ref="V2:V17" ca="1" si="2">IF(ISNUMBER(MATCH(A2,$S$2:$S$11,0)),A2," ")</f>
@@ -702,9 +699,9 @@
         <f t="shared" ref="Y2:Y17" ca="1" si="5">IF(ISNUMBER(MATCH(D2,$S$2:$S$11,0)),D2," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="Z2" s="2">
+      <c r="Z2" s="2" t="str">
         <f t="shared" ref="Z2:Z17" ca="1" si="6">IF(ISNUMBER(MATCH(E2,$S$2:$S$11,0)),E2," ")</f>
-        <v>18</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="AA2" s="2" t="str">
         <f t="shared" ref="AA2:AA17" ca="1" si="7">IF(ISNUMBER(MATCH(F2,$S$2:$S$11,0)),F2," ")</f>
@@ -794,18 +791,18 @@
       </c>
       <c r="O3">
         <f t="shared" ref="O3:O66" ca="1" si="28">RAND()</f>
-        <v>0.52157335097252822</v>
+        <v>3.5646066978272772E-2</v>
       </c>
       <c r="P3" s="1">
         <v>2</v>
       </c>
       <c r="R3" s="1">
         <f t="shared" ref="R3:R11" ca="1" si="29">SMALL(O:O,ROW(R2))</f>
-        <v>3.134557691421791E-3</v>
+        <v>9.4116742906069639E-3</v>
       </c>
       <c r="S3">
         <f t="shared" ref="S3:S11" ca="1" si="30">VLOOKUP(R3,O$2:P$222,2,0)</f>
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="V3" s="2" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -915,18 +912,18 @@
       </c>
       <c r="O4">
         <f t="shared" ca="1" si="28"/>
-        <v>0.63380872530826826</v>
+        <v>0.28156372234141136</v>
       </c>
       <c r="P4" s="1">
         <v>3</v>
       </c>
       <c r="R4" s="1">
         <f t="shared" ca="1" si="29"/>
-        <v>5.8647228006990515E-3</v>
+        <v>2.4377661776564863E-2</v>
       </c>
       <c r="S4">
         <f t="shared" ca="1" si="30"/>
-        <v>174</v>
+        <v>96</v>
       </c>
       <c r="V4" s="2" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -956,9 +953,9 @@
         <f t="shared" ca="1" si="8"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="AC4" s="2">
+      <c r="AC4" s="2" t="str">
         <f t="shared" ca="1" si="9"/>
-        <v>47</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="AD4" s="2" t="str">
         <f t="shared" ca="1" si="10"/>
@@ -1036,18 +1033,18 @@
       </c>
       <c r="O5">
         <f t="shared" ca="1" si="28"/>
-        <v>0.3117588885773076</v>
+        <v>0.24037549610346176</v>
       </c>
       <c r="P5" s="1">
         <v>4</v>
       </c>
       <c r="R5" s="1">
         <f t="shared" ca="1" si="29"/>
-        <v>9.9997976703954938E-3</v>
+        <v>2.5014526854212571E-2</v>
       </c>
       <c r="S5">
         <f t="shared" ca="1" si="30"/>
-        <v>183</v>
+        <v>83</v>
       </c>
       <c r="V5" s="2" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -1085,9 +1082,9 @@
         <f t="shared" ca="1" si="10"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="AE5" s="2">
+      <c r="AE5" s="2" t="str">
         <f t="shared" ca="1" si="11"/>
-        <v>62</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="AF5" s="2" t="str">
         <f t="shared" ca="1" si="12"/>
@@ -1157,18 +1154,18 @@
       </c>
       <c r="O6">
         <f t="shared" ca="1" si="28"/>
-        <v>0.54509459625213796</v>
+        <v>0.51999357889638131</v>
       </c>
       <c r="P6" s="1">
         <v>5</v>
       </c>
       <c r="R6" s="1">
         <f t="shared" ca="1" si="29"/>
-        <v>1.0876098334274831E-2</v>
+        <v>2.7822872982861568E-2</v>
       </c>
       <c r="S6">
         <f t="shared" ca="1" si="30"/>
-        <v>95</v>
+        <v>209</v>
       </c>
       <c r="V6" s="2" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -1278,22 +1275,22 @@
       </c>
       <c r="O7">
         <f t="shared" ca="1" si="28"/>
-        <v>0.51005437621835992</v>
+        <v>0.7991151858179586</v>
       </c>
       <c r="P7" s="1">
         <v>6</v>
       </c>
       <c r="R7" s="1">
         <f t="shared" ca="1" si="29"/>
-        <v>2.043789116537853E-2</v>
+        <v>3.4235637810398623E-2</v>
       </c>
       <c r="S7">
         <f t="shared" ca="1" si="30"/>
-        <v>171</v>
-      </c>
-      <c r="V7" s="2" t="str">
+        <v>213</v>
+      </c>
+      <c r="V7" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v xml:space="preserve"> </v>
+        <v>79</v>
       </c>
       <c r="W7" s="2" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -1307,9 +1304,9 @@
         <f t="shared" ca="1" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="Z7" s="2" t="str">
+      <c r="Z7" s="2">
         <f t="shared" ca="1" si="6"/>
-        <v xml:space="preserve"> </v>
+        <v>83</v>
       </c>
       <c r="AA7" s="2" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -1399,18 +1396,18 @@
       </c>
       <c r="O8">
         <f t="shared" ca="1" si="28"/>
-        <v>0.5663795707219017</v>
+        <v>0.36679436468455628</v>
       </c>
       <c r="P8" s="1">
         <v>7</v>
       </c>
       <c r="R8" s="1">
         <f t="shared" ca="1" si="29"/>
-        <v>2.1567376858265153E-2</v>
+        <v>3.5646066978272772E-2</v>
       </c>
       <c r="S8">
         <f t="shared" ca="1" si="30"/>
-        <v>110</v>
+        <v>2</v>
       </c>
       <c r="V8" s="2" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -1424,13 +1421,13 @@
         <f t="shared" ca="1" si="4"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="Y8" s="2">
+      <c r="Y8" s="2" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>95</v>
-      </c>
-      <c r="Z8" s="2" t="str">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="Z8" s="2">
         <f t="shared" ca="1" si="6"/>
-        <v xml:space="preserve"> </v>
+        <v>96</v>
       </c>
       <c r="AA8" s="2" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -1520,30 +1517,30 @@
       </c>
       <c r="O9">
         <f t="shared" ca="1" si="28"/>
-        <v>0.82494394690037753</v>
+        <v>0.89058617958001085</v>
       </c>
       <c r="P9" s="1">
         <v>8</v>
       </c>
       <c r="R9" s="1">
         <f t="shared" ca="1" si="29"/>
-        <v>2.1602811127403365E-2</v>
+        <v>3.867177641429731E-2</v>
       </c>
       <c r="S9">
         <f t="shared" ca="1" si="30"/>
-        <v>18</v>
+        <v>143</v>
       </c>
       <c r="V9" s="2" t="str">
         <f t="shared" ca="1" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="W9" s="2">
+      <c r="W9" s="2" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>106</v>
-      </c>
-      <c r="X9" s="2" t="str">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="X9" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v xml:space="preserve"> </v>
+        <v>107</v>
       </c>
       <c r="Y9" s="2" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -1553,9 +1550,9 @@
         <f t="shared" ca="1" si="6"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="AA9" s="2">
+      <c r="AA9" s="2" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>110</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="AB9" s="2" t="str">
         <f t="shared" ca="1" si="8"/>
@@ -1641,18 +1638,18 @@
       </c>
       <c r="O10">
         <f t="shared" ca="1" si="28"/>
-        <v>0.51763543851128369</v>
+        <v>0.20838206546241123</v>
       </c>
       <c r="P10" s="1">
         <v>9</v>
       </c>
       <c r="R10" s="1">
         <f t="shared" ca="1" si="29"/>
-        <v>2.4872290531851804E-2</v>
+        <v>3.9104056431970902E-2</v>
       </c>
       <c r="S10">
         <f t="shared" ca="1" si="30"/>
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="V10" s="2" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -1762,18 +1759,18 @@
       </c>
       <c r="O11">
         <f t="shared" ca="1" si="28"/>
-        <v>0.9768084591494286</v>
+        <v>0.29263901972332507</v>
       </c>
       <c r="P11" s="1">
         <v>10</v>
       </c>
       <c r="R11" s="1">
         <f t="shared" ca="1" si="29"/>
-        <v>2.496026590579703E-2</v>
+        <v>4.1702289492631439E-2</v>
       </c>
       <c r="S11">
         <f t="shared" ca="1" si="30"/>
-        <v>141</v>
+        <v>172</v>
       </c>
       <c r="V11" s="2" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -1815,17 +1812,17 @@
         <f t="shared" ca="1" si="11"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="AF11" s="2">
+      <c r="AF11" s="2" t="str">
         <f t="shared" ca="1" si="12"/>
-        <v>141</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="AG11" s="2" t="str">
         <f t="shared" ca="1" si="13"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="AH11" s="2" t="str">
+      <c r="AH11" s="2">
         <f t="shared" ca="1" si="14"/>
-        <v xml:space="preserve"> </v>
+        <v>143</v>
       </c>
     </row>
     <row r="12" spans="1:34" x14ac:dyDescent="0.25">
@@ -1883,7 +1880,7 @@
       </c>
       <c r="O12">
         <f t="shared" ca="1" si="28"/>
-        <v>0.78284801737501664</v>
+        <v>8.9225029078294771E-2</v>
       </c>
       <c r="P12" s="1">
         <v>11</v>
@@ -1996,7 +1993,7 @@
       </c>
       <c r="O13">
         <f t="shared" ca="1" si="28"/>
-        <v>0.94377798994688777</v>
+        <v>0.7194465262264953</v>
       </c>
       <c r="P13" s="1">
         <v>12</v>
@@ -2109,7 +2106,7 @@
       </c>
       <c r="O14">
         <f t="shared" ca="1" si="28"/>
-        <v>0.56791494017624755</v>
+        <v>0.5585129416500878</v>
       </c>
       <c r="P14" s="1">
         <v>13</v>
@@ -2118,21 +2115,21 @@
         <f t="shared" ca="1" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="W14" s="2">
+      <c r="W14" s="2" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>171</v>
-      </c>
-      <c r="X14" s="2" t="str">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="X14" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v xml:space="preserve"> </v>
+        <v>172</v>
       </c>
       <c r="Y14" s="2" t="str">
         <f t="shared" ca="1" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="Z14" s="2">
+      <c r="Z14" s="2" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>174</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="AA14" s="2" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -2222,14 +2219,14 @@
       </c>
       <c r="O15">
         <f t="shared" ca="1" si="28"/>
-        <v>0.4881619094932429</v>
+        <v>0.49931908100869893</v>
       </c>
       <c r="P15" s="1">
         <v>14</v>
       </c>
-      <c r="V15" s="2">
+      <c r="V15" s="2" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>183</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="W15" s="2" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -2239,9 +2236,9 @@
         <f t="shared" ca="1" si="4"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="Y15" s="2" t="str">
+      <c r="Y15" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v xml:space="preserve"> </v>
+        <v>186</v>
       </c>
       <c r="Z15" s="2" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -2335,7 +2332,7 @@
       </c>
       <c r="O16">
         <f t="shared" ca="1" si="28"/>
-        <v>0.85516191515029016</v>
+        <v>0.67942616355787044</v>
       </c>
       <c r="P16" s="1">
         <v>15</v>
@@ -2448,14 +2445,14 @@
       </c>
       <c r="O17">
         <f t="shared" ca="1" si="28"/>
-        <v>0.26573904006182092</v>
+        <v>0.622880169338624</v>
       </c>
       <c r="P17" s="1">
         <v>16</v>
       </c>
-      <c r="V17" s="2" t="str">
+      <c r="V17" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v xml:space="preserve"> </v>
+        <v>209</v>
       </c>
       <c r="W17" s="2" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -2469,9 +2466,9 @@
         <f t="shared" ca="1" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="Z17" s="2" t="str">
+      <c r="Z17" s="2">
         <f t="shared" ca="1" si="6"/>
-        <v xml:space="preserve"> </v>
+        <v>213</v>
       </c>
       <c r="AA17" s="2" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -2509,7 +2506,7 @@
     <row r="18" spans="1:34" x14ac:dyDescent="0.25">
       <c r="O18">
         <f t="shared" ca="1" si="28"/>
-        <v>4.4122555877982195E-2</v>
+        <v>0.72007937885955942</v>
       </c>
       <c r="P18" s="1">
         <v>17</v>
@@ -2517,11 +2514,11 @@
     </row>
     <row r="19" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O19">
         <f t="shared" ca="1" si="28"/>
-        <v>2.1602811127403365E-2</v>
+        <v>0.73922029409958867</v>
       </c>
       <c r="P19" s="1">
         <v>18</v>
@@ -2533,19 +2530,16 @@
       </c>
       <c r="O20">
         <f t="shared" ca="1" si="28"/>
-        <v>0.50949092136283192</v>
+        <v>0.68818217604453069</v>
       </c>
       <c r="P20" s="1">
         <v>19</v>
       </c>
     </row>
     <row r="21" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>11</v>
-      </c>
       <c r="O21">
         <f t="shared" ca="1" si="28"/>
-        <v>0.38293590227926178</v>
+        <v>0.3215200141506116</v>
       </c>
       <c r="P21" s="1">
         <v>20</v>
@@ -2554,7 +2548,7 @@
     <row r="22" spans="1:34" x14ac:dyDescent="0.25">
       <c r="O22">
         <f t="shared" ca="1" si="28"/>
-        <v>0.10403086450863352</v>
+        <v>0.59423041871672944</v>
       </c>
       <c r="P22" s="1">
         <v>21</v>
@@ -2563,7 +2557,7 @@
     <row r="23" spans="1:34" x14ac:dyDescent="0.25">
       <c r="O23">
         <f t="shared" ca="1" si="28"/>
-        <v>0.66199899030155918</v>
+        <v>0.16310161442613247</v>
       </c>
       <c r="P23" s="1">
         <v>22</v>
@@ -2572,7 +2566,7 @@
     <row r="24" spans="1:34" x14ac:dyDescent="0.25">
       <c r="O24">
         <f t="shared" ca="1" si="28"/>
-        <v>0.57929792754602849</v>
+        <v>0.77292016232678828</v>
       </c>
       <c r="P24" s="1">
         <v>23</v>
@@ -2581,7 +2575,7 @@
     <row r="25" spans="1:34" x14ac:dyDescent="0.25">
       <c r="O25">
         <f t="shared" ca="1" si="28"/>
-        <v>0.18681650081644618</v>
+        <v>0.73266721607469187</v>
       </c>
       <c r="P25" s="1">
         <v>24</v>
@@ -2590,7 +2584,7 @@
     <row r="26" spans="1:34" x14ac:dyDescent="0.25">
       <c r="O26">
         <f t="shared" ca="1" si="28"/>
-        <v>0.40530570492740725</v>
+        <v>0.2702325887664726</v>
       </c>
       <c r="P26" s="1">
         <v>25</v>
@@ -2599,7 +2593,7 @@
     <row r="27" spans="1:34" x14ac:dyDescent="0.25">
       <c r="O27">
         <f t="shared" ca="1" si="28"/>
-        <v>0.43327522580525679</v>
+        <v>0.33874351810358094</v>
       </c>
       <c r="P27" s="1">
         <v>26</v>
@@ -2608,7 +2602,7 @@
     <row r="28" spans="1:34" x14ac:dyDescent="0.25">
       <c r="O28">
         <f t="shared" ca="1" si="28"/>
-        <v>0.32810127683493273</v>
+        <v>0.43339893805689655</v>
       </c>
       <c r="P28" s="1">
         <v>27</v>
@@ -2617,7 +2611,7 @@
     <row r="29" spans="1:34" x14ac:dyDescent="0.25">
       <c r="O29">
         <f t="shared" ca="1" si="28"/>
-        <v>0.85484959849554187</v>
+        <v>0.74682465158258848</v>
       </c>
       <c r="P29" s="1">
         <v>28</v>
@@ -2626,7 +2620,7 @@
     <row r="30" spans="1:34" x14ac:dyDescent="0.25">
       <c r="O30">
         <f t="shared" ca="1" si="28"/>
-        <v>0.59696064086587441</v>
+        <v>0.52200702416019618</v>
       </c>
       <c r="P30" s="1">
         <v>29</v>
@@ -2635,7 +2629,7 @@
     <row r="31" spans="1:34" x14ac:dyDescent="0.25">
       <c r="O31">
         <f t="shared" ca="1" si="28"/>
-        <v>0.78807818817708064</v>
+        <v>0.82110504632167314</v>
       </c>
       <c r="P31" s="1">
         <v>30</v>
@@ -2644,7 +2638,7 @@
     <row r="32" spans="1:34" x14ac:dyDescent="0.25">
       <c r="O32">
         <f t="shared" ca="1" si="28"/>
-        <v>0.60507273032808739</v>
+        <v>0.44544697915021703</v>
       </c>
       <c r="P32" s="1">
         <v>31</v>
@@ -2653,7 +2647,7 @@
     <row r="33" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O33">
         <f t="shared" ca="1" si="28"/>
-        <v>0.74922628934047153</v>
+        <v>0.97107259852543415</v>
       </c>
       <c r="P33" s="1">
         <v>32</v>
@@ -2662,7 +2656,7 @@
     <row r="34" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O34">
         <f t="shared" ca="1" si="28"/>
-        <v>0.43020444317209561</v>
+        <v>0.54892468535809358</v>
       </c>
       <c r="P34" s="1">
         <v>33</v>
@@ -2671,7 +2665,7 @@
     <row r="35" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O35">
         <f t="shared" ca="1" si="28"/>
-        <v>0.75671837232957806</v>
+        <v>0.9599714376770363</v>
       </c>
       <c r="P35" s="1">
         <v>34</v>
@@ -2680,7 +2674,7 @@
     <row r="36" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O36">
         <f t="shared" ca="1" si="28"/>
-        <v>0.79568915211013713</v>
+        <v>0.4894581965891075</v>
       </c>
       <c r="P36" s="1">
         <v>35</v>
@@ -2689,7 +2683,7 @@
     <row r="37" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O37">
         <f t="shared" ca="1" si="28"/>
-        <v>0.70449353362568601</v>
+        <v>0.71348935092820198</v>
       </c>
       <c r="P37" s="1">
         <v>36</v>
@@ -2698,7 +2692,7 @@
     <row r="38" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O38">
         <f t="shared" ca="1" si="28"/>
-        <v>0.54292924838758205</v>
+        <v>8.1237896595346082E-2</v>
       </c>
       <c r="P38" s="1">
         <v>37</v>
@@ -2707,7 +2701,7 @@
     <row r="39" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O39">
         <f t="shared" ca="1" si="28"/>
-        <v>0.43388098338988601</v>
+        <v>5.8991241612329937E-2</v>
       </c>
       <c r="P39" s="1">
         <v>38</v>
@@ -2716,7 +2710,7 @@
     <row r="40" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O40">
         <f t="shared" ca="1" si="28"/>
-        <v>0.33783337933943547</v>
+        <v>0.966929444613843</v>
       </c>
       <c r="P40" s="1">
         <v>39</v>
@@ -2725,7 +2719,7 @@
     <row r="41" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O41">
         <f t="shared" ca="1" si="28"/>
-        <v>0.67478873896790381</v>
+        <v>7.2264718074371403E-2</v>
       </c>
       <c r="P41" s="1">
         <v>40</v>
@@ -2734,7 +2728,7 @@
     <row r="42" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O42">
         <f t="shared" ca="1" si="28"/>
-        <v>0.84771265139377228</v>
+        <v>0.79058517087744451</v>
       </c>
       <c r="P42" s="1">
         <v>41</v>
@@ -2743,7 +2737,7 @@
     <row r="43" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O43">
         <f t="shared" ca="1" si="28"/>
-        <v>0.19614379752005506</v>
+        <v>0.16713347420183911</v>
       </c>
       <c r="P43" s="1">
         <v>42</v>
@@ -2752,7 +2746,7 @@
     <row r="44" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O44">
         <f t="shared" ca="1" si="28"/>
-        <v>0.69571575606989555</v>
+        <v>0.97021008946674048</v>
       </c>
       <c r="P44" s="1">
         <v>43</v>
@@ -2761,7 +2755,7 @@
     <row r="45" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O45">
         <f t="shared" ca="1" si="28"/>
-        <v>0.4508797028528494</v>
+        <v>0.21610397668092873</v>
       </c>
       <c r="P45" s="1">
         <v>44</v>
@@ -2770,7 +2764,7 @@
     <row r="46" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O46">
         <f t="shared" ca="1" si="28"/>
-        <v>0.17859237453903565</v>
+        <v>0.44535364974654601</v>
       </c>
       <c r="P46" s="1">
         <v>45</v>
@@ -2779,7 +2773,7 @@
     <row r="47" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O47">
         <f t="shared" ca="1" si="28"/>
-        <v>0.45618890210766461</v>
+        <v>0.60652013395763016</v>
       </c>
       <c r="P47" s="1">
         <v>46</v>
@@ -2788,7 +2782,7 @@
     <row r="48" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O48">
         <f t="shared" ca="1" si="28"/>
-        <v>2.0191793424561011E-3</v>
+        <v>0.13073848660874687</v>
       </c>
       <c r="P48" s="1">
         <v>47</v>
@@ -2797,7 +2791,7 @@
     <row r="49" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O49">
         <f t="shared" ca="1" si="28"/>
-        <v>0.60969741229845043</v>
+        <v>0.65580704556772695</v>
       </c>
       <c r="P49" s="1">
         <v>48</v>
@@ -2806,7 +2800,7 @@
     <row r="50" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O50">
         <f t="shared" ca="1" si="28"/>
-        <v>0.66382264484389664</v>
+        <v>0.42819732396339882</v>
       </c>
       <c r="P50" s="1">
         <v>49</v>
@@ -2815,7 +2809,7 @@
     <row r="51" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O51">
         <f t="shared" ca="1" si="28"/>
-        <v>0.95705523125701253</v>
+        <v>0.46133078060811683</v>
       </c>
       <c r="P51" s="1">
         <v>50</v>
@@ -2824,7 +2818,7 @@
     <row r="52" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O52">
         <f t="shared" ca="1" si="28"/>
-        <v>0.66744084382289759</v>
+        <v>0.50532381241496838</v>
       </c>
       <c r="P52" s="1">
         <v>51</v>
@@ -2833,7 +2827,7 @@
     <row r="53" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O53">
         <f t="shared" ca="1" si="28"/>
-        <v>0.39898415743665983</v>
+        <v>0.15395338140959247</v>
       </c>
       <c r="P53" s="1">
         <v>52</v>
@@ -2842,7 +2836,7 @@
     <row r="54" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O54">
         <f t="shared" ca="1" si="28"/>
-        <v>0.91016522653306331</v>
+        <v>0.56557854912639649</v>
       </c>
       <c r="P54" s="1">
         <v>53</v>
@@ -2851,7 +2845,7 @@
     <row r="55" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O55">
         <f t="shared" ca="1" si="28"/>
-        <v>0.62599551713930812</v>
+        <v>0.2323713319072972</v>
       </c>
       <c r="P55" s="1">
         <v>54</v>
@@ -2860,7 +2854,7 @@
     <row r="56" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O56">
         <f t="shared" ca="1" si="28"/>
-        <v>9.0319112608777674E-2</v>
+        <v>0.63668470583830716</v>
       </c>
       <c r="P56" s="1">
         <v>55</v>
@@ -2869,7 +2863,7 @@
     <row r="57" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O57">
         <f t="shared" ca="1" si="28"/>
-        <v>0.86646538354934843</v>
+        <v>0.55166320175663641</v>
       </c>
       <c r="P57" s="1">
         <v>56</v>
@@ -2878,7 +2872,7 @@
     <row r="58" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O58">
         <f t="shared" ca="1" si="28"/>
-        <v>0.40907002604899423</v>
+        <v>0.2426855356579366</v>
       </c>
       <c r="P58" s="1">
         <v>57</v>
@@ -2887,7 +2881,7 @@
     <row r="59" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O59">
         <f t="shared" ca="1" si="28"/>
-        <v>0.67004623607692304</v>
+        <v>0.24482465684460086</v>
       </c>
       <c r="P59" s="1">
         <v>58</v>
@@ -2896,7 +2890,7 @@
     <row r="60" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O60">
         <f t="shared" ca="1" si="28"/>
-        <v>0.65420911693824546</v>
+        <v>0.89842449171387606</v>
       </c>
       <c r="P60" s="1">
         <v>59</v>
@@ -2905,7 +2899,7 @@
     <row r="61" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O61">
         <f t="shared" ca="1" si="28"/>
-        <v>0.92796509401366678</v>
+        <v>0.3980856269568227</v>
       </c>
       <c r="P61" s="1">
         <v>60</v>
@@ -2914,7 +2908,7 @@
     <row r="62" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O62">
         <f t="shared" ca="1" si="28"/>
-        <v>0.52811227181591003</v>
+        <v>0.57788759823097979</v>
       </c>
       <c r="P62" s="1">
         <v>61</v>
@@ -2923,7 +2917,7 @@
     <row r="63" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O63">
         <f t="shared" ca="1" si="28"/>
-        <v>3.134557691421791E-3</v>
+        <v>0.16355972698944365</v>
       </c>
       <c r="P63" s="1">
         <v>62</v>
@@ -2932,7 +2926,7 @@
     <row r="64" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O64">
         <f t="shared" ca="1" si="28"/>
-        <v>0.54267903475901136</v>
+        <v>0.61249635309499162</v>
       </c>
       <c r="P64" s="1">
         <v>63</v>
@@ -2941,7 +2935,7 @@
     <row r="65" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O65">
         <f t="shared" ca="1" si="28"/>
-        <v>7.0848575465014996E-2</v>
+        <v>0.85986627596385878</v>
       </c>
       <c r="P65" s="1">
         <v>64</v>
@@ -2950,7 +2944,7 @@
     <row r="66" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O66">
         <f t="shared" ca="1" si="28"/>
-        <v>0.82802963644508942</v>
+        <v>0.68696693853113555</v>
       </c>
       <c r="P66" s="1">
         <v>65</v>
@@ -2959,7 +2953,7 @@
     <row r="67" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O67">
         <f t="shared" ref="O67:O130" ca="1" si="31">RAND()</f>
-        <v>0.93039830240936638</v>
+        <v>0.75799578311192373</v>
       </c>
       <c r="P67" s="1">
         <v>66</v>
@@ -2968,7 +2962,7 @@
     <row r="68" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O68">
         <f t="shared" ca="1" si="31"/>
-        <v>0.32292467180316009</v>
+        <v>0.53370966322562174</v>
       </c>
       <c r="P68" s="1">
         <v>67</v>
@@ -2977,7 +2971,7 @@
     <row r="69" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O69">
         <f t="shared" ca="1" si="31"/>
-        <v>0.36243339814992859</v>
+        <v>0.95580001824803829</v>
       </c>
       <c r="P69" s="1">
         <v>68</v>
@@ -2986,7 +2980,7 @@
     <row r="70" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O70">
         <f t="shared" ca="1" si="31"/>
-        <v>0.60584159362207746</v>
+        <v>0.62105172567444311</v>
       </c>
       <c r="P70" s="1">
         <v>69</v>
@@ -2995,7 +2989,7 @@
     <row r="71" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O71">
         <f t="shared" ca="1" si="31"/>
-        <v>0.11713456746873352</v>
+        <v>0.61731207888537531</v>
       </c>
       <c r="P71" s="1">
         <v>70</v>
@@ -3004,7 +2998,7 @@
     <row r="72" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O72">
         <f t="shared" ca="1" si="31"/>
-        <v>0.91711939450652213</v>
+        <v>6.9964958113290621E-2</v>
       </c>
       <c r="P72" s="1">
         <v>71</v>
@@ -3013,7 +3007,7 @@
     <row r="73" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O73">
         <f t="shared" ca="1" si="31"/>
-        <v>0.55367897065532246</v>
+        <v>0.74089119422867655</v>
       </c>
       <c r="P73" s="1">
         <v>72</v>
@@ -3022,7 +3016,7 @@
     <row r="74" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O74">
         <f t="shared" ca="1" si="31"/>
-        <v>0.71957787091052461</v>
+        <v>6.2838749635755975E-2</v>
       </c>
       <c r="P74" s="1">
         <v>73</v>
@@ -3031,7 +3025,7 @@
     <row r="75" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O75">
         <f t="shared" ca="1" si="31"/>
-        <v>0.90282823498110354</v>
+        <v>0.29405172664562296</v>
       </c>
       <c r="P75" s="1">
         <v>74</v>
@@ -3040,7 +3034,7 @@
     <row r="76" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O76">
         <f t="shared" ca="1" si="31"/>
-        <v>0.56214732769817166</v>
+        <v>0.91418522483456666</v>
       </c>
       <c r="P76" s="1">
         <v>75</v>
@@ -3049,7 +3043,7 @@
     <row r="77" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O77">
         <f t="shared" ca="1" si="31"/>
-        <v>0.28595600135760202</v>
+        <v>0.35873543535737706</v>
       </c>
       <c r="P77" s="1">
         <v>76</v>
@@ -3058,7 +3052,7 @@
     <row r="78" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O78">
         <f t="shared" ca="1" si="31"/>
-        <v>2.9168653973689063E-2</v>
+        <v>0.97270987363459871</v>
       </c>
       <c r="P78" s="1">
         <v>77</v>
@@ -3067,7 +3061,7 @@
     <row r="79" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O79">
         <f t="shared" ca="1" si="31"/>
-        <v>0.60736521054292547</v>
+        <v>0.79559796732010302</v>
       </c>
       <c r="P79" s="1">
         <v>78</v>
@@ -3076,7 +3070,7 @@
     <row r="80" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O80">
         <f t="shared" ca="1" si="31"/>
-        <v>0.63721069796361174</v>
+        <v>9.4116742906069639E-3</v>
       </c>
       <c r="P80" s="1">
         <v>79</v>
@@ -3085,7 +3079,7 @@
     <row r="81" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O81">
         <f t="shared" ca="1" si="31"/>
-        <v>0.81462816034269125</v>
+        <v>0.35877086656216883</v>
       </c>
       <c r="P81" s="1">
         <v>80</v>
@@ -3094,7 +3088,7 @@
     <row r="82" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O82">
         <f t="shared" ca="1" si="31"/>
-        <v>0.91037613502909376</v>
+        <v>0.83024536683713424</v>
       </c>
       <c r="P82" s="1">
         <v>81</v>
@@ -3103,7 +3097,7 @@
     <row r="83" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O83">
         <f t="shared" ca="1" si="31"/>
-        <v>5.4968297360973417E-2</v>
+        <v>0.2492912812160728</v>
       </c>
       <c r="P83" s="1">
         <v>82</v>
@@ -3112,7 +3106,7 @@
     <row r="84" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O84">
         <f t="shared" ca="1" si="31"/>
-        <v>0.53871992953234638</v>
+        <v>2.5014526854212571E-2</v>
       </c>
       <c r="P84" s="1">
         <v>83</v>
@@ -3121,7 +3115,7 @@
     <row r="85" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O85">
         <f t="shared" ca="1" si="31"/>
-        <v>0.19803158125461151</v>
+        <v>0.49497022697576709</v>
       </c>
       <c r="P85" s="1">
         <v>84</v>
@@ -3130,7 +3124,7 @@
     <row r="86" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O86">
         <f t="shared" ca="1" si="31"/>
-        <v>0.67765472518094116</v>
+        <v>0.39881530220702865</v>
       </c>
       <c r="P86" s="1">
         <v>85</v>
@@ -3139,7 +3133,7 @@
     <row r="87" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O87">
         <f t="shared" ca="1" si="31"/>
-        <v>0.47701583087396604</v>
+        <v>0.94438326696684205</v>
       </c>
       <c r="P87" s="1">
         <v>86</v>
@@ -3148,7 +3142,7 @@
     <row r="88" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O88">
         <f t="shared" ca="1" si="31"/>
-        <v>0.9953717896134191</v>
+        <v>0.51120933809990832</v>
       </c>
       <c r="P88" s="1">
         <v>87</v>
@@ -3157,7 +3151,7 @@
     <row r="89" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O89">
         <f t="shared" ca="1" si="31"/>
-        <v>0.60296355502827259</v>
+        <v>0.29164154267460762</v>
       </c>
       <c r="P89" s="1">
         <v>88</v>
@@ -3166,7 +3160,7 @@
     <row r="90" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O90">
         <f t="shared" ca="1" si="31"/>
-        <v>0.2504515002470995</v>
+        <v>0.17380292122463581</v>
       </c>
       <c r="P90" s="1">
         <v>89</v>
@@ -3175,7 +3169,7 @@
     <row r="91" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O91">
         <f t="shared" ca="1" si="31"/>
-        <v>0.8422036527324428</v>
+        <v>0.89443418320234791</v>
       </c>
       <c r="P91" s="1">
         <v>90</v>
@@ -3184,7 +3178,7 @@
     <row r="92" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O92">
         <f t="shared" ca="1" si="31"/>
-        <v>0.16916195424214331</v>
+        <v>0.20511804967251801</v>
       </c>
       <c r="P92" s="1">
         <v>91</v>
@@ -3193,7 +3187,7 @@
     <row r="93" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O93">
         <f t="shared" ca="1" si="31"/>
-        <v>0.19041296124807461</v>
+        <v>0.23361906509493424</v>
       </c>
       <c r="P93" s="1">
         <v>92</v>
@@ -3202,7 +3196,7 @@
     <row r="94" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O94">
         <f t="shared" ca="1" si="31"/>
-        <v>0.71714373558348354</v>
+        <v>0.78552720393991493</v>
       </c>
       <c r="P94" s="1">
         <v>93</v>
@@ -3211,7 +3205,7 @@
     <row r="95" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O95">
         <f t="shared" ca="1" si="31"/>
-        <v>0.5104372183439998</v>
+        <v>0.18369033699921067</v>
       </c>
       <c r="P95" s="1">
         <v>94</v>
@@ -3220,7 +3214,7 @@
     <row r="96" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O96">
         <f t="shared" ca="1" si="31"/>
-        <v>1.0876098334274831E-2</v>
+        <v>0.88634774358676838</v>
       </c>
       <c r="P96" s="1">
         <v>95</v>
@@ -3229,7 +3223,7 @@
     <row r="97" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O97">
         <f t="shared" ca="1" si="31"/>
-        <v>0.1624291859768392</v>
+        <v>2.4377661776564863E-2</v>
       </c>
       <c r="P97" s="1">
         <v>96</v>
@@ -3238,7 +3232,7 @@
     <row r="98" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O98">
         <f t="shared" ca="1" si="31"/>
-        <v>0.91746167328523687</v>
+        <v>0.36202865897166392</v>
       </c>
       <c r="P98" s="1">
         <v>97</v>
@@ -3247,7 +3241,7 @@
     <row r="99" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O99">
         <f t="shared" ca="1" si="31"/>
-        <v>0.79631408241411106</v>
+        <v>0.91213721470685372</v>
       </c>
       <c r="P99" s="1">
         <v>98</v>
@@ -3256,7 +3250,7 @@
     <row r="100" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O100">
         <f t="shared" ca="1" si="31"/>
-        <v>0.99632539031565759</v>
+        <v>0.71992628558212202</v>
       </c>
       <c r="P100" s="1">
         <v>99</v>
@@ -3265,7 +3259,7 @@
     <row r="101" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O101">
         <f t="shared" ca="1" si="31"/>
-        <v>0.48044757108451408</v>
+        <v>0.4642139065232086</v>
       </c>
       <c r="P101" s="1">
         <v>100</v>
@@ -3274,7 +3268,7 @@
     <row r="102" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O102">
         <f t="shared" ca="1" si="31"/>
-        <v>0.50756400186222717</v>
+        <v>0.44898366492825159</v>
       </c>
       <c r="P102" s="1">
         <v>101</v>
@@ -3283,7 +3277,7 @@
     <row r="103" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O103">
         <f t="shared" ca="1" si="31"/>
-        <v>0.66587433455487077</v>
+        <v>0.52307708987722379</v>
       </c>
       <c r="P103" s="1">
         <v>102</v>
@@ -3292,7 +3286,7 @@
     <row r="104" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O104">
         <f t="shared" ca="1" si="31"/>
-        <v>0.68929232624988379</v>
+        <v>0.10753194977876712</v>
       </c>
       <c r="P104" s="1">
         <v>103</v>
@@ -3301,7 +3295,7 @@
     <row r="105" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O105">
         <f t="shared" ca="1" si="31"/>
-        <v>0.72518088675187298</v>
+        <v>0.81557795087768814</v>
       </c>
       <c r="P105" s="1">
         <v>104</v>
@@ -3310,7 +3304,7 @@
     <row r="106" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O106">
         <f t="shared" ca="1" si="31"/>
-        <v>0.41492760649780125</v>
+        <v>0.616156408385234</v>
       </c>
       <c r="P106" s="1">
         <v>105</v>
@@ -3319,7 +3313,7 @@
     <row r="107" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O107">
         <f t="shared" ca="1" si="31"/>
-        <v>2.4872290531851804E-2</v>
+        <v>0.75578623242114029</v>
       </c>
       <c r="P107" s="1">
         <v>106</v>
@@ -3328,7 +3322,7 @@
     <row r="108" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O108">
         <f t="shared" ca="1" si="31"/>
-        <v>6.4474859784251271E-2</v>
+        <v>3.9104056431970902E-2</v>
       </c>
       <c r="P108" s="1">
         <v>107</v>
@@ -3337,7 +3331,7 @@
     <row r="109" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O109">
         <f t="shared" ca="1" si="31"/>
-        <v>0.32786625687497406</v>
+        <v>4.6436073235252451E-2</v>
       </c>
       <c r="P109" s="1">
         <v>108</v>
@@ -3346,7 +3340,7 @@
     <row r="110" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O110">
         <f t="shared" ca="1" si="31"/>
-        <v>0.98280473646816258</v>
+        <v>0.85323805709267131</v>
       </c>
       <c r="P110" s="1">
         <v>109</v>
@@ -3355,7 +3349,7 @@
     <row r="111" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O111">
         <f t="shared" ca="1" si="31"/>
-        <v>2.1567376858265153E-2</v>
+        <v>0.20447888184167762</v>
       </c>
       <c r="P111" s="1">
         <v>110</v>
@@ -3364,7 +3358,7 @@
     <row r="112" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O112">
         <f t="shared" ca="1" si="31"/>
-        <v>0.72423513309502774</v>
+        <v>0.7993373897702637</v>
       </c>
       <c r="P112" s="1">
         <v>111</v>
@@ -3373,7 +3367,7 @@
     <row r="113" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O113">
         <f t="shared" ca="1" si="31"/>
-        <v>0.70849985449114783</v>
+        <v>0.79130264350183599</v>
       </c>
       <c r="P113" s="1">
         <v>112</v>
@@ -3382,7 +3376,7 @@
     <row r="114" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O114">
         <f t="shared" ca="1" si="31"/>
-        <v>0.8361117802596244</v>
+        <v>0.33416587297222489</v>
       </c>
       <c r="P114" s="1">
         <v>113</v>
@@ -3391,7 +3385,7 @@
     <row r="115" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O115">
         <f t="shared" ca="1" si="31"/>
-        <v>0.68010145468997629</v>
+        <v>0.26447554899847092</v>
       </c>
       <c r="P115" s="1">
         <v>114</v>
@@ -3400,7 +3394,7 @@
     <row r="116" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O116">
         <f t="shared" ca="1" si="31"/>
-        <v>0.11657535518248574</v>
+        <v>0.74499314418325779</v>
       </c>
       <c r="P116" s="1">
         <v>115</v>
@@ -3409,7 +3403,7 @@
     <row r="117" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O117">
         <f t="shared" ca="1" si="31"/>
-        <v>0.785828441240498</v>
+        <v>0.60541683973266458</v>
       </c>
       <c r="P117" s="1">
         <v>116</v>
@@ -3418,7 +3412,7 @@
     <row r="118" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O118">
         <f t="shared" ca="1" si="31"/>
-        <v>0.13505586812171488</v>
+        <v>0.39396065722355644</v>
       </c>
       <c r="P118" s="1">
         <v>117</v>
@@ -3427,7 +3421,7 @@
     <row r="119" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O119">
         <f t="shared" ca="1" si="31"/>
-        <v>0.82411230217701925</v>
+        <v>0.3850116226931356</v>
       </c>
       <c r="P119" s="1">
         <v>118</v>
@@ -3436,7 +3430,7 @@
     <row r="120" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O120">
         <f t="shared" ca="1" si="31"/>
-        <v>0.13698393131398234</v>
+        <v>0.69597943286442487</v>
       </c>
       <c r="P120" s="1">
         <v>119</v>
@@ -3445,7 +3439,7 @@
     <row r="121" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O121">
         <f t="shared" ca="1" si="31"/>
-        <v>0.15011548775569883</v>
+        <v>0.83946148858013814</v>
       </c>
       <c r="P121" s="1">
         <v>120</v>
@@ -3454,7 +3448,7 @@
     <row r="122" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O122">
         <f t="shared" ca="1" si="31"/>
-        <v>0.33208773736786845</v>
+        <v>0.28437519068028849</v>
       </c>
       <c r="P122" s="1">
         <v>121</v>
@@ -3463,7 +3457,7 @@
     <row r="123" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O123">
         <f t="shared" ca="1" si="31"/>
-        <v>0.26813588114065268</v>
+        <v>0.45161305138601959</v>
       </c>
       <c r="P123" s="1">
         <v>122</v>
@@ -3472,7 +3466,7 @@
     <row r="124" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O124">
         <f t="shared" ca="1" si="31"/>
-        <v>0.92196776053228335</v>
+        <v>0.72305684633558065</v>
       </c>
       <c r="P124" s="1">
         <v>123</v>
@@ -3481,7 +3475,7 @@
     <row r="125" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O125">
         <f t="shared" ca="1" si="31"/>
-        <v>0.49118736941859731</v>
+        <v>0.45698816881923243</v>
       </c>
       <c r="P125" s="1">
         <v>124</v>
@@ -3490,7 +3484,7 @@
     <row r="126" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O126">
         <f t="shared" ca="1" si="31"/>
-        <v>0.82853278720272339</v>
+        <v>0.27031942995020108</v>
       </c>
       <c r="P126" s="1">
         <v>125</v>
@@ -3499,7 +3493,7 @@
     <row r="127" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O127">
         <f t="shared" ca="1" si="31"/>
-        <v>0.96015135877776248</v>
+        <v>0.26067432508495092</v>
       </c>
       <c r="P127" s="1">
         <v>126</v>
@@ -3508,7 +3502,7 @@
     <row r="128" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O128">
         <f t="shared" ca="1" si="31"/>
-        <v>0.30290632972651699</v>
+        <v>0.39690413186706286</v>
       </c>
       <c r="P128" s="1">
         <v>127</v>
@@ -3517,7 +3511,7 @@
     <row r="129" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O129">
         <f t="shared" ca="1" si="31"/>
-        <v>0.60495503284161145</v>
+        <v>7.9315326224109861E-2</v>
       </c>
       <c r="P129" s="1">
         <v>128</v>
@@ -3526,7 +3520,7 @@
     <row r="130" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O130">
         <f t="shared" ca="1" si="31"/>
-        <v>0.44274706306232103</v>
+        <v>0.69573658740670707</v>
       </c>
       <c r="P130" s="1">
         <v>129</v>
@@ -3535,7 +3529,7 @@
     <row r="131" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O131">
         <f t="shared" ref="O131:O194" ca="1" si="32">RAND()</f>
-        <v>0.35196722874369657</v>
+        <v>0.98931608231993751</v>
       </c>
       <c r="P131" s="1">
         <v>130</v>
@@ -3544,7 +3538,7 @@
     <row r="132" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O132">
         <f t="shared" ca="1" si="32"/>
-        <v>0.70528369745677877</v>
+        <v>0.2516315034148453</v>
       </c>
       <c r="P132" s="1">
         <v>131</v>
@@ -3553,7 +3547,7 @@
     <row r="133" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O133">
         <f t="shared" ca="1" si="32"/>
-        <v>0.67262272412633217</v>
+        <v>0.85246278230825601</v>
       </c>
       <c r="P133" s="1">
         <v>132</v>
@@ -3562,7 +3556,7 @@
     <row r="134" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O134">
         <f t="shared" ca="1" si="32"/>
-        <v>0.31019658883370549</v>
+        <v>0.2529344509975362</v>
       </c>
       <c r="P134" s="1">
         <v>133</v>
@@ -3571,7 +3565,7 @@
     <row r="135" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O135">
         <f t="shared" ca="1" si="32"/>
-        <v>0.96678661400499066</v>
+        <v>0.4660758185937186</v>
       </c>
       <c r="P135" s="1">
         <v>134</v>
@@ -3580,7 +3574,7 @@
     <row r="136" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O136">
         <f t="shared" ca="1" si="32"/>
-        <v>0.85906860087074066</v>
+        <v>0.68828982047886267</v>
       </c>
       <c r="P136" s="1">
         <v>135</v>
@@ -3589,7 +3583,7 @@
     <row r="137" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O137">
         <f t="shared" ca="1" si="32"/>
-        <v>0.75896553026846625</v>
+        <v>0.90881996531928921</v>
       </c>
       <c r="P137" s="1">
         <v>136</v>
@@ -3598,7 +3592,7 @@
     <row r="138" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O138">
         <f t="shared" ca="1" si="32"/>
-        <v>5.7108499154303272E-2</v>
+        <v>0.29197443884959273</v>
       </c>
       <c r="P138" s="1">
         <v>137</v>
@@ -3607,7 +3601,7 @@
     <row r="139" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O139">
         <f t="shared" ca="1" si="32"/>
-        <v>0.36255180480669624</v>
+        <v>0.69869643048695484</v>
       </c>
       <c r="P139" s="1">
         <v>138</v>
@@ -3616,7 +3610,7 @@
     <row r="140" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O140">
         <f t="shared" ca="1" si="32"/>
-        <v>0.10250334862150412</v>
+        <v>0.51693881794440222</v>
       </c>
       <c r="P140" s="1">
         <v>139</v>
@@ -3625,7 +3619,7 @@
     <row r="141" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O141">
         <f t="shared" ca="1" si="32"/>
-        <v>0.13608167162239948</v>
+        <v>0.78264683935599633</v>
       </c>
       <c r="P141" s="1">
         <v>140</v>
@@ -3634,7 +3628,7 @@
     <row r="142" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O142">
         <f t="shared" ca="1" si="32"/>
-        <v>2.496026590579703E-2</v>
+        <v>0.37513582094879871</v>
       </c>
       <c r="P142" s="1">
         <v>141</v>
@@ -3643,7 +3637,7 @@
     <row r="143" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O143">
         <f t="shared" ca="1" si="32"/>
-        <v>0.33787865183972765</v>
+        <v>5.1896346266935511E-2</v>
       </c>
       <c r="P143" s="1">
         <v>142</v>
@@ -3652,7 +3646,7 @@
     <row r="144" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O144">
         <f t="shared" ca="1" si="32"/>
-        <v>0.32122947831847681</v>
+        <v>3.867177641429731E-2</v>
       </c>
       <c r="P144" s="1">
         <v>143</v>
@@ -3661,7 +3655,7 @@
     <row r="145" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O145">
         <f t="shared" ca="1" si="32"/>
-        <v>0.21570467384455738</v>
+        <v>4.4478048218034139E-2</v>
       </c>
       <c r="P145" s="1">
         <v>144</v>
@@ -3670,7 +3664,7 @@
     <row r="146" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O146">
         <f t="shared" ca="1" si="32"/>
-        <v>8.3187238755551896E-2</v>
+        <v>0.65776545479231896</v>
       </c>
       <c r="P146" s="1">
         <v>145</v>
@@ -3679,7 +3673,7 @@
     <row r="147" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O147">
         <f t="shared" ca="1" si="32"/>
-        <v>0.10216043399934338</v>
+        <v>0.13951807476804068</v>
       </c>
       <c r="P147" s="1">
         <v>146</v>
@@ -3688,7 +3682,7 @@
     <row r="148" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O148">
         <f t="shared" ca="1" si="32"/>
-        <v>0.57068108631110903</v>
+        <v>0.968111916585632</v>
       </c>
       <c r="P148" s="1">
         <v>147</v>
@@ -3697,7 +3691,7 @@
     <row r="149" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O149">
         <f t="shared" ca="1" si="32"/>
-        <v>0.42405091624656033</v>
+        <v>0.2756936479524057</v>
       </c>
       <c r="P149" s="1">
         <v>148</v>
@@ -3706,7 +3700,7 @@
     <row r="150" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O150">
         <f t="shared" ca="1" si="32"/>
-        <v>0.48323474957528911</v>
+        <v>0.78667273572645768</v>
       </c>
       <c r="P150" s="1">
         <v>149</v>
@@ -3715,7 +3709,7 @@
     <row r="151" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O151">
         <f t="shared" ca="1" si="32"/>
-        <v>0.66228742058501477</v>
+        <v>0.27289562336953965</v>
       </c>
       <c r="P151" s="1">
         <v>150</v>
@@ -3724,7 +3718,7 @@
     <row r="152" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O152">
         <f t="shared" ca="1" si="32"/>
-        <v>0.66453772645222686</v>
+        <v>0.80353392595370232</v>
       </c>
       <c r="P152" s="1">
         <v>151</v>
@@ -3733,7 +3727,7 @@
     <row r="153" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O153">
         <f t="shared" ca="1" si="32"/>
-        <v>0.10796709734928545</v>
+        <v>5.2473571827122312E-2</v>
       </c>
       <c r="P153" s="1">
         <v>152</v>
@@ -3742,7 +3736,7 @@
     <row r="154" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O154">
         <f t="shared" ca="1" si="32"/>
-        <v>0.65901473406715105</v>
+        <v>9.3346350576234194E-2</v>
       </c>
       <c r="P154" s="1">
         <v>153</v>
@@ -3751,7 +3745,7 @@
     <row r="155" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O155">
         <f t="shared" ca="1" si="32"/>
-        <v>0.11710923897490855</v>
+        <v>0.37816255574708335</v>
       </c>
       <c r="P155" s="1">
         <v>154</v>
@@ -3760,7 +3754,7 @@
     <row r="156" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O156">
         <f t="shared" ca="1" si="32"/>
-        <v>0.78409418665093511</v>
+        <v>0.25422200040651377</v>
       </c>
       <c r="P156" s="1">
         <v>155</v>
@@ -3769,7 +3763,7 @@
     <row r="157" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O157">
         <f t="shared" ca="1" si="32"/>
-        <v>0.22717806886817848</v>
+        <v>0.90861002764777232</v>
       </c>
       <c r="P157" s="1">
         <v>156</v>
@@ -3778,7 +3772,7 @@
     <row r="158" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O158">
         <f t="shared" ca="1" si="32"/>
-        <v>0.37318065322452665</v>
+        <v>0.99524984674591366</v>
       </c>
       <c r="P158" s="1">
         <v>157</v>
@@ -3787,7 +3781,7 @@
     <row r="159" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O159">
         <f t="shared" ca="1" si="32"/>
-        <v>0.63173651668483621</v>
+        <v>0.38048233150491861</v>
       </c>
       <c r="P159" s="1">
         <v>158</v>
@@ -3796,7 +3790,7 @@
     <row r="160" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O160">
         <f t="shared" ca="1" si="32"/>
-        <v>0.70136634820263954</v>
+        <v>0.82417599156197396</v>
       </c>
       <c r="P160" s="1">
         <v>159</v>
@@ -3805,7 +3799,7 @@
     <row r="161" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O161">
         <f t="shared" ca="1" si="32"/>
-        <v>0.68384226068898579</v>
+        <v>0.46836398848163918</v>
       </c>
       <c r="P161" s="1">
         <v>160</v>
@@ -3814,7 +3808,7 @@
     <row r="162" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O162">
         <f t="shared" ca="1" si="32"/>
-        <v>0.33547050111315546</v>
+        <v>5.3051371703555894E-2</v>
       </c>
       <c r="P162" s="1">
         <v>161</v>
@@ -3823,7 +3817,7 @@
     <row r="163" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O163">
         <f t="shared" ca="1" si="32"/>
-        <v>7.5723221467644986E-2</v>
+        <v>0.27814350324824788</v>
       </c>
       <c r="P163" s="1">
         <v>162</v>
@@ -3832,7 +3826,7 @@
     <row r="164" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O164">
         <f t="shared" ca="1" si="32"/>
-        <v>0.96219244612567145</v>
+        <v>0.45201463426204158</v>
       </c>
       <c r="P164" s="1">
         <v>163</v>
@@ -3841,7 +3835,7 @@
     <row r="165" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O165">
         <f t="shared" ca="1" si="32"/>
-        <v>0.24420794448505045</v>
+        <v>0.29309357557688109</v>
       </c>
       <c r="P165" s="1">
         <v>164</v>
@@ -3850,7 +3844,7 @@
     <row r="166" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O166">
         <f t="shared" ca="1" si="32"/>
-        <v>0.41897911496815832</v>
+        <v>0.42816238905002313</v>
       </c>
       <c r="P166" s="1">
         <v>165</v>
@@ -3859,7 +3853,7 @@
     <row r="167" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O167">
         <f t="shared" ca="1" si="32"/>
-        <v>0.62292861889822304</v>
+        <v>0.15009217588009494</v>
       </c>
       <c r="P167" s="1">
         <v>166</v>
@@ -3868,7 +3862,7 @@
     <row r="168" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O168">
         <f t="shared" ca="1" si="32"/>
-        <v>0.45457631236544649</v>
+        <v>0.37051413537374311</v>
       </c>
       <c r="P168" s="1">
         <v>167</v>
@@ -3877,7 +3871,7 @@
     <row r="169" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O169">
         <f t="shared" ca="1" si="32"/>
-        <v>0.62317720230498452</v>
+        <v>6.9276786119726208E-2</v>
       </c>
       <c r="P169" s="1">
         <v>168</v>
@@ -3886,7 +3880,7 @@
     <row r="170" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O170">
         <f t="shared" ca="1" si="32"/>
-        <v>0.15211289797988026</v>
+        <v>0.71697219438346504</v>
       </c>
       <c r="P170" s="1">
         <v>169</v>
@@ -3895,7 +3889,7 @@
     <row r="171" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O171">
         <f t="shared" ca="1" si="32"/>
-        <v>0.53725297797994886</v>
+        <v>0.37792631476944083</v>
       </c>
       <c r="P171" s="1">
         <v>170</v>
@@ -3904,7 +3898,7 @@
     <row r="172" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O172">
         <f t="shared" ca="1" si="32"/>
-        <v>2.043789116537853E-2</v>
+        <v>7.5951854312831912E-2</v>
       </c>
       <c r="P172" s="1">
         <v>171</v>
@@ -3913,7 +3907,7 @@
     <row r="173" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O173">
         <f t="shared" ca="1" si="32"/>
-        <v>0.6112790838705594</v>
+        <v>4.1702289492631439E-2</v>
       </c>
       <c r="P173" s="1">
         <v>172</v>
@@ -3922,7 +3916,7 @@
     <row r="174" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O174">
         <f t="shared" ca="1" si="32"/>
-        <v>0.83410146612990888</v>
+        <v>0.72386436492345851</v>
       </c>
       <c r="P174" s="1">
         <v>173</v>
@@ -3931,7 +3925,7 @@
     <row r="175" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O175">
         <f t="shared" ca="1" si="32"/>
-        <v>5.8647228006990515E-3</v>
+        <v>0.71164133256302653</v>
       </c>
       <c r="P175" s="1">
         <v>174</v>
@@ -3940,7 +3934,7 @@
     <row r="176" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O176">
         <f t="shared" ca="1" si="32"/>
-        <v>0.78804923752719824</v>
+        <v>0.17799784591872148</v>
       </c>
       <c r="P176" s="1">
         <v>175</v>
@@ -3949,7 +3943,7 @@
     <row r="177" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O177">
         <f t="shared" ca="1" si="32"/>
-        <v>0.26740644882034192</v>
+        <v>0.73569856736145967</v>
       </c>
       <c r="P177" s="1">
         <v>176</v>
@@ -3958,7 +3952,7 @@
     <row r="178" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O178">
         <f t="shared" ca="1" si="32"/>
-        <v>0.83707383465372964</v>
+        <v>0.71442046247433844</v>
       </c>
       <c r="P178" s="1">
         <v>177</v>
@@ -3967,7 +3961,7 @@
     <row r="179" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O179">
         <f t="shared" ca="1" si="32"/>
-        <v>0.83856072580808427</v>
+        <v>0.60548998016848687</v>
       </c>
       <c r="P179" s="1">
         <v>178</v>
@@ -3976,7 +3970,7 @@
     <row r="180" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O180">
         <f t="shared" ca="1" si="32"/>
-        <v>0.20977321400085447</v>
+        <v>0.15972065053916407</v>
       </c>
       <c r="P180" s="1">
         <v>179</v>
@@ -3985,7 +3979,7 @@
     <row r="181" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O181">
         <f t="shared" ca="1" si="32"/>
-        <v>3.1969972690118031E-2</v>
+        <v>0.9808342054026945</v>
       </c>
       <c r="P181" s="1">
         <v>180</v>
@@ -3994,7 +3988,7 @@
     <row r="182" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O182">
         <f t="shared" ca="1" si="32"/>
-        <v>8.4487516497218973E-2</v>
+        <v>0.9064184512383503</v>
       </c>
       <c r="P182" s="1">
         <v>181</v>
@@ -4003,7 +3997,7 @@
     <row r="183" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O183">
         <f t="shared" ca="1" si="32"/>
-        <v>0.56820810750476936</v>
+        <v>0.4760035061297565</v>
       </c>
       <c r="P183" s="1">
         <v>182</v>
@@ -4012,7 +4006,7 @@
     <row r="184" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O184">
         <f t="shared" ca="1" si="32"/>
-        <v>9.9997976703954938E-3</v>
+        <v>0.18107091893410099</v>
       </c>
       <c r="P184" s="1">
         <v>183</v>
@@ -4021,7 +4015,7 @@
     <row r="185" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O185">
         <f t="shared" ca="1" si="32"/>
-        <v>0.90727809459489406</v>
+        <v>0.24100774498308075</v>
       </c>
       <c r="P185" s="1">
         <v>184</v>
@@ -4030,7 +4024,7 @@
     <row r="186" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O186">
         <f t="shared" ca="1" si="32"/>
-        <v>0.74834157915915245</v>
+        <v>0.44482289859385415</v>
       </c>
       <c r="P186" s="1">
         <v>185</v>
@@ -4039,7 +4033,7 @@
     <row r="187" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O187">
         <f t="shared" ca="1" si="32"/>
-        <v>0.29790608789289774</v>
+        <v>4.0241779871056371E-3</v>
       </c>
       <c r="P187" s="1">
         <v>186</v>
@@ -4048,7 +4042,7 @@
     <row r="188" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O188">
         <f t="shared" ca="1" si="32"/>
-        <v>0.99391878774475151</v>
+        <v>7.2052232695478668E-2</v>
       </c>
       <c r="P188" s="1">
         <v>187</v>
@@ -4057,7 +4051,7 @@
     <row r="189" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O189">
         <f t="shared" ca="1" si="32"/>
-        <v>0.54302648229043893</v>
+        <v>0.60251788064990897</v>
       </c>
       <c r="P189" s="1">
         <v>188</v>
@@ -4066,7 +4060,7 @@
     <row r="190" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O190">
         <f t="shared" ca="1" si="32"/>
-        <v>0.64272566124523534</v>
+        <v>0.94572182094113855</v>
       </c>
       <c r="P190" s="1">
         <v>189</v>
@@ -4075,7 +4069,7 @@
     <row r="191" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O191">
         <f t="shared" ca="1" si="32"/>
-        <v>0.79947156716615819</v>
+        <v>0.25108737533241232</v>
       </c>
       <c r="P191" s="1">
         <v>190</v>
@@ -4084,7 +4078,7 @@
     <row r="192" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O192">
         <f t="shared" ca="1" si="32"/>
-        <v>0.35835189157138292</v>
+        <v>0.81426639039130233</v>
       </c>
       <c r="P192" s="1">
         <v>191</v>
@@ -4093,7 +4087,7 @@
     <row r="193" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O193">
         <f t="shared" ca="1" si="32"/>
-        <v>0.53584384500145554</v>
+        <v>0.99623262355769637</v>
       </c>
       <c r="P193" s="1">
         <v>192</v>
@@ -4102,7 +4096,7 @@
     <row r="194" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O194">
         <f t="shared" ca="1" si="32"/>
-        <v>0.28928949756728006</v>
+        <v>0.97251013199758551</v>
       </c>
       <c r="P194" s="1">
         <v>193</v>
@@ -4111,7 +4105,7 @@
     <row r="195" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O195">
         <f t="shared" ref="O195:O222" ca="1" si="33">RAND()</f>
-        <v>0.93940711727172299</v>
+        <v>0.79067634270783127</v>
       </c>
       <c r="P195" s="1">
         <v>194</v>
@@ -4120,7 +4114,7 @@
     <row r="196" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O196">
         <f t="shared" ca="1" si="33"/>
-        <v>0.48204445362154047</v>
+        <v>0.47341053219809148</v>
       </c>
       <c r="P196" s="1">
         <v>195</v>
@@ -4129,7 +4123,7 @@
     <row r="197" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O197">
         <f t="shared" ca="1" si="33"/>
-        <v>0.53030932643513662</v>
+        <v>0.18924597594153347</v>
       </c>
       <c r="P197" s="1">
         <v>196</v>
@@ -4138,7 +4132,7 @@
     <row r="198" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O198">
         <f t="shared" ca="1" si="33"/>
-        <v>0.98674010512214916</v>
+        <v>0.1979344205322594</v>
       </c>
       <c r="P198" s="1">
         <v>197</v>
@@ -4147,7 +4141,7 @@
     <row r="199" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O199">
         <f t="shared" ca="1" si="33"/>
-        <v>0.42339260450519434</v>
+        <v>0.96291542611320158</v>
       </c>
       <c r="P199" s="1">
         <v>198</v>
@@ -4156,7 +4150,7 @@
     <row r="200" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O200">
         <f t="shared" ca="1" si="33"/>
-        <v>0.67163720026758378</v>
+        <v>0.75169795376474069</v>
       </c>
       <c r="P200" s="1">
         <v>199</v>
@@ -4165,7 +4159,7 @@
     <row r="201" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O201">
         <f t="shared" ca="1" si="33"/>
-        <v>0.24441153209615374</v>
+        <v>0.70048601410850175</v>
       </c>
       <c r="P201" s="1">
         <v>200</v>
@@ -4174,7 +4168,7 @@
     <row r="202" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O202">
         <f t="shared" ca="1" si="33"/>
-        <v>0.65738980248946821</v>
+        <v>4.1839811440287145E-2</v>
       </c>
       <c r="P202" s="1">
         <v>201</v>
@@ -4183,7 +4177,7 @@
     <row r="203" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O203">
         <f t="shared" ca="1" si="33"/>
-        <v>0.84835050469506468</v>
+        <v>0.5541104449263351</v>
       </c>
       <c r="P203" s="1">
         <v>202</v>
@@ -4192,7 +4186,7 @@
     <row r="204" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O204">
         <f t="shared" ca="1" si="33"/>
-        <v>6.1949787275221713E-2</v>
+        <v>0.54752520759915524</v>
       </c>
       <c r="P204" s="1">
         <v>203</v>
@@ -4201,7 +4195,7 @@
     <row r="205" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O205">
         <f t="shared" ca="1" si="33"/>
-        <v>0.51926425677058929</v>
+        <v>0.70408330901745919</v>
       </c>
       <c r="P205" s="1">
         <v>204</v>
@@ -4210,7 +4204,7 @@
     <row r="206" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O206">
         <f t="shared" ca="1" si="33"/>
-        <v>0.45740207081125361</v>
+        <v>0.5422459616653269</v>
       </c>
       <c r="P206" s="1">
         <v>205</v>
@@ -4219,7 +4213,7 @@
     <row r="207" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O207">
         <f t="shared" ca="1" si="33"/>
-        <v>0.29277343059472505</v>
+        <v>0.67471909239351202</v>
       </c>
       <c r="P207" s="1">
         <v>206</v>
@@ -4228,7 +4222,7 @@
     <row r="208" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O208">
         <f t="shared" ca="1" si="33"/>
-        <v>5.9444428281968942E-2</v>
+        <v>0.6936059324469378</v>
       </c>
       <c r="P208" s="1">
         <v>207</v>
@@ -4237,7 +4231,7 @@
     <row r="209" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O209">
         <f t="shared" ca="1" si="33"/>
-        <v>0.26822387151998994</v>
+        <v>0.11395477510117769</v>
       </c>
       <c r="P209" s="1">
         <v>208</v>
@@ -4246,7 +4240,7 @@
     <row r="210" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O210">
         <f t="shared" ca="1" si="33"/>
-        <v>0.92919533711423996</v>
+        <v>2.7822872982861568E-2</v>
       </c>
       <c r="P210" s="1">
         <v>209</v>
@@ -4255,7 +4249,7 @@
     <row r="211" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O211">
         <f t="shared" ca="1" si="33"/>
-        <v>0.56699365043089933</v>
+        <v>5.6017526269500406E-2</v>
       </c>
       <c r="P211" s="1">
         <v>210</v>
@@ -4264,7 +4258,7 @@
     <row r="212" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O212">
         <f t="shared" ca="1" si="33"/>
-        <v>0.62225103718860098</v>
+        <v>0.46038293867894398</v>
       </c>
       <c r="P212" s="1">
         <v>211</v>
@@ -4273,7 +4267,7 @@
     <row r="213" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O213">
         <f t="shared" ca="1" si="33"/>
-        <v>0.70040619839778429</v>
+        <v>0.56336210147927013</v>
       </c>
       <c r="P213" s="1">
         <v>212</v>
@@ -4282,7 +4276,7 @@
     <row r="214" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O214">
         <f t="shared" ca="1" si="33"/>
-        <v>0.93416932205974712</v>
+        <v>3.4235637810398623E-2</v>
       </c>
       <c r="P214" s="1">
         <v>213</v>
@@ -4291,7 +4285,7 @@
     <row r="215" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O215">
         <f t="shared" ca="1" si="33"/>
-        <v>0.29767583571706757</v>
+        <v>0.24826363886105718</v>
       </c>
       <c r="P215" s="1">
         <v>214</v>
@@ -4300,7 +4294,7 @@
     <row r="216" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O216">
         <f t="shared" ca="1" si="33"/>
-        <v>3.6456132735434355E-2</v>
+        <v>0.32029670838082169</v>
       </c>
       <c r="P216" s="1">
         <v>215</v>
@@ -4309,7 +4303,7 @@
     <row r="217" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O217">
         <f t="shared" ca="1" si="33"/>
-        <v>0.57724486547908849</v>
+        <v>4.3547637558527419E-2</v>
       </c>
       <c r="P217" s="1">
         <v>216</v>
@@ -4318,7 +4312,7 @@
     <row r="218" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O218">
         <f t="shared" ca="1" si="33"/>
-        <v>0.11366185476222712</v>
+        <v>9.1307333828923642E-2</v>
       </c>
       <c r="P218" s="1">
         <v>217</v>
@@ -4327,7 +4321,7 @@
     <row r="219" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O219">
         <f t="shared" ca="1" si="33"/>
-        <v>0.96226551434339669</v>
+        <v>0.25789844455359312</v>
       </c>
       <c r="P219" s="1">
         <v>218</v>
@@ -4336,7 +4330,7 @@
     <row r="220" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O220">
         <f t="shared" ca="1" si="33"/>
-        <v>5.6711937564035586E-2</v>
+        <v>0.4508464678484807</v>
       </c>
       <c r="P220" s="1">
         <v>219</v>
@@ -4345,7 +4339,7 @@
     <row r="221" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O221">
         <f t="shared" ca="1" si="33"/>
-        <v>0.8479141676931522</v>
+        <v>0.11806626885808269</v>
       </c>
       <c r="P221" s="1">
         <v>220</v>
@@ -4354,7 +4348,7 @@
     <row r="222" spans="15:16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="O222">
         <f t="shared" ca="1" si="33"/>
-        <v>0.90983261464045517</v>
+        <v>0.15192992659361249</v>
       </c>
       <c r="P222" s="1">
         <v>221</v>
@@ -4362,7 +4356,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="V1:AH17">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="notEqual">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="notEqual">
       <formula>" "</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4541,7 +4535,7 @@
       </c>
       <c r="O2">
         <f ca="1">RAND()+Q2-1</f>
-        <v>0.70661561804824635</v>
+        <v>0.88408536435606311</v>
       </c>
       <c r="P2" s="1">
         <v>1</v>
@@ -4551,15 +4545,15 @@
       </c>
       <c r="S2" s="1">
         <f ca="1">SMALL($O$2:$O$98,ROW(S1))</f>
-        <v>1.8104560211276155E-3</v>
+        <v>6.5274171805507208E-3</v>
       </c>
       <c r="T2">
         <f ca="1">VLOOKUP(S2,O$2:P$222,2,0)</f>
-        <v>132</v>
-      </c>
-      <c r="W2" s="3" t="str">
+        <v>107</v>
+      </c>
+      <c r="W2" s="3">
         <f t="shared" ref="W2:W17" ca="1" si="2">IF(ISNUMBER(MATCH(A2,$T$2:$T$13,0)),A2," ")</f>
-        <v xml:space="preserve"> </v>
+        <v>14</v>
       </c>
       <c r="X2" s="3" t="str">
         <f t="shared" ref="X2:X17" ca="1" si="3">IF(ISNUMBER(MATCH(B2,$T$2:$T$13,0)),B2," ")</f>
@@ -4665,7 +4659,7 @@
       </c>
       <c r="O3">
         <f t="shared" ref="O3:O66" ca="1" si="16">RAND()+Q3-1</f>
-        <v>0.66613182857729303</v>
+        <v>0.56518754682955885</v>
       </c>
       <c r="P3" s="1">
         <v>2</v>
@@ -4675,23 +4669,23 @@
       </c>
       <c r="S3" s="1">
         <f t="shared" ref="S3:S5" ca="1" si="17">SMALL($O$2:$O$98,ROW(S2))</f>
-        <v>9.2462136276438844E-3</v>
+        <v>2.7658956321535033E-2</v>
       </c>
       <c r="T3">
         <f t="shared" ref="T3:T13" ca="1" si="18">VLOOKUP(S3,O$2:P$222,2,0)</f>
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="W3" s="3" t="str">
         <f t="shared" ca="1" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="X3" s="3">
+      <c r="X3" s="3" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>28</v>
-      </c>
-      <c r="Y3" s="3">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="Y3" s="3" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>29</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="Z3" s="3" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -4789,7 +4783,7 @@
       </c>
       <c r="O4">
         <f t="shared" ca="1" si="16"/>
-        <v>0.88900533642096713</v>
+        <v>0.42222789541176842</v>
       </c>
       <c r="P4" s="1">
         <v>3</v>
@@ -4799,11 +4793,11 @@
       </c>
       <c r="S4" s="1">
         <f t="shared" ca="1" si="17"/>
-        <v>9.8450800144562756E-3</v>
+        <v>2.9917115535596395E-2</v>
       </c>
       <c r="T4">
         <f t="shared" ca="1" si="18"/>
-        <v>55</v>
+        <v>132</v>
       </c>
       <c r="W4" s="3" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4837,9 +4831,9 @@
         <f t="shared" ca="1" si="9"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="AE4" s="4">
+      <c r="AE4" s="4" t="str">
         <f t="shared" ca="1" si="10"/>
-        <v>48</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="AF4" s="4" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -4913,7 +4907,7 @@
       </c>
       <c r="O5">
         <f t="shared" ca="1" si="16"/>
-        <v>0.19426679070990271</v>
+        <v>0.29643236813080742</v>
       </c>
       <c r="P5" s="1">
         <v>4</v>
@@ -4923,11 +4917,11 @@
       </c>
       <c r="S5" s="1">
         <f t="shared" ca="1" si="17"/>
-        <v>2.65951674308047E-2</v>
+        <v>3.1516549393512783E-2</v>
       </c>
       <c r="T5">
         <f t="shared" ca="1" si="18"/>
-        <v>28</v>
+        <v>170</v>
       </c>
       <c r="W5" s="3" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4937,9 +4931,9 @@
         <f t="shared" ca="1" si="3"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="Y5" s="3">
+      <c r="Y5" s="3" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>55</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="Z5" s="3" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5037,7 +5031,7 @@
       </c>
       <c r="O6">
         <f t="shared" ca="1" si="16"/>
-        <v>0.90579152326301071</v>
+        <v>0.88436926051951859</v>
       </c>
       <c r="P6" s="1">
         <v>5</v>
@@ -5077,9 +5071,9 @@
         <f t="shared" ca="1" si="9"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="AE6" s="4" t="str">
+      <c r="AE6" s="4">
         <f t="shared" ca="1" si="10"/>
-        <v xml:space="preserve"> </v>
+        <v>74</v>
       </c>
       <c r="AF6" s="4" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -5153,7 +5147,7 @@
       </c>
       <c r="O7">
         <f t="shared" ca="1" si="16"/>
-        <v>0.35738493734063748</v>
+        <v>0.13799011475125811</v>
       </c>
       <c r="P7" s="1">
         <v>6</v>
@@ -5163,11 +5157,11 @@
       </c>
       <c r="S7" s="1">
         <f ca="1">SMALL($O$99:$O$165,ROW(S1))</f>
-        <v>1.0282975161509644</v>
+        <v>1.001815456474938</v>
       </c>
       <c r="T7">
         <f t="shared" ca="1" si="18"/>
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="W7" s="3" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -5193,9 +5187,9 @@
         <f t="shared" ca="1" si="7"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="AC7" s="4" t="str">
+      <c r="AC7" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v xml:space="preserve"> </v>
+        <v>85</v>
       </c>
       <c r="AD7" s="4" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -5277,7 +5271,7 @@
       </c>
       <c r="O8">
         <f t="shared" ca="1" si="16"/>
-        <v>0.31019268482105611</v>
+        <v>0.95478077181875554</v>
       </c>
       <c r="P8" s="1">
         <v>7</v>
@@ -5287,11 +5281,11 @@
       </c>
       <c r="S8" s="1">
         <f t="shared" ref="S8:S9" ca="1" si="19">SMALL($O$99:$O$165,ROW(S2))</f>
-        <v>1.0337386028857027</v>
+        <v>1.0176788967399544</v>
       </c>
       <c r="T8">
         <f t="shared" ca="1" si="18"/>
-        <v>115</v>
+        <v>74</v>
       </c>
       <c r="W8" s="3" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -5401,7 +5395,7 @@
       </c>
       <c r="O9">
         <f t="shared" ca="1" si="16"/>
-        <v>3.5072532324097239E-2</v>
+        <v>0.24280257685157847</v>
       </c>
       <c r="P9" s="1">
         <v>8</v>
@@ -5411,11 +5405,11 @@
       </c>
       <c r="S9" s="1">
         <f t="shared" ca="1" si="19"/>
-        <v>1.0364116818047995</v>
+        <v>1.0423011160256248</v>
       </c>
       <c r="T9">
         <f t="shared" ca="1" si="18"/>
-        <v>48</v>
+        <v>85</v>
       </c>
       <c r="W9" s="3" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -5425,9 +5419,9 @@
         <f t="shared" ca="1" si="3"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="Y9" s="3" t="str">
+      <c r="Y9" s="3">
         <f t="shared" ca="1" si="4"/>
-        <v xml:space="preserve"> </v>
+        <v>107</v>
       </c>
       <c r="Z9" s="4" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5441,9 +5435,9 @@
         <f t="shared" ca="1" si="7"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="AC9" s="4" t="str">
+      <c r="AC9" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v xml:space="preserve"> </v>
+        <v>111</v>
       </c>
       <c r="AD9" s="4" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -5457,9 +5451,9 @@
         <f t="shared" ca="1" si="11"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="AG9" s="4">
+      <c r="AG9" s="4" t="str">
         <f t="shared" ca="1" si="12"/>
-        <v>115</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="AH9" s="4" t="str">
         <f t="shared" ca="1" si="13"/>
@@ -5525,7 +5519,7 @@
       </c>
       <c r="O10">
         <f t="shared" ca="1" si="16"/>
-        <v>0.67948801189331309</v>
+        <v>0.68698736679593808</v>
       </c>
       <c r="P10" s="1">
         <v>9</v>
@@ -5549,9 +5543,9 @@
         <f t="shared" ca="1" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="AA10" s="4">
+      <c r="AA10" s="4" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>122</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="AB10" s="4" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -5561,17 +5555,17 @@
         <f t="shared" ca="1" si="8"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="AD10" s="2" t="str">
+      <c r="AD10" s="2">
         <f t="shared" ca="1" si="9"/>
-        <v xml:space="preserve"> </v>
+        <v>125</v>
       </c>
       <c r="AE10" s="2" t="str">
         <f t="shared" ca="1" si="10"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="AF10" s="2">
+      <c r="AF10" s="2" t="str">
         <f t="shared" ca="1" si="11"/>
-        <v>127</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="AG10" s="2" t="str">
         <f t="shared" ca="1" si="12"/>
@@ -5641,7 +5635,7 @@
       </c>
       <c r="O11">
         <f t="shared" ca="1" si="16"/>
-        <v>0.66848010648665124</v>
+        <v>0.60088872447420583</v>
       </c>
       <c r="P11" s="1">
         <v>10</v>
@@ -5651,11 +5645,11 @@
       </c>
       <c r="S11" s="1">
         <f ca="1">SMALL($O$166:$O$222,ROW(S1))</f>
-        <v>2.0035863748764622</v>
+        <v>2.0262333452817329</v>
       </c>
       <c r="T11">
         <f t="shared" ca="1" si="18"/>
-        <v>150</v>
+        <v>204</v>
       </c>
       <c r="W11" s="3" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -5765,7 +5759,7 @@
       </c>
       <c r="O12">
         <f t="shared" ca="1" si="16"/>
-        <v>0.80534536879258267</v>
+        <v>2.7658956321535033E-2</v>
       </c>
       <c r="P12" s="1">
         <v>14</v>
@@ -5775,11 +5769,11 @@
       </c>
       <c r="S12" s="1">
         <f t="shared" ref="S12:S13" ca="1" si="20">SMALL($O$166:$O$222,ROW(S2))</f>
-        <v>2.0051640064158267</v>
+        <v>2.0763933840089672</v>
       </c>
       <c r="T12">
         <f t="shared" ca="1" si="18"/>
-        <v>162</v>
+        <v>180</v>
       </c>
       <c r="W12" s="3" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -5805,9 +5799,9 @@
         <f t="shared" ca="1" si="7"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="AC12" s="2">
+      <c r="AC12" s="2" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>150</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="AD12" s="2" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -5889,7 +5883,7 @@
       </c>
       <c r="O13">
         <f t="shared" ca="1" si="16"/>
-        <v>0.98080433451040294</v>
+        <v>0.91314781662239053</v>
       </c>
       <c r="P13" s="1">
         <v>15</v>
@@ -5899,11 +5893,11 @@
       </c>
       <c r="S13" s="1">
         <f t="shared" ca="1" si="20"/>
-        <v>2.0451219544345527</v>
+        <v>2.082705020186955</v>
       </c>
       <c r="T13">
         <f t="shared" ca="1" si="18"/>
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="W13" s="3" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -5925,9 +5919,9 @@
         <f t="shared" ca="1" si="6"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="AB13" s="2">
+      <c r="AB13" s="2" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>162</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="AC13" s="2" t="str">
         <f t="shared" ca="1" si="8"/>
@@ -6013,7 +6007,7 @@
       </c>
       <c r="O14">
         <f t="shared" ca="1" si="16"/>
-        <v>0.99105427683577929</v>
+        <v>0.6893228812970138</v>
       </c>
       <c r="P14" s="1">
         <v>16</v>
@@ -6021,9 +6015,9 @@
       <c r="Q14" s="1">
         <v>1</v>
       </c>
-      <c r="W14" s="3" t="str">
+      <c r="W14" s="3">
         <f t="shared" ca="1" si="2"/>
-        <v xml:space="preserve"> </v>
+        <v>170</v>
       </c>
       <c r="X14" s="3" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -6061,9 +6055,9 @@
         <f t="shared" ca="1" si="11"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="AG14" s="2" t="str">
+      <c r="AG14" s="2">
         <f t="shared" ca="1" si="12"/>
-        <v xml:space="preserve"> </v>
+        <v>180</v>
       </c>
       <c r="AH14" s="2" t="str">
         <f t="shared" ca="1" si="13"/>
@@ -6129,7 +6123,7 @@
       </c>
       <c r="O15">
         <f t="shared" ca="1" si="16"/>
-        <v>0.41633572348529668</v>
+        <v>5.6073216803891768E-2</v>
       </c>
       <c r="P15" s="1">
         <v>17</v>
@@ -6245,7 +6239,7 @@
       </c>
       <c r="O16">
         <f t="shared" ca="1" si="16"/>
-        <v>0.25494546541157881</v>
+        <v>0.56732444315322805</v>
       </c>
       <c r="P16" s="1">
         <v>18</v>
@@ -6285,9 +6279,9 @@
         <f t="shared" ca="1" si="9"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="AE16" s="2" t="str">
+      <c r="AE16" s="2">
         <f t="shared" ca="1" si="10"/>
-        <v xml:space="preserve"> </v>
+        <v>204</v>
       </c>
       <c r="AF16" s="2" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -6361,7 +6355,7 @@
       </c>
       <c r="O17">
         <f t="shared" ca="1" si="16"/>
-        <v>0.57488383472423177</v>
+        <v>0.36552106437358867</v>
       </c>
       <c r="P17" s="1">
         <v>19</v>
@@ -6425,7 +6419,7 @@
     <row r="18" spans="1:35" x14ac:dyDescent="0.25">
       <c r="O18">
         <f t="shared" ca="1" si="16"/>
-        <v>0.35152353120206903</v>
+        <v>0.94900329860845201</v>
       </c>
       <c r="P18" s="1">
         <v>20</v>
@@ -6437,7 +6431,7 @@
     <row r="19" spans="1:35" x14ac:dyDescent="0.25">
       <c r="O19">
         <f t="shared" ca="1" si="16"/>
-        <v>0.49553129263636175</v>
+        <v>0.38475147300637169</v>
       </c>
       <c r="P19" s="1">
         <v>21</v>
@@ -6449,7 +6443,7 @@
     <row r="20" spans="1:35" x14ac:dyDescent="0.25">
       <c r="O20">
         <f t="shared" ca="1" si="16"/>
-        <v>0.89012964952931917</v>
+        <v>0.25473373920174303</v>
       </c>
       <c r="P20" s="1">
         <v>22</v>
@@ -6461,7 +6455,7 @@
     <row r="21" spans="1:35" x14ac:dyDescent="0.25">
       <c r="O21">
         <f t="shared" ca="1" si="16"/>
-        <v>7.940302147731515E-2</v>
+        <v>0.93378515398222506</v>
       </c>
       <c r="P21" s="1">
         <v>23</v>
@@ -6473,7 +6467,7 @@
     <row r="22" spans="1:35" x14ac:dyDescent="0.25">
       <c r="O22">
         <f t="shared" ca="1" si="16"/>
-        <v>0.44071433118763226</v>
+        <v>0.52236453852893439</v>
       </c>
       <c r="P22" s="1">
         <v>27</v>
@@ -6485,7 +6479,7 @@
     <row r="23" spans="1:35" x14ac:dyDescent="0.25">
       <c r="O23">
         <f t="shared" ca="1" si="16"/>
-        <v>2.65951674308047E-2</v>
+        <v>0.42925747969103067</v>
       </c>
       <c r="P23" s="1">
         <v>28</v>
@@ -6497,7 +6491,7 @@
     <row r="24" spans="1:35" x14ac:dyDescent="0.25">
       <c r="O24">
         <f t="shared" ca="1" si="16"/>
-        <v>9.2462136276438844E-3</v>
+        <v>0.87307613644217019</v>
       </c>
       <c r="P24" s="1">
         <v>29</v>
@@ -6509,7 +6503,7 @@
     <row r="25" spans="1:35" x14ac:dyDescent="0.25">
       <c r="O25">
         <f t="shared" ca="1" si="16"/>
-        <v>0.64136126004207306</v>
+        <v>0.75868488270994527</v>
       </c>
       <c r="P25" s="1">
         <v>30</v>
@@ -6521,7 +6515,7 @@
     <row r="26" spans="1:35" x14ac:dyDescent="0.25">
       <c r="O26">
         <f t="shared" ca="1" si="16"/>
-        <v>0.35487937371985678</v>
+        <v>0.4285392282643985</v>
       </c>
       <c r="P26" s="1">
         <v>31</v>
@@ -6533,7 +6527,7 @@
     <row r="27" spans="1:35" x14ac:dyDescent="0.25">
       <c r="O27">
         <f t="shared" ca="1" si="16"/>
-        <v>0.19158553260641531</v>
+        <v>0.4383675843070387</v>
       </c>
       <c r="P27" s="1">
         <v>32</v>
@@ -6545,7 +6539,7 @@
     <row r="28" spans="1:35" x14ac:dyDescent="0.25">
       <c r="O28">
         <f t="shared" ca="1" si="16"/>
-        <v>0.25318950848080313</v>
+        <v>4.6410043088259689E-2</v>
       </c>
       <c r="P28" s="1">
         <v>33</v>
@@ -6557,7 +6551,7 @@
     <row r="29" spans="1:35" x14ac:dyDescent="0.25">
       <c r="O29">
         <f t="shared" ca="1" si="16"/>
-        <v>0.566848489086347</v>
+        <v>0.54001755148117159</v>
       </c>
       <c r="P29" s="1">
         <v>34</v>
@@ -6569,7 +6563,7 @@
     <row r="30" spans="1:35" x14ac:dyDescent="0.25">
       <c r="O30">
         <f t="shared" ca="1" si="16"/>
-        <v>0.41900819200952322</v>
+        <v>0.11800373268438924</v>
       </c>
       <c r="P30" s="1">
         <v>35</v>
@@ -6581,7 +6575,7 @@
     <row r="31" spans="1:35" x14ac:dyDescent="0.25">
       <c r="O31">
         <f t="shared" ca="1" si="16"/>
-        <v>0.22392565973468193</v>
+        <v>0.53430770436475528</v>
       </c>
       <c r="P31" s="1">
         <v>36</v>
@@ -6593,7 +6587,7 @@
     <row r="32" spans="1:35" x14ac:dyDescent="0.25">
       <c r="O32">
         <f t="shared" ca="1" si="16"/>
-        <v>0.67733897500504003</v>
+        <v>0.41911171772937772</v>
       </c>
       <c r="P32" s="1">
         <v>40</v>
@@ -6605,7 +6599,7 @@
     <row r="33" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O33">
         <f t="shared" ca="1" si="16"/>
-        <v>0.25578096126918437</v>
+        <v>0.20056495573584288</v>
       </c>
       <c r="P33" s="1">
         <v>41</v>
@@ -6617,7 +6611,7 @@
     <row r="34" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O34">
         <f t="shared" ca="1" si="16"/>
-        <v>0.61086774940585897</v>
+        <v>0.72054214934528127</v>
       </c>
       <c r="P34" s="1">
         <v>42</v>
@@ -6629,7 +6623,7 @@
     <row r="35" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O35">
         <f t="shared" ca="1" si="16"/>
-        <v>0.60199293957647093</v>
+        <v>0.37264676179678791</v>
       </c>
       <c r="P35" s="1">
         <v>43</v>
@@ -6641,7 +6635,7 @@
     <row r="36" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O36">
         <f t="shared" ca="1" si="16"/>
-        <v>0.80273518874798433</v>
+        <v>0.40145141561536124</v>
       </c>
       <c r="P36" s="1">
         <v>44</v>
@@ -6653,7 +6647,7 @@
     <row r="37" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O37">
         <f t="shared" ca="1" si="16"/>
-        <v>0.25896135543046062</v>
+        <v>5.2080170005346815E-2</v>
       </c>
       <c r="P37" s="1">
         <v>45</v>
@@ -6665,7 +6659,7 @@
     <row r="38" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O38">
         <f t="shared" ca="1" si="16"/>
-        <v>0.3080171192421024</v>
+        <v>0.61190080268719127</v>
       </c>
       <c r="P38" s="1">
         <v>53</v>
@@ -6677,7 +6671,7 @@
     <row r="39" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O39">
         <f t="shared" ca="1" si="16"/>
-        <v>3.7626490271922552E-2</v>
+        <v>0.55820651510291719</v>
       </c>
       <c r="P39" s="1">
         <v>54</v>
@@ -6689,7 +6683,7 @@
     <row r="40" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O40">
         <f t="shared" ca="1" si="16"/>
-        <v>9.8450800144562756E-3</v>
+        <v>0.18249565692114622</v>
       </c>
       <c r="P40" s="1">
         <v>55</v>
@@ -6701,7 +6695,7 @@
     <row r="41" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O41">
         <f t="shared" ca="1" si="16"/>
-        <v>8.4423758698035201E-2</v>
+        <v>0.37778443928647376</v>
       </c>
       <c r="P41" s="1">
         <v>56</v>
@@ -6713,7 +6707,7 @@
     <row r="42" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O42">
         <f t="shared" ca="1" si="16"/>
-        <v>0.38211139433740815</v>
+        <v>0.87473953059351017</v>
       </c>
       <c r="P42" s="1">
         <v>57</v>
@@ -6725,7 +6719,7 @@
     <row r="43" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O43">
         <f t="shared" ca="1" si="16"/>
-        <v>0.5276434350633028</v>
+        <v>0.32892881911507588</v>
       </c>
       <c r="P43" s="1">
         <v>58</v>
@@ -6737,7 +6731,7 @@
     <row r="44" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O44">
         <f t="shared" ca="1" si="16"/>
-        <v>0.89028373085397816</v>
+        <v>0.79083658894759479</v>
       </c>
       <c r="P44" s="1">
         <v>66</v>
@@ -6749,7 +6743,7 @@
     <row r="45" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O45">
         <f t="shared" ca="1" si="16"/>
-        <v>0.57950284345104874</v>
+        <v>0.71317138498115096</v>
       </c>
       <c r="P45" s="1">
         <v>67</v>
@@ -6761,7 +6755,7 @@
     <row r="46" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O46">
         <f t="shared" ca="1" si="16"/>
-        <v>0.52803310394443104</v>
+        <v>0.8478103013717404</v>
       </c>
       <c r="P46" s="1">
         <v>68</v>
@@ -6773,7 +6767,7 @@
     <row r="47" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O47">
         <f t="shared" ca="1" si="16"/>
-        <v>0.28898544951846872</v>
+        <v>0.2695699502898683</v>
       </c>
       <c r="P47" s="1">
         <v>69</v>
@@ -6785,7 +6779,7 @@
     <row r="48" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O48">
         <f t="shared" ca="1" si="16"/>
-        <v>0.73090959491613372</v>
+        <v>0.81214177792866571</v>
       </c>
       <c r="P48" s="1">
         <v>70</v>
@@ -6797,7 +6791,7 @@
     <row r="49" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O49">
         <f t="shared" ca="1" si="16"/>
-        <v>0.87610573860335839</v>
+        <v>0.64979416681476287</v>
       </c>
       <c r="P49" s="1">
         <v>71</v>
@@ -6809,7 +6803,7 @@
     <row r="50" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O50">
         <f t="shared" ca="1" si="16"/>
-        <v>0.80492267402790341</v>
+        <v>0.49013649555891292</v>
       </c>
       <c r="P50" s="1">
         <v>79</v>
@@ -6821,7 +6815,7 @@
     <row r="51" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O51">
         <f t="shared" ca="1" si="16"/>
-        <v>0.24451907312305021</v>
+        <v>0.20578861264418058</v>
       </c>
       <c r="P51" s="1">
         <v>80</v>
@@ -6833,7 +6827,7 @@
     <row r="52" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O52">
         <f t="shared" ca="1" si="16"/>
-        <v>0.35234866330813186</v>
+        <v>4.560130838167753E-2</v>
       </c>
       <c r="P52" s="1">
         <v>81</v>
@@ -6845,7 +6839,7 @@
     <row r="53" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O53">
         <f t="shared" ca="1" si="16"/>
-        <v>0.66281703870446584</v>
+        <v>0.24059167456155217</v>
       </c>
       <c r="P53" s="1">
         <v>82</v>
@@ -6857,7 +6851,7 @@
     <row r="54" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O54">
         <f t="shared" ca="1" si="16"/>
-        <v>0.77916915066249759</v>
+        <v>0.59683139226730031</v>
       </c>
       <c r="P54" s="1">
         <v>83</v>
@@ -6869,7 +6863,7 @@
     <row r="55" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O55">
         <f t="shared" ca="1" si="16"/>
-        <v>0.46701535927808235</v>
+        <v>0.82909133811429592</v>
       </c>
       <c r="P55" s="1">
         <v>84</v>
@@ -6881,7 +6875,7 @@
     <row r="56" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O56">
         <f t="shared" ca="1" si="16"/>
-        <v>0.95170743321131157</v>
+        <v>0.55879608084812382</v>
       </c>
       <c r="P56" s="1">
         <v>92</v>
@@ -6893,7 +6887,7 @@
     <row r="57" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O57">
         <f t="shared" ca="1" si="16"/>
-        <v>0.92871826631246046</v>
+        <v>0.96349066773801351</v>
       </c>
       <c r="P57" s="1">
         <v>93</v>
@@ -6905,7 +6899,7 @@
     <row r="58" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O58">
         <f t="shared" ca="1" si="16"/>
-        <v>0.44957255588532519</v>
+        <v>0.24648711725059802</v>
       </c>
       <c r="P58" s="1">
         <v>94</v>
@@ -6917,7 +6911,7 @@
     <row r="59" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O59">
         <f t="shared" ca="1" si="16"/>
-        <v>5.0810597016182957E-2</v>
+        <v>0.62445099800662041</v>
       </c>
       <c r="P59" s="1">
         <v>105</v>
@@ -6929,7 +6923,7 @@
     <row r="60" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O60">
         <f t="shared" ca="1" si="16"/>
-        <v>0.10407822390821897</v>
+        <v>0.81449760694680728</v>
       </c>
       <c r="P60" s="1">
         <v>106</v>
@@ -6941,7 +6935,7 @@
     <row r="61" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O61">
         <f t="shared" ca="1" si="16"/>
-        <v>0.69325195329346645</v>
+        <v>6.5274171805507208E-3</v>
       </c>
       <c r="P61" s="1">
         <v>107</v>
@@ -6953,7 +6947,7 @@
     <row r="62" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O62">
         <f t="shared" ca="1" si="16"/>
-        <v>0.71308314454489397</v>
+        <v>0.37425029683171163</v>
       </c>
       <c r="P62" s="1">
         <v>118</v>
@@ -6965,7 +6959,7 @@
     <row r="63" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O63">
         <f t="shared" ca="1" si="16"/>
-        <v>0.63980282147290013</v>
+        <v>0.57348068227071725</v>
       </c>
       <c r="P63" s="1">
         <v>119</v>
@@ -6977,7 +6971,7 @@
     <row r="64" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O64">
         <f t="shared" ca="1" si="16"/>
-        <v>0.49721298764043809</v>
+        <v>0.82415424983614649</v>
       </c>
       <c r="P64" s="1">
         <v>120</v>
@@ -6989,7 +6983,7 @@
     <row r="65" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O65">
         <f t="shared" ca="1" si="16"/>
-        <v>0.59727505671690562</v>
+        <v>0.82961011282720087</v>
       </c>
       <c r="P65" s="1">
         <v>131</v>
@@ -7001,7 +6995,7 @@
     <row r="66" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O66">
         <f t="shared" ca="1" si="16"/>
-        <v>1.8104560211276155E-3</v>
+        <v>2.9917115535596395E-2</v>
       </c>
       <c r="P66" s="1">
         <v>132</v>
@@ -7013,7 +7007,7 @@
     <row r="67" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O67">
         <f t="shared" ref="O67:O130" ca="1" si="21">RAND()+Q67-1</f>
-        <v>0.84947665531298444</v>
+        <v>0.28480770447262072</v>
       </c>
       <c r="P67" s="1">
         <v>133</v>
@@ -7025,7 +7019,7 @@
     <row r="68" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O68">
         <f t="shared" ca="1" si="21"/>
-        <v>0.64407509380125161</v>
+        <v>0.34336797076350667</v>
       </c>
       <c r="P68" s="1">
         <v>144</v>
@@ -7037,7 +7031,7 @@
     <row r="69" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O69">
         <f t="shared" ca="1" si="21"/>
-        <v>4.9107292164731753E-2</v>
+        <v>0.78566990298061956</v>
       </c>
       <c r="P69" s="1">
         <v>145</v>
@@ -7049,7 +7043,7 @@
     <row r="70" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O70">
         <f t="shared" ca="1" si="21"/>
-        <v>0.55329794899101992</v>
+        <v>0.40602078970027944</v>
       </c>
       <c r="P70" s="1">
         <v>146</v>
@@ -7061,7 +7055,7 @@
     <row r="71" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O71">
         <f t="shared" ca="1" si="21"/>
-        <v>0.69070212832337763</v>
+        <v>0.26307595114292326</v>
       </c>
       <c r="P71" s="1">
         <v>157</v>
@@ -7073,7 +7067,7 @@
     <row r="72" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O72">
         <f t="shared" ca="1" si="21"/>
-        <v>0.59773455298464229</v>
+        <v>0.79770563509165671</v>
       </c>
       <c r="P72" s="1">
         <v>158</v>
@@ -7085,7 +7079,7 @@
     <row r="73" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O73">
         <f t="shared" ca="1" si="21"/>
-        <v>0.21228756527964299</v>
+        <v>7.4082631896353668E-2</v>
       </c>
       <c r="P73" s="1">
         <v>159</v>
@@ -7097,7 +7091,7 @@
     <row r="74" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O74">
         <f t="shared" ca="1" si="21"/>
-        <v>0.6078022658518778</v>
+        <v>3.1516549393512783E-2</v>
       </c>
       <c r="P74" s="1">
         <v>170</v>
@@ -7109,7 +7103,7 @@
     <row r="75" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O75">
         <f t="shared" ca="1" si="21"/>
-        <v>0.36374682144973991</v>
+        <v>0.44342049188694954</v>
       </c>
       <c r="P75" s="1">
         <v>171</v>
@@ -7121,7 +7115,7 @@
     <row r="76" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O76">
         <f t="shared" ca="1" si="21"/>
-        <v>0.94352576244291386</v>
+        <v>0.13825226336850172</v>
       </c>
       <c r="P76" s="1">
         <v>172</v>
@@ -7133,7 +7127,7 @@
     <row r="77" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O77">
         <f t="shared" ca="1" si="21"/>
-        <v>0.80291962948725892</v>
+        <v>0.65999753887061741</v>
       </c>
       <c r="P77" s="1">
         <v>173</v>
@@ -7145,7 +7139,7 @@
     <row r="78" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O78">
         <f t="shared" ca="1" si="21"/>
-        <v>0.42701699396168369</v>
+        <v>0.90374036316349793</v>
       </c>
       <c r="P78" s="1">
         <v>183</v>
@@ -7157,7 +7151,7 @@
     <row r="79" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O79">
         <f t="shared" ca="1" si="21"/>
-        <v>0.92360286597141683</v>
+        <v>0.71210496757501063</v>
       </c>
       <c r="P79" s="1">
         <v>184</v>
@@ -7169,7 +7163,7 @@
     <row r="80" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O80">
         <f t="shared" ca="1" si="21"/>
-        <v>0.73350046627032461</v>
+        <v>0.71168745453511395</v>
       </c>
       <c r="P80" s="1">
         <v>185</v>
@@ -7181,7 +7175,7 @@
     <row r="81" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O81">
         <f t="shared" ca="1" si="21"/>
-        <v>0.98692115766644739</v>
+        <v>0.62489947769769794</v>
       </c>
       <c r="P81" s="1">
         <v>186</v>
@@ -7193,7 +7187,7 @@
     <row r="82" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O82">
         <f t="shared" ca="1" si="21"/>
-        <v>0.88822633439651355</v>
+        <v>0.22699734196638577</v>
       </c>
       <c r="P82" s="1">
         <v>187</v>
@@ -7205,7 +7199,7 @@
     <row r="83" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O83">
         <f t="shared" ca="1" si="21"/>
-        <v>0.69461857625521972</v>
+        <v>0.72333158254153229</v>
       </c>
       <c r="P83" s="1">
         <v>188</v>
@@ -7217,7 +7211,7 @@
     <row r="84" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O84">
         <f t="shared" ca="1" si="21"/>
-        <v>0.75301507474924723</v>
+        <v>0.34083770796030244</v>
       </c>
       <c r="P84" s="1">
         <v>189</v>
@@ -7229,7 +7223,7 @@
     <row r="85" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O85">
         <f t="shared" ca="1" si="21"/>
-        <v>0.43640896114493755</v>
+        <v>0.27639533388399395</v>
       </c>
       <c r="P85" s="1">
         <v>196</v>
@@ -7241,7 +7235,7 @@
     <row r="86" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O86">
         <f t="shared" ca="1" si="21"/>
-        <v>0.18642515046723007</v>
+        <v>4.3878606781866836E-2</v>
       </c>
       <c r="P86" s="1">
         <v>197</v>
@@ -7253,7 +7247,7 @@
     <row r="87" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O87">
         <f t="shared" ca="1" si="21"/>
-        <v>0.1565098515049228</v>
+        <v>0.91938255588257212</v>
       </c>
       <c r="P87" s="1">
         <v>198</v>
@@ -7265,7 +7259,7 @@
     <row r="88" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O88">
         <f t="shared" ca="1" si="21"/>
-        <v>0.67945331156915012</v>
+        <v>0.52180927076186379</v>
       </c>
       <c r="P88" s="1">
         <v>199</v>
@@ -7277,7 +7271,7 @@
     <row r="89" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O89">
         <f t="shared" ca="1" si="21"/>
-        <v>0.27239964939965278</v>
+        <v>7.1358185130708573E-2</v>
       </c>
       <c r="P89" s="1">
         <v>200</v>
@@ -7289,7 +7283,7 @@
     <row r="90" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O90">
         <f t="shared" ca="1" si="21"/>
-        <v>0.70104231037932752</v>
+        <v>0.56313329832435621</v>
       </c>
       <c r="P90" s="1">
         <v>201</v>
@@ -7301,7 +7295,7 @@
     <row r="91" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O91">
         <f t="shared" ca="1" si="21"/>
-        <v>0.80265544059482918</v>
+        <v>0.28530624958316331</v>
       </c>
       <c r="P91" s="1">
         <v>202</v>
@@ -7313,7 +7307,7 @@
     <row r="92" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O92">
         <f t="shared" ca="1" si="21"/>
-        <v>0.14542478167282269</v>
+        <v>0.67699045703578542</v>
       </c>
       <c r="P92" s="1">
         <v>209</v>
@@ -7325,7 +7319,7 @@
     <row r="93" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O93">
         <f t="shared" ca="1" si="21"/>
-        <v>0.95422235850352255</v>
+        <v>0.31788508788920877</v>
       </c>
       <c r="P93" s="1">
         <v>210</v>
@@ -7337,7 +7331,7 @@
     <row r="94" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O94">
         <f t="shared" ca="1" si="21"/>
-        <v>0.31502148588586287</v>
+        <v>0.35643316456955443</v>
       </c>
       <c r="P94" s="1">
         <v>211</v>
@@ -7349,7 +7343,7 @@
     <row r="95" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O95">
         <f t="shared" ca="1" si="21"/>
-        <v>0.24527061838256792</v>
+        <v>0.4820948475390443</v>
       </c>
       <c r="P95" s="1">
         <v>212</v>
@@ -7361,7 +7355,7 @@
     <row r="96" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O96">
         <f t="shared" ca="1" si="21"/>
-        <v>0.35225017668555214</v>
+        <v>0.47110433463715617</v>
       </c>
       <c r="P96" s="1">
         <v>213</v>
@@ -7373,7 +7367,7 @@
     <row r="97" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O97">
         <f t="shared" ca="1" si="21"/>
-        <v>0.2979597341318867</v>
+        <v>0.88997463219094408</v>
       </c>
       <c r="P97" s="1">
         <v>214</v>
@@ -7385,7 +7379,7 @@
     <row r="98" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O98">
         <f t="shared" ca="1" si="21"/>
-        <v>0.54847389707238969</v>
+        <v>0.10836456497725111</v>
       </c>
       <c r="P98" s="1">
         <v>215</v>
@@ -7397,7 +7391,7 @@
     <row r="99" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O99">
         <f t="shared" ca="1" si="21"/>
-        <v>1.2585297617521407</v>
+        <v>1.9403237909510738</v>
       </c>
       <c r="P99" s="1">
         <v>11</v>
@@ -7409,7 +7403,7 @@
     <row r="100" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O100">
         <f t="shared" ca="1" si="21"/>
-        <v>1.6363983916083455</v>
+        <v>1.3956358581241277</v>
       </c>
       <c r="P100" s="1">
         <v>12</v>
@@ -7421,7 +7415,7 @@
     <row r="101" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O101">
         <f t="shared" ca="1" si="21"/>
-        <v>1.1812661961459936</v>
+        <v>1.580787744381821</v>
       </c>
       <c r="P101" s="1">
         <v>13</v>
@@ -7433,7 +7427,7 @@
     <row r="102" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O102">
         <f t="shared" ca="1" si="21"/>
-        <v>1.3910786005248337</v>
+        <v>1.2594624889067627</v>
       </c>
       <c r="P102" s="1">
         <v>24</v>
@@ -7445,7 +7439,7 @@
     <row r="103" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O103">
         <f t="shared" ca="1" si="21"/>
-        <v>1.2077592177944787</v>
+        <v>1.8480844855317526</v>
       </c>
       <c r="P103" s="1">
         <v>25</v>
@@ -7457,7 +7451,7 @@
     <row r="104" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O104">
         <f t="shared" ca="1" si="21"/>
-        <v>1.2068238342177939</v>
+        <v>1.2867503726127074</v>
       </c>
       <c r="P104" s="1">
         <v>26</v>
@@ -7469,7 +7463,7 @@
     <row r="105" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O105">
         <f t="shared" ca="1" si="21"/>
-        <v>1.6384633430345192</v>
+        <v>1.9036124662362646</v>
       </c>
       <c r="P105" s="1">
         <v>37</v>
@@ -7481,7 +7475,7 @@
     <row r="106" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O106">
         <f t="shared" ca="1" si="21"/>
-        <v>1.7190110131832954</v>
+        <v>1.3643687471782</v>
       </c>
       <c r="P106" s="1">
         <v>38</v>
@@ -7493,7 +7487,7 @@
     <row r="107" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O107">
         <f t="shared" ca="1" si="21"/>
-        <v>1.3731805236336037</v>
+        <v>1.8809271581243534</v>
       </c>
       <c r="P107" s="1">
         <v>39</v>
@@ -7505,7 +7499,7 @@
     <row r="108" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O108">
         <f t="shared" ca="1" si="21"/>
-        <v>1.8608398024382726</v>
+        <v>1.3254888352245677</v>
       </c>
       <c r="P108" s="1">
         <v>46</v>
@@ -7517,7 +7511,7 @@
     <row r="109" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O109">
         <f t="shared" ca="1" si="21"/>
-        <v>1.3155673087004951</v>
+        <v>1.9277918483107452</v>
       </c>
       <c r="P109" s="1">
         <v>47</v>
@@ -7529,7 +7523,7 @@
     <row r="110" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O110">
         <f t="shared" ca="1" si="21"/>
-        <v>1.0364116818047995</v>
+        <v>1.6925170560061433</v>
       </c>
       <c r="P110" s="1">
         <v>48</v>
@@ -7541,7 +7535,7 @@
     <row r="111" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O111">
         <f t="shared" ca="1" si="21"/>
-        <v>1.7180657292667565</v>
+        <v>1.6355385939939646</v>
       </c>
       <c r="P111" s="1">
         <v>49</v>
@@ -7553,7 +7547,7 @@
     <row r="112" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O112">
         <f t="shared" ca="1" si="21"/>
-        <v>1.9509645473745736</v>
+        <v>1.194010522413862</v>
       </c>
       <c r="P112" s="1">
         <v>50</v>
@@ -7565,7 +7559,7 @@
     <row r="113" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O113">
         <f t="shared" ca="1" si="21"/>
-        <v>1.7159799320421758</v>
+        <v>1.8534400614214461</v>
       </c>
       <c r="P113" s="1">
         <v>51</v>
@@ -7577,7 +7571,7 @@
     <row r="114" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O114">
         <f t="shared" ca="1" si="21"/>
-        <v>1.8809216667669544</v>
+        <v>1.098427416858192</v>
       </c>
       <c r="P114" s="1">
         <v>52</v>
@@ -7589,7 +7583,7 @@
     <row r="115" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O115">
         <f t="shared" ca="1" si="21"/>
-        <v>1.0915648492672125</v>
+        <v>1.1644324338990724</v>
       </c>
       <c r="P115" s="1">
         <v>59</v>
@@ -7601,7 +7595,7 @@
     <row r="116" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O116">
         <f t="shared" ca="1" si="21"/>
-        <v>1.5282050835086989</v>
+        <v>1.998562571916104</v>
       </c>
       <c r="P116" s="1">
         <v>60</v>
@@ -7613,7 +7607,7 @@
     <row r="117" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O117">
         <f t="shared" ca="1" si="21"/>
-        <v>1.1424864700765518</v>
+        <v>1.3903358490391353</v>
       </c>
       <c r="P117" s="1">
         <v>61</v>
@@ -7625,7 +7619,7 @@
     <row r="118" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O118">
         <f t="shared" ca="1" si="21"/>
-        <v>1.5572924803033561</v>
+        <v>1.0660853022388723</v>
       </c>
       <c r="P118" s="1">
         <v>62</v>
@@ -7637,7 +7631,7 @@
     <row r="119" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O119">
         <f t="shared" ca="1" si="21"/>
-        <v>1.3314108293703888</v>
+        <v>1.2910921720011652</v>
       </c>
       <c r="P119" s="1">
         <v>63</v>
@@ -7649,7 +7643,7 @@
     <row r="120" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O120">
         <f t="shared" ca="1" si="21"/>
-        <v>1.4821240292389852</v>
+        <v>1.9216317559489013</v>
       </c>
       <c r="P120" s="1">
         <v>64</v>
@@ -7661,7 +7655,7 @@
     <row r="121" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O121">
         <f t="shared" ca="1" si="21"/>
-        <v>1.8246372488912042</v>
+        <v>1.7369541201488548</v>
       </c>
       <c r="P121" s="1">
         <v>65</v>
@@ -7673,7 +7667,7 @@
     <row r="122" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O122">
         <f t="shared" ca="1" si="21"/>
-        <v>1.4818406953963015</v>
+        <v>1.6199072971912898</v>
       </c>
       <c r="P122" s="1">
         <v>72</v>
@@ -7685,7 +7679,7 @@
     <row r="123" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O123">
         <f t="shared" ca="1" si="21"/>
-        <v>1.8176242648010961</v>
+        <v>1.8549808264686822</v>
       </c>
       <c r="P123" s="1">
         <v>73</v>
@@ -7697,7 +7691,7 @@
     <row r="124" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O124">
         <f t="shared" ca="1" si="21"/>
-        <v>1.2140899859246446</v>
+        <v>1.0176788967399544</v>
       </c>
       <c r="P124" s="1">
         <v>74</v>
@@ -7709,7 +7703,7 @@
     <row r="125" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O125">
         <f t="shared" ca="1" si="21"/>
-        <v>1.5309802672590975</v>
+        <v>1.9355523865939372</v>
       </c>
       <c r="P125" s="1">
         <v>75</v>
@@ -7721,7 +7715,7 @@
     <row r="126" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O126">
         <f t="shared" ca="1" si="21"/>
-        <v>1.8037149238307864</v>
+        <v>1.7527515057417515</v>
       </c>
       <c r="P126" s="1">
         <v>76</v>
@@ -7733,7 +7727,7 @@
     <row r="127" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O127">
         <f t="shared" ca="1" si="21"/>
-        <v>1.790318452959049</v>
+        <v>1.9068314153812347</v>
       </c>
       <c r="P127" s="1">
         <v>77</v>
@@ -7745,7 +7739,7 @@
     <row r="128" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O128">
         <f t="shared" ca="1" si="21"/>
-        <v>1.3963170625976833</v>
+        <v>1.3803531732780137</v>
       </c>
       <c r="P128" s="1">
         <v>78</v>
@@ -7757,7 +7751,7 @@
     <row r="129" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O129">
         <f t="shared" ca="1" si="21"/>
-        <v>1.3427501354840645</v>
+        <v>1.0423011160256248</v>
       </c>
       <c r="P129" s="1">
         <v>85</v>
@@ -7769,7 +7763,7 @@
     <row r="130" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O130">
         <f t="shared" ca="1" si="21"/>
-        <v>1.6448935666569864</v>
+        <v>1.6504942508094045</v>
       </c>
       <c r="P130" s="1">
         <v>86</v>
@@ -7781,7 +7775,7 @@
     <row r="131" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O131">
         <f t="shared" ref="O131:O194" ca="1" si="22">RAND()+Q131-1</f>
-        <v>1.1897816813050004</v>
+        <v>1.4912947001609376</v>
       </c>
       <c r="P131" s="1">
         <v>87</v>
@@ -7793,7 +7787,7 @@
     <row r="132" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O132">
         <f t="shared" ca="1" si="22"/>
-        <v>1.0758465046529055</v>
+        <v>1.426034364761136</v>
       </c>
       <c r="P132" s="1">
         <v>88</v>
@@ -7805,7 +7799,7 @@
     <row r="133" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O133">
         <f t="shared" ca="1" si="22"/>
-        <v>1.4588280294557574</v>
+        <v>1.6678957677215882</v>
       </c>
       <c r="P133" s="1">
         <v>89</v>
@@ -7817,7 +7811,7 @@
     <row r="134" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O134">
         <f t="shared" ca="1" si="22"/>
-        <v>1.0528382741772</v>
+        <v>1.4616032885150609</v>
       </c>
       <c r="P134" s="1">
         <v>90</v>
@@ -7829,7 +7823,7 @@
     <row r="135" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O135">
         <f t="shared" ca="1" si="22"/>
-        <v>1.4396840842748393</v>
+        <v>1.412338725845121</v>
       </c>
       <c r="P135" s="1">
         <v>91</v>
@@ -7841,7 +7835,7 @@
     <row r="136" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O136">
         <f t="shared" ca="1" si="22"/>
-        <v>1.8685548660244633</v>
+        <v>1.8602862498411059</v>
       </c>
       <c r="P136" s="1">
         <v>95</v>
@@ -7853,7 +7847,7 @@
     <row r="137" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O137">
         <f t="shared" ca="1" si="22"/>
-        <v>1.6727284267035523</v>
+        <v>1.1143348460334117</v>
       </c>
       <c r="P137" s="1">
         <v>96</v>
@@ -7865,7 +7859,7 @@
     <row r="138" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O138">
         <f t="shared" ca="1" si="22"/>
-        <v>1.9090171102642071</v>
+        <v>1.7077813811179996</v>
       </c>
       <c r="P138" s="1">
         <v>97</v>
@@ -7877,7 +7871,7 @@
     <row r="139" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O139">
         <f t="shared" ca="1" si="22"/>
-        <v>1.7815679531806126</v>
+        <v>1.3026788595799266</v>
       </c>
       <c r="P139" s="1">
         <v>98</v>
@@ -7889,7 +7883,7 @@
     <row r="140" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O140">
         <f t="shared" ca="1" si="22"/>
-        <v>1.1062891131235673</v>
+        <v>1.8175676485503955</v>
       </c>
       <c r="P140" s="1">
         <v>99</v>
@@ -7901,7 +7895,7 @@
     <row r="141" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O141">
         <f t="shared" ca="1" si="22"/>
-        <v>1.160159861405528</v>
+        <v>1.1332207719159522</v>
       </c>
       <c r="P141" s="1">
         <v>100</v>
@@ -7913,7 +7907,7 @@
     <row r="142" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O142">
         <f t="shared" ca="1" si="22"/>
-        <v>1.1832418227163739</v>
+        <v>1.6421505974696364</v>
       </c>
       <c r="P142" s="1">
         <v>101</v>
@@ -7925,7 +7919,7 @@
     <row r="143" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O143">
         <f t="shared" ca="1" si="22"/>
-        <v>1.2874368359733479</v>
+        <v>1.8653249599145676</v>
       </c>
       <c r="P143" s="1">
         <v>102</v>
@@ -7937,7 +7931,7 @@
     <row r="144" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O144">
         <f t="shared" ca="1" si="22"/>
-        <v>1.4377800819938606</v>
+        <v>1.7443384820497343</v>
       </c>
       <c r="P144" s="1">
         <v>103</v>
@@ -7949,7 +7943,7 @@
     <row r="145" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O145">
         <f t="shared" ca="1" si="22"/>
-        <v>1.4335483237838909</v>
+        <v>1.5412980979861146</v>
       </c>
       <c r="P145" s="1">
         <v>104</v>
@@ -7961,7 +7955,7 @@
     <row r="146" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O146">
         <f t="shared" ca="1" si="22"/>
-        <v>1.7538105238574682</v>
+        <v>1.4002656051541726</v>
       </c>
       <c r="P146" s="1">
         <v>108</v>
@@ -7973,7 +7967,7 @@
     <row r="147" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O147">
         <f t="shared" ca="1" si="22"/>
-        <v>1.6171071242309241</v>
+        <v>1.9726119038171168</v>
       </c>
       <c r="P147" s="1">
         <v>109</v>
@@ -7985,7 +7979,7 @@
     <row r="148" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O148">
         <f t="shared" ca="1" si="22"/>
-        <v>1.0461073443884419</v>
+        <v>1.9523705147290853</v>
       </c>
       <c r="P148" s="1">
         <v>110</v>
@@ -7997,7 +7991,7 @@
     <row r="149" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O149">
         <f t="shared" ca="1" si="22"/>
-        <v>1.9483988670150691</v>
+        <v>1.001815456474938</v>
       </c>
       <c r="P149" s="1">
         <v>111</v>
@@ -8009,7 +8003,7 @@
     <row r="150" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O150">
         <f t="shared" ca="1" si="22"/>
-        <v>1.0493398153445495</v>
+        <v>1.9477166351452571</v>
       </c>
       <c r="P150" s="1">
         <v>112</v>
@@ -8021,7 +8015,7 @@
     <row r="151" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O151">
         <f t="shared" ca="1" si="22"/>
-        <v>1.1760113813311679</v>
+        <v>1.784670431669944</v>
       </c>
       <c r="P151" s="1">
         <v>113</v>
@@ -8033,7 +8027,7 @@
     <row r="152" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O152">
         <f t="shared" ca="1" si="22"/>
-        <v>1.908493416413017</v>
+        <v>1.4050426024404139</v>
       </c>
       <c r="P152" s="1">
         <v>114</v>
@@ -8045,7 +8039,7 @@
     <row r="153" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O153">
         <f t="shared" ca="1" si="22"/>
-        <v>1.0337386028857027</v>
+        <v>1.6388929889911719</v>
       </c>
       <c r="P153" s="1">
         <v>115</v>
@@ -8057,7 +8051,7 @@
     <row r="154" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O154">
         <f t="shared" ca="1" si="22"/>
-        <v>1.9732811488212318</v>
+        <v>1.179192425658774</v>
       </c>
       <c r="P154" s="1">
         <v>116</v>
@@ -8069,7 +8063,7 @@
     <row r="155" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O155">
         <f t="shared" ca="1" si="22"/>
-        <v>1.7769085476308795</v>
+        <v>1.3667578879281472</v>
       </c>
       <c r="P155" s="1">
         <v>117</v>
@@ -8081,7 +8075,7 @@
     <row r="156" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O156">
         <f t="shared" ca="1" si="22"/>
-        <v>1.5683651710770388</v>
+        <v>1.533541990166043</v>
       </c>
       <c r="P156" s="1">
         <v>121</v>
@@ -8093,7 +8087,7 @@
     <row r="157" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O157">
         <f t="shared" ca="1" si="22"/>
-        <v>1.0282975161509644</v>
+        <v>1.3203928738916897</v>
       </c>
       <c r="P157" s="1">
         <v>122</v>
@@ -8105,7 +8099,7 @@
     <row r="158" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O158">
         <f t="shared" ca="1" si="22"/>
-        <v>1.688364997666655</v>
+        <v>1.7942744499494765</v>
       </c>
       <c r="P158" s="1">
         <v>123</v>
@@ -8117,7 +8111,7 @@
     <row r="159" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O159">
         <f t="shared" ca="1" si="22"/>
-        <v>1.2080017843691748</v>
+        <v>1.1548658320594134</v>
       </c>
       <c r="P159" s="1">
         <v>124</v>
@@ -8129,7 +8123,7 @@
     <row r="160" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O160">
         <f t="shared" ca="1" si="22"/>
-        <v>1.6425331745764264</v>
+        <v>1.2552894234770235</v>
       </c>
       <c r="P160" s="1">
         <v>134</v>
@@ -8141,7 +8135,7 @@
     <row r="161" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O161">
         <f t="shared" ca="1" si="22"/>
-        <v>1.8713126635952637</v>
+        <v>1.4876585314037722</v>
       </c>
       <c r="P161" s="1">
         <v>135</v>
@@ -8153,7 +8147,7 @@
     <row r="162" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O162">
         <f t="shared" ca="1" si="22"/>
-        <v>1.9207436647612721</v>
+        <v>1.7543117197548472</v>
       </c>
       <c r="P162" s="1">
         <v>136</v>
@@ -8165,7 +8159,7 @@
     <row r="163" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O163">
         <f t="shared" ca="1" si="22"/>
-        <v>1.426463804652113</v>
+        <v>1.1249752578945378</v>
       </c>
       <c r="P163" s="1">
         <v>137</v>
@@ -8177,7 +8171,7 @@
     <row r="164" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O164">
         <f t="shared" ca="1" si="22"/>
-        <v>1.0559011448667852</v>
+        <v>1.9867750886518767</v>
       </c>
       <c r="P164" s="1">
         <v>147</v>
@@ -8189,7 +8183,7 @@
     <row r="165" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O165">
         <f t="shared" ca="1" si="22"/>
-        <v>1.3912194474467752</v>
+        <v>1.0521183010826065</v>
       </c>
       <c r="P165" s="1">
         <v>160</v>
@@ -8201,7 +8195,7 @@
     <row r="166" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O166">
         <f t="shared" ca="1" si="22"/>
-        <v>2.4074659942086143</v>
+        <v>2.082705020186955</v>
       </c>
       <c r="P166" s="1">
         <v>125</v>
@@ -8213,7 +8207,7 @@
     <row r="167" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O167">
         <f t="shared" ca="1" si="22"/>
-        <v>2.2609931943446018</v>
+        <v>2.2949032849328961</v>
       </c>
       <c r="P167" s="1">
         <v>126</v>
@@ -8225,7 +8219,7 @@
     <row r="168" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O168">
         <f t="shared" ca="1" si="22"/>
-        <v>2.0451219544345527</v>
+        <v>2.2454201575770121</v>
       </c>
       <c r="P168" s="1">
         <v>127</v>
@@ -8237,7 +8231,7 @@
     <row r="169" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O169">
         <f t="shared" ca="1" si="22"/>
-        <v>2.920409239780271</v>
+        <v>2.1795996471593178</v>
       </c>
       <c r="P169" s="1">
         <v>128</v>
@@ -8249,7 +8243,7 @@
     <row r="170" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O170">
         <f t="shared" ca="1" si="22"/>
-        <v>2.5804636789270066</v>
+        <v>2.7761554199331009</v>
       </c>
       <c r="P170" s="1">
         <v>129</v>
@@ -8261,7 +8255,7 @@
     <row r="171" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O171">
         <f t="shared" ca="1" si="22"/>
-        <v>2.7206069086465581</v>
+        <v>2.9124275599355944</v>
       </c>
       <c r="P171" s="1">
         <v>130</v>
@@ -8273,7 +8267,7 @@
     <row r="172" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O172">
         <f t="shared" ca="1" si="22"/>
-        <v>2.2976429030775858</v>
+        <v>2.8004862057490247</v>
       </c>
       <c r="P172" s="1">
         <v>138</v>
@@ -8285,7 +8279,7 @@
     <row r="173" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O173">
         <f t="shared" ca="1" si="22"/>
-        <v>2.0513317477575139</v>
+        <v>2.459336137076813</v>
       </c>
       <c r="P173" s="1">
         <v>139</v>
@@ -8297,7 +8291,7 @@
     <row r="174" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O174">
         <f t="shared" ca="1" si="22"/>
-        <v>2.3716948860138327</v>
+        <v>2.3450347158310674</v>
       </c>
       <c r="P174" s="1">
         <v>140</v>
@@ -8309,7 +8303,7 @@
     <row r="175" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O175">
         <f t="shared" ca="1" si="22"/>
-        <v>2.154310377636953</v>
+        <v>2.9745128586245482</v>
       </c>
       <c r="P175" s="1">
         <v>141</v>
@@ -8321,7 +8315,7 @@
     <row r="176" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O176">
         <f t="shared" ca="1" si="22"/>
-        <v>2.2798447201759897</v>
+        <v>2.0874221938588251</v>
       </c>
       <c r="P176" s="1">
         <v>142</v>
@@ -8333,7 +8327,7 @@
     <row r="177" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O177">
         <f t="shared" ca="1" si="22"/>
-        <v>2.59249056135334</v>
+        <v>2.0968195270118555</v>
       </c>
       <c r="P177" s="1">
         <v>143</v>
@@ -8345,7 +8339,7 @@
     <row r="178" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O178">
         <f t="shared" ca="1" si="22"/>
-        <v>2.4219336762809256</v>
+        <v>2.6381430851960124</v>
       </c>
       <c r="P178" s="1">
         <v>148</v>
@@ -8357,7 +8351,7 @@
     <row r="179" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O179">
         <f t="shared" ca="1" si="22"/>
-        <v>2.2432041153425679</v>
+        <v>2.2602939525526686</v>
       </c>
       <c r="P179" s="1">
         <v>149</v>
@@ -8369,7 +8363,7 @@
     <row r="180" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O180">
         <f t="shared" ca="1" si="22"/>
-        <v>2.0035863748764622</v>
+        <v>2.2668476305164802</v>
       </c>
       <c r="P180" s="1">
         <v>150</v>
@@ -8381,7 +8375,7 @@
     <row r="181" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O181">
         <f t="shared" ca="1" si="22"/>
-        <v>2.2951147206237805</v>
+        <v>2.1845410221884114</v>
       </c>
       <c r="P181" s="1">
         <v>151</v>
@@ -8393,7 +8387,7 @@
     <row r="182" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O182">
         <f t="shared" ca="1" si="22"/>
-        <v>2.4240468289836934</v>
+        <v>2.5262594219308654</v>
       </c>
       <c r="P182" s="1">
         <v>152</v>
@@ -8405,7 +8399,7 @@
     <row r="183" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O183">
         <f t="shared" ca="1" si="22"/>
-        <v>2.9535892771474339</v>
+        <v>2.8691609912209599</v>
       </c>
       <c r="P183" s="1">
         <v>153</v>
@@ -8417,7 +8411,7 @@
     <row r="184" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O184">
         <f t="shared" ca="1" si="22"/>
-        <v>2.4557711525468302</v>
+        <v>2.6933240106624323</v>
       </c>
       <c r="P184" s="1">
         <v>154</v>
@@ -8429,7 +8423,7 @@
     <row r="185" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O185">
         <f t="shared" ca="1" si="22"/>
-        <v>2.2187880304122647</v>
+        <v>2.1228220795096262</v>
       </c>
       <c r="P185" s="1">
         <v>155</v>
@@ -8441,7 +8435,7 @@
     <row r="186" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O186">
         <f t="shared" ca="1" si="22"/>
-        <v>2.6071711637420161</v>
+        <v>2.646584019271625</v>
       </c>
       <c r="P186" s="1">
         <v>156</v>
@@ -8453,7 +8447,7 @@
     <row r="187" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O187">
         <f t="shared" ca="1" si="22"/>
-        <v>2.918795360878562</v>
+        <v>2.1628951353380503</v>
       </c>
       <c r="P187" s="1">
         <v>161</v>
@@ -8465,7 +8459,7 @@
     <row r="188" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O188">
         <f t="shared" ca="1" si="22"/>
-        <v>2.0051640064158267</v>
+        <v>2.1116056135821677</v>
       </c>
       <c r="P188" s="1">
         <v>162</v>
@@ -8477,7 +8471,7 @@
     <row r="189" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O189">
         <f t="shared" ca="1" si="22"/>
-        <v>2.7284151418549198</v>
+        <v>2.7545136783638022</v>
       </c>
       <c r="P189" s="1">
         <v>163</v>
@@ -8489,7 +8483,7 @@
     <row r="190" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O190">
         <f t="shared" ca="1" si="22"/>
-        <v>2.2471350941225352</v>
+        <v>2.8554466576411395</v>
       </c>
       <c r="P190" s="1">
         <v>164</v>
@@ -8501,7 +8495,7 @@
     <row r="191" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O191">
         <f t="shared" ca="1" si="22"/>
-        <v>2.5237400587844681</v>
+        <v>2.7857485151850234</v>
       </c>
       <c r="P191" s="1">
         <v>165</v>
@@ -8513,7 +8507,7 @@
     <row r="192" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O192">
         <f t="shared" ca="1" si="22"/>
-        <v>2.280873054801873</v>
+        <v>2.8413636353442993</v>
       </c>
       <c r="P192" s="1">
         <v>166</v>
@@ -8525,7 +8519,7 @@
     <row r="193" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O193">
         <f t="shared" ca="1" si="22"/>
-        <v>2.618665176201481</v>
+        <v>2.1908544940951442</v>
       </c>
       <c r="P193" s="1">
         <v>167</v>
@@ -8537,7 +8531,7 @@
     <row r="194" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O194">
         <f t="shared" ca="1" si="22"/>
-        <v>2.5553603395948414</v>
+        <v>2.7314357800529949</v>
       </c>
       <c r="P194" s="1">
         <v>168</v>
@@ -8549,7 +8543,7 @@
     <row r="195" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O195">
         <f t="shared" ref="O195:O222" ca="1" si="23">RAND()+Q195-1</f>
-        <v>2.3097852014917875</v>
+        <v>2.5489831040007207</v>
       </c>
       <c r="P195" s="1">
         <v>169</v>
@@ -8561,7 +8555,7 @@
     <row r="196" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O196">
         <f t="shared" ca="1" si="23"/>
-        <v>2.5489449771962551</v>
+        <v>2.4750465276016471</v>
       </c>
       <c r="P196" s="1">
         <v>174</v>
@@ -8573,7 +8567,7 @@
     <row r="197" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O197">
         <f t="shared" ca="1" si="23"/>
-        <v>2.1483745327361938</v>
+        <v>2.2063093056340839</v>
       </c>
       <c r="P197" s="1">
         <v>175</v>
@@ -8585,7 +8579,7 @@
     <row r="198" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O198">
         <f t="shared" ca="1" si="23"/>
-        <v>2.2985162155148013</v>
+        <v>2.1395867086563691</v>
       </c>
       <c r="P198" s="1">
         <v>176</v>
@@ -8597,7 +8591,7 @@
     <row r="199" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O199">
         <f t="shared" ca="1" si="23"/>
-        <v>2.6817322971690478</v>
+        <v>2.5820059982832793</v>
       </c>
       <c r="P199" s="1">
         <v>177</v>
@@ -8609,7 +8603,7 @@
     <row r="200" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O200">
         <f t="shared" ca="1" si="23"/>
-        <v>2.5968313429970582</v>
+        <v>2.5051398777787344</v>
       </c>
       <c r="P200" s="1">
         <v>178</v>
@@ -8621,7 +8615,7 @@
     <row r="201" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O201">
         <f t="shared" ca="1" si="23"/>
-        <v>2.4236829171693546</v>
+        <v>2.6477451705295119</v>
       </c>
       <c r="P201" s="1">
         <v>179</v>
@@ -8633,7 +8627,7 @@
     <row r="202" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O202">
         <f t="shared" ca="1" si="23"/>
-        <v>2.9008393659041851</v>
+        <v>2.0763933840089672</v>
       </c>
       <c r="P202" s="1">
         <v>180</v>
@@ -8645,7 +8639,7 @@
     <row r="203" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O203">
         <f t="shared" ca="1" si="23"/>
-        <v>2.6275655462014154</v>
+        <v>2.3815650317726584</v>
       </c>
       <c r="P203" s="1">
         <v>181</v>
@@ -8657,7 +8651,7 @@
     <row r="204" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O204">
         <f t="shared" ca="1" si="23"/>
-        <v>2.0889356528317715</v>
+        <v>2.4598262198569487</v>
       </c>
       <c r="P204" s="1">
         <v>182</v>
@@ -8669,7 +8663,7 @@
     <row r="205" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O205">
         <f t="shared" ca="1" si="23"/>
-        <v>2.2671625451645268</v>
+        <v>2.3206033828445234</v>
       </c>
       <c r="P205" s="1">
         <v>190</v>
@@ -8681,7 +8675,7 @@
     <row r="206" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O206">
         <f t="shared" ca="1" si="23"/>
-        <v>2.6407324537158732</v>
+        <v>2.8593031265457594</v>
       </c>
       <c r="P206" s="1">
         <v>191</v>
@@ -8693,7 +8687,7 @@
     <row r="207" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O207">
         <f t="shared" ca="1" si="23"/>
-        <v>2.6014973395768761</v>
+        <v>2.6440943493442282</v>
       </c>
       <c r="P207" s="1">
         <v>192</v>
@@ -8705,7 +8699,7 @@
     <row r="208" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O208">
         <f t="shared" ca="1" si="23"/>
-        <v>2.6422437600098814</v>
+        <v>2.2383285773665831</v>
       </c>
       <c r="P208" s="1">
         <v>193</v>
@@ -8717,7 +8711,7 @@
     <row r="209" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O209">
         <f t="shared" ca="1" si="23"/>
-        <v>2.9532412561146359</v>
+        <v>2.91365432261719</v>
       </c>
       <c r="P209" s="1">
         <v>194</v>
@@ -8729,7 +8723,7 @@
     <row r="210" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O210">
         <f t="shared" ca="1" si="23"/>
-        <v>2.317509813795148</v>
+        <v>2.5827444268787252</v>
       </c>
       <c r="P210" s="1">
         <v>195</v>
@@ -8741,7 +8735,7 @@
     <row r="211" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O211">
         <f t="shared" ca="1" si="23"/>
-        <v>2.2636384952618229</v>
+        <v>2.3260840341608975</v>
       </c>
       <c r="P211" s="1">
         <v>203</v>
@@ -8753,7 +8747,7 @@
     <row r="212" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O212">
         <f t="shared" ca="1" si="23"/>
-        <v>2.547011214009562</v>
+        <v>2.0262333452817329</v>
       </c>
       <c r="P212" s="1">
         <v>204</v>
@@ -8765,7 +8759,7 @@
     <row r="213" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O213">
         <f t="shared" ca="1" si="23"/>
-        <v>2.7658140613647948</v>
+        <v>2.960738108108802</v>
       </c>
       <c r="P213" s="1">
         <v>205</v>
@@ -8777,7 +8771,7 @@
     <row r="214" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O214">
         <f t="shared" ca="1" si="23"/>
-        <v>2.4273060109489082</v>
+        <v>2.4863261685587479</v>
       </c>
       <c r="P214" s="1">
         <v>206</v>
@@ -8789,7 +8783,7 @@
     <row r="215" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O215">
         <f t="shared" ca="1" si="23"/>
-        <v>2.3756147398347838</v>
+        <v>2.458516175019374</v>
       </c>
       <c r="P215" s="1">
         <v>207</v>
@@ -8801,7 +8795,7 @@
     <row r="216" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O216">
         <f t="shared" ca="1" si="23"/>
-        <v>2.5733191645225881</v>
+        <v>2.7364060774103458</v>
       </c>
       <c r="P216" s="1">
         <v>208</v>
@@ -8813,7 +8807,7 @@
     <row r="217" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O217">
         <f t="shared" ca="1" si="23"/>
-        <v>2.371562636394724</v>
+        <v>2.251128791838632</v>
       </c>
       <c r="P217" s="1">
         <v>216</v>
@@ -8825,7 +8819,7 @@
     <row r="218" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O218">
         <f t="shared" ca="1" si="23"/>
-        <v>2.9233594739757156</v>
+        <v>2.8324159213267119</v>
       </c>
       <c r="P218" s="1">
         <v>217</v>
@@ -8837,7 +8831,7 @@
     <row r="219" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O219">
         <f t="shared" ca="1" si="23"/>
-        <v>2.3710708568553396</v>
+        <v>2.6213012140328602</v>
       </c>
       <c r="P219" s="1">
         <v>218</v>
@@ -8849,7 +8843,7 @@
     <row r="220" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O220">
         <f t="shared" ca="1" si="23"/>
-        <v>2.3581203636957091</v>
+        <v>2.4823901547978795</v>
       </c>
       <c r="P220" s="1">
         <v>219</v>
@@ -8861,7 +8855,7 @@
     <row r="221" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O221">
         <f t="shared" ca="1" si="23"/>
-        <v>2.0741894238366507</v>
+        <v>2.9085951059408774</v>
       </c>
       <c r="P221" s="1">
         <v>220</v>
@@ -8873,7 +8867,7 @@
     <row r="222" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O222">
         <f t="shared" ca="1" si="23"/>
-        <v>2.1652813875890606</v>
+        <v>2.1788827244733739</v>
       </c>
       <c r="P222" s="1">
         <v>221</v>
@@ -8888,7 +8882,7 @@
     <sortCondition ref="P2:P222"/>
   </sortState>
   <conditionalFormatting sqref="W1:AI17">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="notEqual">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="notEqual">
       <formula>" "</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9066,7 +9060,7 @@
       </c>
       <c r="Q2" s="1">
         <f ca="1">RANDBETWEEN(1,$C$19)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R2" s="1">
         <f ca="1">RANDBETWEEN(1,$C$20)</f>
@@ -9074,7 +9068,7 @@
       </c>
       <c r="S2" s="1">
         <f ca="1">IF(R2&gt;$C$23,"",$C$22*(R2-1)+Q2)</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="U2" s="2" t="str">
         <f t="shared" ref="U2:U17" ca="1" si="2">IF(ISNUMBER(MATCH(A2,$S$2:$S$26,0)),A2," ")</f>
@@ -9088,13 +9082,13 @@
         <f t="shared" ref="W2:W17" ca="1" si="4">IF(ISNUMBER(MATCH(C2,$S$2:$S$26,0)),C2," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="X2" s="2">
+      <c r="X2" s="2" t="str">
         <f t="shared" ref="X2:X17" ca="1" si="5">IF(ISNUMBER(MATCH(D2,$S$2:$S$26,0)),D2," ")</f>
-        <v>17</v>
-      </c>
-      <c r="Y2" s="2" t="str">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="Y2" s="2">
         <f t="shared" ref="Y2:Y17" ca="1" si="6">IF(ISNUMBER(MATCH(E2,$S$2:$S$26,0)),E2," ")</f>
-        <v xml:space="preserve"> </v>
+        <v>18</v>
       </c>
       <c r="Z2" s="2" t="str">
         <f t="shared" ref="Z2:Z17" ca="1" si="7">IF(ISNUMBER(MATCH(F2,$S$2:$S$26,0)),F2," ")</f>
@@ -9108,13 +9102,13 @@
         <f t="shared" ref="AB2:AB17" ca="1" si="9">IF(ISNUMBER(MATCH(H2,$S$2:$S$26,0)),H2," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="AC2" s="2">
+      <c r="AC2" s="2" t="str">
         <f t="shared" ref="AC2:AC17" ca="1" si="10">IF(ISNUMBER(MATCH(I2,$S$2:$S$26,0)),I2," ")</f>
-        <v>22</v>
-      </c>
-      <c r="AD2" s="2" t="str">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="AD2" s="2">
         <f t="shared" ref="AD2:AD17" ca="1" si="11">IF(ISNUMBER(MATCH(J2,$S$2:$S$26,0)),J2," ")</f>
-        <v xml:space="preserve"> </v>
+        <v>23</v>
       </c>
       <c r="AE2" s="2" t="str">
         <f t="shared" ref="AE2:AE17" ca="1" si="12">IF(ISNUMBER(MATCH(K2,$S$2:$S$26,0)),K2," ")</f>
@@ -9185,7 +9179,7 @@
       <c r="P3" s="1"/>
       <c r="Q3" s="1">
         <f t="shared" ref="Q3:Q10" ca="1" si="16">IF(S2="","",IF(Q2+$C$19&lt;=$C$22,Q2+$C$19,$Q$2))</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R3" s="1">
         <f ca="1">IF(S2="","",IF(Q3&lt;&gt;$Q$2,R2,R2+$C$20))</f>
@@ -9193,7 +9187,7 @@
       </c>
       <c r="S3" s="1">
         <f t="shared" ref="S3:S23" ca="1" si="17">IF(R3&gt;$C$23,"",$C$22*(R3-1)+Q3)</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U3" s="2" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -9304,7 +9298,7 @@
       <c r="P4" s="1"/>
       <c r="Q4" s="1">
         <f t="shared" ca="1" si="16"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R4" s="1">
         <f t="shared" ref="R4:R23" ca="1" si="18">IF(S3="","",IF(Q4&lt;&gt;$Q$2,R3,R3+$C$20))</f>
@@ -9312,7 +9306,7 @@
       </c>
       <c r="S4" s="1">
         <f t="shared" ca="1" si="17"/>
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="U4" s="2" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -9423,7 +9417,7 @@
       <c r="P5" s="1"/>
       <c r="Q5" s="1">
         <f t="shared" ca="1" si="16"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R5" s="1">
         <f t="shared" ca="1" si="18"/>
@@ -9431,7 +9425,7 @@
       </c>
       <c r="S5" s="1">
         <f t="shared" ca="1" si="17"/>
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="U5" s="2" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -9542,7 +9536,7 @@
       <c r="P6" s="1"/>
       <c r="Q6" s="1">
         <f t="shared" ca="1" si="16"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R6" s="1">
         <f t="shared" ca="1" si="18"/>
@@ -9550,7 +9544,7 @@
       </c>
       <c r="S6" s="1">
         <f t="shared" ca="1" si="17"/>
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="U6" s="2" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -9564,13 +9558,13 @@
         <f t="shared" ca="1" si="4"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="X6" s="2">
+      <c r="X6" s="2" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>69</v>
-      </c>
-      <c r="Y6" s="2" t="str">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="Y6" s="2">
         <f t="shared" ca="1" si="6"/>
-        <v xml:space="preserve"> </v>
+        <v>70</v>
       </c>
       <c r="Z6" s="2" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -9584,13 +9578,13 @@
         <f t="shared" ca="1" si="9"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="AC6" s="2">
+      <c r="AC6" s="2" t="str">
         <f t="shared" ca="1" si="10"/>
-        <v>74</v>
-      </c>
-      <c r="AD6" s="2" t="str">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="AD6" s="2">
         <f t="shared" ca="1" si="11"/>
-        <v xml:space="preserve"> </v>
+        <v>75</v>
       </c>
       <c r="AE6" s="2" t="str">
         <f t="shared" ca="1" si="12"/>
@@ -9661,7 +9655,7 @@
       <c r="P7" s="1"/>
       <c r="Q7" s="1">
         <f t="shared" ca="1" si="16"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R7" s="1">
         <f t="shared" ca="1" si="18"/>
@@ -9669,7 +9663,7 @@
       </c>
       <c r="S7" s="1">
         <f t="shared" ca="1" si="17"/>
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="U7" s="2" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -9780,7 +9774,7 @@
       <c r="P8" s="1"/>
       <c r="Q8" s="1">
         <f t="shared" ca="1" si="16"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R8" s="1">
         <f t="shared" ca="1" si="18"/>
@@ -9788,7 +9782,7 @@
       </c>
       <c r="S8" s="1">
         <f t="shared" ca="1" si="17"/>
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="U8" s="2" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -9899,7 +9893,7 @@
       <c r="P9" s="1"/>
       <c r="Q9" s="1">
         <f t="shared" ca="1" si="16"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R9" s="1">
         <f t="shared" ca="1" si="18"/>
@@ -9907,7 +9901,7 @@
       </c>
       <c r="S9" s="1">
         <f t="shared" ca="1" si="17"/>
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="U9" s="2" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -10018,7 +10012,7 @@
       <c r="P10" s="1"/>
       <c r="Q10" s="1">
         <f t="shared" ca="1" si="16"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R10" s="1">
         <f t="shared" ca="1" si="18"/>
@@ -10040,13 +10034,13 @@
         <f t="shared" ca="1" si="4"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="X10" s="2">
+      <c r="X10" s="2" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>121</v>
-      </c>
-      <c r="Y10" s="2" t="str">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="Y10" s="2">
         <f t="shared" ca="1" si="6"/>
-        <v xml:space="preserve"> </v>
+        <v>122</v>
       </c>
       <c r="Z10" s="2" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -10060,13 +10054,13 @@
         <f t="shared" ca="1" si="9"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="AC10" s="2">
+      <c r="AC10" s="2" t="str">
         <f t="shared" ca="1" si="10"/>
-        <v>126</v>
-      </c>
-      <c r="AD10" s="2" t="str">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="AD10" s="2">
         <f t="shared" ca="1" si="11"/>
-        <v xml:space="preserve"> </v>
+        <v>127</v>
       </c>
       <c r="AE10" s="2" t="str">
         <f t="shared" ca="1" si="12"/>
@@ -10516,13 +10510,13 @@
         <f t="shared" ca="1" si="4"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="X14" s="2">
+      <c r="X14" s="2" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>173</v>
-      </c>
-      <c r="Y14" s="2" t="str">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="Y14" s="2">
         <f t="shared" ca="1" si="6"/>
-        <v xml:space="preserve"> </v>
+        <v>174</v>
       </c>
       <c r="Z14" s="2" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -10536,13 +10530,13 @@
         <f t="shared" ca="1" si="9"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="AC14" s="2">
+      <c r="AC14" s="2" t="str">
         <f t="shared" ca="1" si="10"/>
-        <v>178</v>
-      </c>
-      <c r="AD14" s="2" t="str">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="AD14" s="2">
         <f t="shared" ca="1" si="11"/>
-        <v xml:space="preserve"> </v>
+        <v>179</v>
       </c>
       <c r="AE14" s="2" t="str">
         <f t="shared" ca="1" si="12"/>
@@ -11030,7 +11024,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="U1:AG17">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="notEqual">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="notEqual">
       <formula>" "</formula>
     </cfRule>
   </conditionalFormatting>
